--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45093</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44809</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45544</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>45232</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>44893</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>45230</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44936</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>45907</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45371</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>44914</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>45558</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>45531</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44461</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44501</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44529</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44594</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44474</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44847</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44482</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44846</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44511</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44581</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44572</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44636</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44483</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44511</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44511</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44517</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>44820</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44474</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44511</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44502</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44522</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44859</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44550</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>44790</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44589</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44482</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44466</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44811</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44481</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44517</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45378</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45252</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44927</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44847</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45397</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44735</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45501</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>45501</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>45243</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45037</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>45538</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45749</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>45705</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>45294</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>45264</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45419</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>45531</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45037</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>45163</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44754</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45568</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>44966</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>44510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>45252</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>45683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45310</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>45548</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45271</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45720</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45279</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>44657</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>45287</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>45420</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>44825</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44768</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>45579</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>45309</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>46139</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>45271</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44489</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45112</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>45807</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>45245</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>45811</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>45747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>45519</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>45910</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44942</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>45923</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>44581</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44581</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45694</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>45280</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45931</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>45931</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45931</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45931</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45931</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>45931</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>45931</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45642</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44680</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>45934</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>45527</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>45427</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45378</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>45953</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45953</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>46150</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>45175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>45956</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44847</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45961</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>45961</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45965</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44995</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45640</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>44578</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>44489</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>44991</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>45384</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>45098</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>45642</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>45435</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>45978</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>45109</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45525</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44942</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>45978</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45709</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45349</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45797</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45404</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>44550</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45399</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>45399</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44623</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>46162</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45378</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>44959</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45694</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45629</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>45378</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45548</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>46001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45061</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>44481</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45586</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45287</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>44927</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44592</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45271</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>46020</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45166</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46171</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>44511</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45463</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>46041</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>44941</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44571</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45601</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44915</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45582</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45684</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45574</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>45574</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45436</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>44874</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>45600</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>45761</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44587</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45621</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45541</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45541</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45229</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45484</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>44722</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>46190</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44930</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>46094</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45636</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>45091</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>46098</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>45713</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>45713</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>46112</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45520</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44543</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>46245</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>46125</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>46125</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44907</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45253</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45367</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44792</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>46246</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45041</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45671</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44544</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>46139</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45985</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45797</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45030</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45694</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45463</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45448</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45704</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>45392</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>44655</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45367</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>44487</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>46246</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>45310</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>45397</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>44803</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>44964</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45713</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45436</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45574</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45642</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45616</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>44775</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45207</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>44565</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44746</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>45398</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45287</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45784</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45629</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>46258</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45194</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>46282</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45727</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>46282</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>46282</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46283</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45538</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45194</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>45789</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45827</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45839</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45838</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45757</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45531</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44755</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45569</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45266</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>44901</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45266</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45476</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45476</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45499</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>46037</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE276"/>
+  <dimension ref="A1:AE274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45093</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44809</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45544</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>45232</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>44893</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53498-2023</t>
+          <t>A 42668-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45230</v>
+        <v>45907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1800,20 +1800,25 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>11</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1825,374 +1830,369 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 42668-2025 artfynd.xlsx", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 42668-2025 karta.png", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 42668-2025 georefererad karta.tif", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 42668-2025 FSC-klagomål.docx", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 42668-2025 FSC-klagomål mail.docx", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 42668-2025 tillsynsbegäran.docx", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 42668-2025 tillsynsbegäran mail.docx", "A 42668-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 53498-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45230</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 1320-2023</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>44936</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>0.5</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Vanlig snok</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 23794-2023</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>45078</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>1.5</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 42668-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45907</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>11</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Kambräken</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 42668-2025 artfynd.xlsx", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 42668-2025 karta.png", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 42668-2025 georefererad karta.tif", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 42668-2025 FSC-klagomål.docx", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 42668-2025 FSC-klagomål mail.docx", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 42668-2025 tillsynsbegäran.docx", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 42668-2025 tillsynsbegäran mail.docx", "A 42668-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45371</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>44914</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>45558</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>45531</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51174-2021</t>
+          <t>A 61638-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44461</v>
+        <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 61638-2021</t>
+          <t>A 68728-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44501</v>
+        <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 68728-2021</t>
+          <t>A 5415-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44529</v>
+        <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5415-2022</t>
+          <t>A 65271-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44594</v>
+        <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 65271-2021</t>
+          <t>A 1256-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44515</v>
+        <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1256-2022</t>
+          <t>A 55070-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44572</v>
+        <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 55070-2021</t>
+          <t>A 46295-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44474</v>
+        <v>44847</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>44803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 46295-2022</t>
+          <t>A 57069-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44847</v>
+        <v>44482</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57069-2021</t>
+          <t>A 45773-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44482</v>
+        <v>44846</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 45773-2022</t>
+          <t>A 64508-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44846</v>
+        <v>44511</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64508-2021</t>
+          <t>A 2993-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44511</v>
+        <v>44581</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2993-2022</t>
+          <t>A 1330-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3657,14 +3657,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44581</v>
+        <v>44572</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 1330-2022</t>
+          <t>A 12043-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3730,14 +3730,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44572</v>
+        <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3793,7 +3793,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12043-2022</t>
+          <t>A 70942-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44636</v>
+        <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3866,7 +3866,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 70942-2021</t>
+          <t>A 65904-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44538</v>
+        <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3939,7 +3939,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 65904-2021</t>
+          <t>A 4450-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44517</v>
+        <v>44589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4450-2022</t>
+          <t>A 57314-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44589</v>
+        <v>44483</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57314-2021</t>
+          <t>A 64543-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44483</v>
+        <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4158,7 +4158,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64543-2021</t>
+          <t>A 64559-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4175,7 +4175,7 @@
         <v>44511</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64559-2021</t>
+          <t>A 65900-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44511</v>
+        <v>44517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4304,7 +4304,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 65900-2021</t>
+          <t>A 40107-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44517</v>
+        <v>44820</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4333,8 +4333,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4377,7 +4382,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40107-2022</t>
+          <t>A 4448-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4391,10 +4396,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44820</v>
+        <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4406,13 +4411,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4455,7 +4455,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 4448-2022</t>
+          <t>A 55059-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44589</v>
+        <v>44474</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4528,7 +4528,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55059-2021</t>
+          <t>A 64552-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44474</v>
+        <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64552-2021</t>
+          <t>A 62135-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44511</v>
+        <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62135-2021</t>
+          <t>A 66809-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44502</v>
+        <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>13.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 66809-2021</t>
+          <t>A 48787-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44522</v>
+        <v>44859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>13.7</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4820,7 +4820,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 48787-2022</t>
+          <t>A 73022-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44859</v>
+        <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 73022-2021</t>
+          <t>A 33907-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44550</v>
+        <v>44790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4922,8 +4922,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4966,7 +4971,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33907-2022</t>
+          <t>A 4445-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4980,10 +4985,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44790</v>
+        <v>44589</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4995,13 +5000,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4445-2022</t>
+          <t>A 57065-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44589</v>
+        <v>44482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57065-2021</t>
+          <t>A 52526-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44482</v>
+        <v>44466</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52526-2021</t>
+          <t>A 37962-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5200,14 +5200,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44466</v>
+        <v>44811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37962-2022</t>
+          <t>A 56762-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5273,14 +5273,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44811</v>
+        <v>44481</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56762-2021</t>
+          <t>A 65891-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44481</v>
+        <v>44517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 65891-2021</t>
+          <t>A 12280-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44517</v>
+        <v>45378</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12280-2024</t>
+          <t>A 59061-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45378</v>
+        <v>45252</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>7.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59061-2023</t>
+          <t>A 3-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45252</v>
+        <v>44927</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3-2023</t>
+          <t>A 14651-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44927</v>
+        <v>45397</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5718,7 +5718,7 @@
         <v>44847</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14651-2024</t>
+          <t>A 26270-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45397</v>
+        <v>44735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5920,7 +5920,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26270-2022</t>
+          <t>A 31032-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44735</v>
+        <v>45501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5993,7 +5993,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31032-2024</t>
+          <t>A 31033-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6010,7 +6010,7 @@
         <v>45501</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31033-2024</t>
+          <t>A 56641-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45501</v>
+        <v>45243</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56641-2023</t>
+          <t>A 36971-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45243</v>
+        <v>45538</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>17.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6229,7 +6229,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45037</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36971-2024</t>
+          <t>A 15962-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45538</v>
+        <v>45749</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>17.9</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6431,7 +6431,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15962-2025</t>
+          <t>A 7586-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45749</v>
+        <v>45705</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6504,7 +6504,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7586-2025</t>
+          <t>A 242-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6518,10 +6518,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45705</v>
+        <v>45294</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6533,8 +6533,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6577,7 +6582,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 242-2024</t>
+          <t>A 29615-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6591,10 +6596,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45294</v>
+        <v>44754</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6612,7 +6617,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6672,7 +6677,7 @@
         <v>45264</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6745,7 +6750,7 @@
         <v>45419</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6818,7 +6823,7 @@
         <v>45531</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6891,7 +6896,7 @@
         <v>45037</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6964,7 +6969,7 @@
         <v>45163</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7020,7 +7025,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29615-2022</t>
+          <t>A 43285-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7034,10 +7039,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44754</v>
+        <v>45568</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7049,13 +7054,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7098,7 +7098,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 43285-2024</t>
+          <t>A 6687-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45568</v>
+        <v>44966</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7171,7 +7171,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 6687-2023</t>
+          <t>A 64193-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44966</v>
+        <v>44510</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7244,7 +7244,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 64193-2021</t>
+          <t>A 38835-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44510</v>
+        <v>45547</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7317,173 +7317,173 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
+          <t>A 3851-2025</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>45683</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>A 59064-2023</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="n">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="n">
         <v>45252</v>
       </c>
-      <c r="E85" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
+      <c r="E86" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
         <v>1.1</v>
       </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" s="2" t="inlineStr"/>
-      <c r="Z85">
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="Z86">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AA85">
+      <c r="AA86">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AB85">
+      <c r="AB86">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AC85">
+      <c r="AC86">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AD85">
+      <c r="AD86">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>A 38835-2024</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="n">
-        <v>45547</v>
-      </c>
-      <c r="E86" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" s="2" t="inlineStr"/>
-    </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3851-2025</t>
+          <t>A 39039-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45683</v>
+        <v>45548</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7512,8 +7512,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7556,7 +7561,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2309-2024</t>
+          <t>A 64140-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7570,10 +7575,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45310</v>
+        <v>45279</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7586,7 +7591,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7629,7 +7634,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 39039-2024</t>
+          <t>A 62669-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7643,10 +7648,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45548</v>
+        <v>45271</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7658,13 +7663,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7707,7 +7707,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62669-2023</t>
+          <t>A 10476-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45271</v>
+        <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7736,8 +7736,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7780,7 +7785,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10476-2025</t>
+          <t>A 2309-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7794,10 +7799,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45720</v>
+        <v>45310</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7809,13 +7814,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7858,7 +7858,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 64140-2023</t>
+          <t>A 15039-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45279</v>
+        <v>44657</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7931,7 +7931,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15039-2022</t>
+          <t>A 1847-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7945,10 +7945,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44657</v>
+        <v>45671</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8004,7 +8004,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 65007-2023</t>
+          <t>A 20259-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45287</v>
+        <v>46139</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>14.2</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8077,7 +8077,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18049-2024</t>
+          <t>A 58244-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45420</v>
+        <v>45985</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8150,7 +8150,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41074-2022</t>
+          <t>A 24247-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8164,10 +8164,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44825</v>
+        <v>45797</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8223,7 +8223,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30951-2022</t>
+          <t>A 65007-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8237,10 +8237,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44768</v>
+        <v>45287</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5</v>
+        <v>14.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8296,7 +8296,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 45672-2024</t>
+          <t>A 18049-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45579</v>
+        <v>45420</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8369,7 +8369,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2077-2024</t>
+          <t>A 41074-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45309</v>
+        <v>44825</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>46139</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62807-2023</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45271</v>
+        <v>44489</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8588,7 +8588,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 30951-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8602,10 +8602,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44489</v>
+        <v>44768</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8661,7 +8661,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30599-2023</t>
+          <t>A 15472-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8675,10 +8675,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45112</v>
+        <v>45747</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>10.1</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8751,7 +8751,7 @@
         <v>45807</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 57151-2023</t>
+          <t>A 45672-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45245</v>
+        <v>45579</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8880,7 +8880,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26910-2025</t>
+          <t>A 2077-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45811</v>
+        <v>45309</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15472-2025</t>
+          <t>A 26910-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8967,10 +8967,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45747</v>
+        <v>45811</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9026,7 +9026,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33475-2024</t>
+          <t>A 62807-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9040,10 +9040,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45519</v>
+        <v>45271</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9099,7 +9099,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 43194-2025</t>
+          <t>A 47786-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9113,10 +9113,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45910</v>
+        <v>45931</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9172,7 +9172,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 2708-2023</t>
+          <t>A 47801-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9186,10 +9186,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44942</v>
+        <v>45931</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9245,7 +9245,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 45786-2025</t>
+          <t>A 47704-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45923</v>
+        <v>45931</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9318,7 +9318,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 2990-2022</t>
+          <t>A 47722-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44581</v>
+        <v>45931</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 2994-2022</t>
+          <t>A 30599-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9405,10 +9405,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44581</v>
+        <v>45112</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>10.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9464,7 +9464,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 5753-2025</t>
+          <t>A 47798-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9478,10 +9478,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45694</v>
+        <v>45931</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9537,7 +9537,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 64374-2023</t>
+          <t>A 47804-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9551,10 +9551,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45280</v>
+        <v>45931</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9610,7 +9610,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 47786-2025</t>
+          <t>A 47784-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9627,7 +9627,7 @@
         <v>45931</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9683,7 +9683,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 47801-2025</t>
+          <t>A 33475-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9697,10 +9697,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45931</v>
+        <v>45519</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9756,7 +9756,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 47704-2025</t>
+          <t>A 57151-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45931</v>
+        <v>45245</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9829,7 +9829,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 47722-2025</t>
+          <t>A 48427-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45931</v>
+        <v>45934</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9902,7 +9902,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 47798-2025</t>
+          <t>A 43194-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45931</v>
+        <v>45910</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9975,7 +9975,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 47804-2025</t>
+          <t>A 22226-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9989,10 +9989,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45931</v>
+        <v>46150</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10048,7 +10048,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 47784-2025</t>
+          <t>A 2708-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10062,10 +10062,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45931</v>
+        <v>44942</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10121,7 +10121,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59944-2024</t>
+          <t>A 52621-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45642</v>
+        <v>45953</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10194,7 +10194,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 17635-2022</t>
+          <t>A 52622-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10208,10 +10208,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44680</v>
+        <v>45953</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10267,7 +10267,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 48427-2025</t>
+          <t>A 8541-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10281,10 +10281,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45934</v>
+        <v>45709</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10340,7 +10340,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 35084-2024</t>
+          <t>A 2990-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45527</v>
+        <v>44581</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10413,7 +10413,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 18948-2024</t>
+          <t>A 2994-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45427</v>
+        <v>44581</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10486,7 +10486,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 12252-2024</t>
+          <t>A 52697-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10500,10 +10500,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45378</v>
+        <v>45956</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10559,7 +10559,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 52621-2025</t>
+          <t>A 7822-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10573,10 +10573,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45953</v>
+        <v>45349</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10632,7 +10632,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 52622-2025</t>
+          <t>A 5753-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10646,10 +10646,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45953</v>
+        <v>45694</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10705,7 +10705,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22226-2026</t>
+          <t>A 64374-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46150</v>
+        <v>45280</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10778,7 +10778,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 41526-2023</t>
+          <t>A 24262-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10792,10 +10792,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45175</v>
+        <v>45797</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10807,13 +10807,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10856,7 +10851,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 52697-2025</t>
+          <t>A 53839-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10870,10 +10865,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45956</v>
+        <v>45961</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10886,7 +10881,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10929,7 +10924,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 46117-2022</t>
+          <t>A 53841-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10943,10 +10938,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44847</v>
+        <v>45961</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10959,7 +10954,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11002,7 +10997,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 53839-2025</t>
+          <t>A 54593-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11016,10 +11011,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11032,7 +11027,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11075,7 +11070,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 53841-2025</t>
+          <t>A 23327-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11089,10 +11084,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45961</v>
+        <v>46162</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11105,7 +11100,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11148,7 +11143,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 54593-2025</t>
+          <t>A 59944-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11162,10 +11157,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45965</v>
+        <v>45642</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11178,7 +11173,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11221,7 +11216,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 11929-2023</t>
+          <t>A 17635-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11235,10 +11230,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44995</v>
+        <v>44680</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11251,7 +11246,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11294,7 +11289,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 59871-2024</t>
+          <t>A 57011-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11308,10 +11303,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45640</v>
+        <v>45978</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11323,8 +11318,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11367,7 +11367,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 2314-2022</t>
+          <t>A 35084-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11381,10 +11381,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44578</v>
+        <v>45527</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11440,7 +11440,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 18948-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11454,10 +11454,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44489</v>
+        <v>45427</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11513,7 +11513,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 10910-2023</t>
+          <t>A 56957-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11523,14 +11523,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44991</v>
+        <v>45978</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11542,8 +11542,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11586,7 +11591,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 12652-2024</t>
+          <t>A 12252-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11600,10 +11605,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45384</v>
+        <v>45378</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11616,7 +11621,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11659,7 +11664,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 27792-2023</t>
+          <t>A 24640-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11673,10 +11678,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45098</v>
+        <v>46171</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11689,7 +11694,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11732,7 +11737,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 60201-2024</t>
+          <t>A 41526-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11746,10 +11751,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45642</v>
+        <v>45175</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11761,8 +11766,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11805,7 +11815,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 20476-2024</t>
+          <t>A 46117-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11819,10 +11829,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45435</v>
+        <v>44847</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11835,7 +11845,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11878,7 +11888,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 57011-2025</t>
+          <t>A 61436-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11892,10 +11902,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45978</v>
+        <v>46001</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11907,13 +11917,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11956,7 +11961,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32839-2023</t>
+          <t>A 11929-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11970,10 +11975,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45109</v>
+        <v>44995</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11986,7 +11991,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12029,7 +12034,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 34408-2024</t>
+          <t>A 59871-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12039,14 +12044,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45525</v>
+        <v>45640</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12059,7 +12064,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12102,7 +12107,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 2688-2023</t>
+          <t>A 2314-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12116,10 +12121,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44942</v>
+        <v>44578</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12132,7 +12137,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12175,7 +12180,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 56957-2025</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12185,14 +12190,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45978</v>
+        <v>44489</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12204,13 +12209,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12253,7 +12253,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 8541-2025</t>
+          <t>A 10910-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12267,10 +12267,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45709</v>
+        <v>44991</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12326,7 +12326,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7822-2024</t>
+          <t>A 12652-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12340,10 +12340,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45349</v>
+        <v>45384</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12399,7 +12399,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 24262-2025</t>
+          <t>A 27792-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12413,10 +12413,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45797</v>
+        <v>45098</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12472,7 +12472,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 15721-2024</t>
+          <t>A 60201-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12486,10 +12486,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45404</v>
+        <v>45642</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12545,7 +12545,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 73251-2021</t>
+          <t>A 20476-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12559,10 +12559,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44550</v>
+        <v>45435</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12618,7 +12618,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 14984-2024</t>
+          <t>A 63811-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12632,10 +12632,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45399</v>
+        <v>46020</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12691,7 +12691,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 14987-2024</t>
+          <t>A 32839-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12705,10 +12705,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45399</v>
+        <v>45109</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12764,7 +12764,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 10374-2022</t>
+          <t>A 34408-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12774,14 +12774,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44623</v>
+        <v>45525</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12837,7 +12837,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 23327-2026</t>
+          <t>A 2688-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12851,10 +12851,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46162</v>
+        <v>44942</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12910,7 +12910,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 12281-2024</t>
+          <t>A 3174-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12924,10 +12924,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45378</v>
+        <v>46041</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12983,7 +12983,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 5286-2023</t>
+          <t>A 969-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12997,10 +12997,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44959</v>
+        <v>44571</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13056,7 +13056,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 5754-2025</t>
+          <t>A 15721-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13070,10 +13070,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45694</v>
+        <v>45404</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 57386-2024</t>
+          <t>A 27638-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13139,14 +13139,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45629</v>
+        <v>46190</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13158,8 +13158,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13202,7 +13207,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 12272-2024</t>
+          <t>A 73251-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13216,10 +13221,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45378</v>
+        <v>44550</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13232,7 +13237,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13275,7 +13280,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 39055-2024</t>
+          <t>A 14984-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13289,10 +13294,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45548</v>
+        <v>45399</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13304,13 +13309,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13353,7 +13353,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 61436-2025</t>
+          <t>A 14987-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13367,10 +13367,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46001</v>
+        <v>45399</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13426,7 +13426,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 21032-2023</t>
+          <t>A 10374-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13440,10 +13440,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45061</v>
+        <v>44623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13499,7 +13499,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 57483-2022</t>
+          <t>A 12281-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44896</v>
+        <v>45378</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13528,13 +13528,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13577,7 +13572,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 56765-2021</t>
+          <t>A 5286-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13591,10 +13586,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44481</v>
+        <v>44959</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13607,7 +13602,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13650,7 +13645,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 46998-2024</t>
+          <t>A 5754-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13664,10 +13659,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45586</v>
+        <v>45694</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13680,7 +13675,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13723,7 +13718,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 65008-2023</t>
+          <t>A 57386-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13737,10 +13732,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45287</v>
+        <v>45629</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13753,7 +13748,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13796,7 +13791,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 2-2023</t>
+          <t>A 12272-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13810,10 +13805,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44927</v>
+        <v>45378</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13826,7 +13821,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13869,7 +13864,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 4832-2022</t>
+          <t>A 39055-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13883,10 +13878,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44592</v>
+        <v>45548</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13896,6 +13891,11 @@
       <c r="G174" t="inlineStr">
         <is>
           <t>KIL</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -13942,7 +13942,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 62667-2023</t>
+          <t>A 21032-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13956,10 +13956,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45271</v>
+        <v>45061</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14015,7 +14015,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 63811-2025</t>
+          <t>A 57483-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14029,10 +14029,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46020</v>
+        <v>44896</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14044,8 +14044,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14088,7 +14093,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 39492-2023</t>
+          <t>A 56765-2021</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14102,10 +14107,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45166</v>
+        <v>44481</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14117,13 +14122,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>24.9</v>
+        <v>0.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14166,7 +14166,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 24640-2026</t>
+          <t>A 46998-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14180,10 +14180,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46171</v>
+        <v>45586</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14239,7 +14239,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 64518-2021</t>
+          <t>A 65008-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14253,10 +14253,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44511</v>
+        <v>45287</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 25409-2024</t>
+          <t>A 2-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14326,10 +14326,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45463</v>
+        <v>44927</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14341,13 +14341,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14390,7 +14385,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 3174-2026</t>
+          <t>A 71728-2021</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14404,10 +14399,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46041</v>
+        <v>44543</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14420,7 +14415,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14463,7 +14458,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 2263-2023</t>
+          <t>A 4832-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14477,10 +14472,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44941</v>
+        <v>44592</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14493,7 +14488,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14536,7 +14531,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 969-2022</t>
+          <t>A 62667-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14550,10 +14545,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44571</v>
+        <v>45271</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14566,7 +14561,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14609,7 +14604,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 50461-2024</t>
+          <t>A 39492-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14623,10 +14618,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45601</v>
+        <v>45166</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14638,8 +14633,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>24.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14682,7 +14682,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 61229-2022</t>
+          <t>A 13504-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14696,10 +14696,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44915</v>
+        <v>46094</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14755,7 +14755,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 46445-2024</t>
+          <t>A 33266-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14769,10 +14769,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45582</v>
+        <v>46246</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14828,7 +14828,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 4069-2025</t>
+          <t>A 64518-2021</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14842,10 +14842,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45684</v>
+        <v>44511</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14857,13 +14857,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14906,7 +14901,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 44660-2024</t>
+          <t>A 25409-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14920,10 +14915,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45574</v>
+        <v>45463</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14935,8 +14930,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14979,7 +14979,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 44666-2024</t>
+          <t>A 14036-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14993,10 +14993,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45574</v>
+        <v>46098</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15052,7 +15052,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 20745-2024</t>
+          <t>A 2263-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15066,10 +15066,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45436</v>
+        <v>44941</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15125,7 +15125,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 52438-2022</t>
+          <t>A 50461-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15139,10 +15139,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44874</v>
+        <v>45601</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15198,7 +15198,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 50252-2024</t>
+          <t>A 61229-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45600</v>
+        <v>44915</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15271,7 +15271,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 18117-2025</t>
+          <t>A 46445-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15285,10 +15285,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45761</v>
+        <v>45582</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 3996-2022</t>
+          <t>A 4069-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15358,10 +15358,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44587</v>
+        <v>45684</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15373,8 +15373,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15417,7 +15422,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 55306-2024</t>
+          <t>A 44660-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15431,10 +15436,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45621</v>
+        <v>45574</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15447,7 +15452,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15490,7 +15495,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 37620-2024</t>
+          <t>A 44666-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15504,10 +15509,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45541</v>
+        <v>45574</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15520,7 +15525,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15563,7 +15568,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 37622-2024</t>
+          <t>A 16585-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15577,10 +15582,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45541</v>
+        <v>46112</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15593,7 +15598,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15636,7 +15641,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 53416-2023</t>
+          <t>A 20745-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15650,10 +15655,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45229</v>
+        <v>45436</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15666,7 +15671,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15709,7 +15714,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 29698-2024</t>
+          <t>A 52438-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15719,14 +15724,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45484</v>
+        <v>44874</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15739,7 +15744,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15782,7 +15787,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 23786-2022</t>
+          <t>A 50252-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15796,10 +15801,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44722</v>
+        <v>45600</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15812,7 +15817,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15855,7 +15860,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 27638-2026</t>
+          <t>A 18101-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15865,14 +15870,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46190</v>
+        <v>46125</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15884,13 +15889,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15933,7 +15933,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 666-2023</t>
+          <t>A 18096-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15947,10 +15947,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44930</v>
+        <v>46125</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16006,7 +16006,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 13504-2026</t>
+          <t>A 18117-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16020,10 +16020,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46094</v>
+        <v>45761</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16079,7 +16079,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 59012-2024</t>
+          <t>A 3996-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16093,10 +16093,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45636</v>
+        <v>44587</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16152,7 +16152,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 26263-2023</t>
+          <t>A 55306-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16166,10 +16166,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45091</v>
+        <v>45621</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16225,7 +16225,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 14036-2026</t>
+          <t>A 37620-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16239,10 +16239,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46098</v>
+        <v>45541</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 8910-2025</t>
+          <t>A 37622-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16312,10 +16312,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45713</v>
+        <v>45541</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 8916-2025</t>
+          <t>A 53416-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16385,10 +16385,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45713</v>
+        <v>45229</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16444,7 +16444,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 16585-2026</t>
+          <t>A 29698-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16454,14 +16454,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46112</v>
+        <v>45484</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16517,7 +16517,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 33566-2024</t>
+          <t>A 23786-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16531,10 +16531,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45520</v>
+        <v>44722</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.8</v>
+        <v>7.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16590,7 +16590,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 71728-2021</t>
+          <t>A 33233-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16604,10 +16604,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44543</v>
+        <v>46246</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16663,7 +16663,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 33037-2026</t>
+          <t>A 666-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16677,10 +16677,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46245</v>
+        <v>44930</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16736,7 +16736,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 18101-2026</t>
+          <t>A 59012-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16750,10 +16750,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46125</v>
+        <v>45636</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16809,7 +16809,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 18096-2026</t>
+          <t>A 26263-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16823,10 +16823,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46125</v>
+        <v>45091</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16882,7 +16882,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 59503-2022</t>
+          <t>A 8910-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16896,10 +16896,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44907</v>
+        <v>45713</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16955,7 +16955,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 59200-2023</t>
+          <t>A 8916-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16969,10 +16969,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45253</v>
+        <v>45713</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17028,7 +17028,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 10634-2024</t>
+          <t>A 33566-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17042,10 +17042,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45367</v>
+        <v>45520</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17101,7 +17101,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 34402-2022</t>
+          <t>A 59503-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17115,10 +17115,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44792</v>
+        <v>44907</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17174,7 +17174,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 33266-2026</t>
+          <t>A 59200-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17188,10 +17188,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46246</v>
+        <v>45253</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 18336-2023</t>
+          <t>A 10634-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17261,10 +17261,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45041</v>
+        <v>45367</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17276,13 +17276,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17325,7 +17320,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 1847-2025</t>
+          <t>A 34402-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17339,10 +17334,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45671</v>
+        <v>44792</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17355,7 +17350,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17398,7 +17393,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 72073-2021</t>
+          <t>A 18336-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17412,10 +17407,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44544</v>
+        <v>45041</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17427,8 +17422,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>9.6</v>
+        <v>2.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17471,7 +17471,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 20259-2026</t>
+          <t>A 72073-2021</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17485,10 +17485,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46139</v>
+        <v>44544</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>9.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17544,7 +17544,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 58244-2025</t>
+          <t>A 16596-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17558,10 +17558,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45985</v>
+        <v>45030</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17617,7 +17617,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 24247-2025</t>
+          <t>A 5758-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17631,10 +17631,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45797</v>
+        <v>45694</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17690,7 +17690,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 16596-2023</t>
+          <t>A 25435-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45030</v>
+        <v>45463</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17719,8 +17719,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17763,7 +17768,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 5758-2025</t>
+          <t>A 22798-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17777,10 +17782,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45694</v>
+        <v>45448</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17792,8 +17797,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17836,7 +17846,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 25435-2024</t>
+          <t>A 7368-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17850,10 +17860,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45463</v>
+        <v>45704</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17865,13 +17875,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17914,7 +17919,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 22798-2024</t>
+          <t>A 14143-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17928,10 +17933,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45448</v>
+        <v>45392</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17943,13 +17948,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17992,7 +17992,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 7368-2025</t>
+          <t>A 14732-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18006,10 +18006,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45704</v>
+        <v>44655</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18065,7 +18065,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 14143-2024</t>
+          <t>A 10635-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45392</v>
+        <v>45367</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18138,7 +18138,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 14732-2022</t>
+          <t>A 57967-2021</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18152,10 +18152,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44655</v>
+        <v>44487</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18211,7 +18211,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 10635-2024</t>
+          <t>A 34846-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18225,10 +18225,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45367</v>
+        <v>46258</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18284,7 +18284,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 57967-2021</t>
+          <t>A 38499-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18298,10 +18298,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44487</v>
+        <v>46282</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18357,7 +18357,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 33233-2026</t>
+          <t>A 2306-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18371,10 +18371,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46246</v>
+        <v>45310</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18430,7 +18430,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 2306-2024</t>
+          <t>A 38494-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18444,10 +18444,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45310</v>
+        <v>46282</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18503,7 +18503,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 14675-2024</t>
+          <t>A 38489-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18517,10 +18517,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45397</v>
+        <v>46282</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18576,7 +18576,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 36296-2022</t>
+          <t>A 38517-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18590,10 +18590,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44803</v>
+        <v>46283</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18605,8 +18605,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18649,7 +18654,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 6015-2023</t>
+          <t>A 14675-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18663,10 +18668,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44964</v>
+        <v>45397</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18679,7 +18684,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18722,7 +18727,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 8911-2025</t>
+          <t>A 36296-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18736,10 +18741,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45713</v>
+        <v>44803</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18752,7 +18757,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18795,7 +18800,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 20743-2024</t>
+          <t>A 6015-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18809,10 +18814,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45436</v>
+        <v>44964</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18825,7 +18830,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18868,7 +18873,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 44646-2024</t>
+          <t>A 33037-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18882,10 +18887,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45574</v>
+        <v>46245</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18898,7 +18903,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18941,7 +18946,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 59938-2024</t>
+          <t>A 8911-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18955,10 +18960,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45642</v>
+        <v>45713</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18971,7 +18976,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19014,7 +19019,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 53956-2024</t>
+          <t>A 20743-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19028,10 +19033,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45616</v>
+        <v>45436</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19044,7 +19049,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19087,7 +19092,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 31621-2022</t>
+          <t>A 44646-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19101,10 +19106,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44775</v>
+        <v>45574</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19117,7 +19122,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19160,7 +19165,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 49604-2023</t>
+          <t>A 59938-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19174,10 +19179,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45207</v>
+        <v>45642</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19190,7 +19195,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19233,7 +19238,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 249-2022</t>
+          <t>A 53956-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19247,10 +19252,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44565</v>
+        <v>45616</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19263,7 +19268,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19306,7 +19311,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 28195-2022</t>
+          <t>A 31621-2022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19320,10 +19325,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44746</v>
+        <v>44775</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19335,13 +19340,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I248" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19384,7 +19384,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 14954-2024</t>
+          <t>A 49604-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19398,10 +19398,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45398</v>
+        <v>45207</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19457,7 +19457,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 65002-2023</t>
+          <t>A 249-2022</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19471,10 +19471,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45287</v>
+        <v>44565</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>6.9</v>
+        <v>5.5</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19530,7 +19530,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 22008-2025</t>
+          <t>A 28195-2022</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19544,10 +19544,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45784</v>
+        <v>44746</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19559,8 +19559,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19603,7 +19608,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 57220-2024</t>
+          <t>A 14954-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19617,10 +19622,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45629</v>
+        <v>45398</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19633,7 +19638,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19676,7 +19681,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 34846-2026</t>
+          <t>A 65002-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19690,10 +19695,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46258</v>
+        <v>45287</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19706,7 +19711,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19749,7 +19754,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 45599-2023</t>
+          <t>A 22008-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19763,10 +19768,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45194</v>
+        <v>45784</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19779,7 +19784,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19822,7 +19827,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 38499-2026</t>
+          <t>A 57220-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19836,10 +19841,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46282</v>
+        <v>45629</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19852,7 +19857,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19895,7 +19900,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 11558-2025</t>
+          <t>A 45599-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19909,10 +19914,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45727</v>
+        <v>45194</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19925,7 +19930,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19968,7 +19973,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 38494-2026</t>
+          <t>A 11558-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19982,10 +19987,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46282</v>
+        <v>45727</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20041,7 +20046,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 38489-2026</t>
+          <t>A 36795-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20055,10 +20060,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46282</v>
+        <v>45538</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20071,7 +20076,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20114,7 +20119,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 38517-2026</t>
+          <t>A 45591-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20128,10 +20133,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46283</v>
+        <v>45194</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20143,13 +20148,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20192,7 +20192,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 36795-2024</t>
+          <t>A 22566-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20206,10 +20206,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45538</v>
+        <v>45789</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>9.300000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20265,7 +20265,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 45591-2023</t>
+          <t>A 30260-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20279,10 +20279,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45194</v>
+        <v>45827</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>11</v>
+        <v>0.9</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20338,7 +20338,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 22566-2025</t>
+          <t>A 32982-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20352,10 +20352,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45789</v>
+        <v>45839</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20367,8 +20367,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I262" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20411,7 +20416,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 30260-2025</t>
+          <t>A 32410-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20425,10 +20430,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45827</v>
+        <v>45838</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20441,7 +20446,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20484,7 +20489,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 32982-2025</t>
+          <t>A 17473-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20498,10 +20503,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45839</v>
+        <v>45757</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20513,13 +20518,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I264" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20562,7 +20562,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 32410-2025</t>
+          <t>A 35449-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20576,10 +20576,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45838</v>
+        <v>45531</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20635,24 +20635,24 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 17473-2025</t>
+          <t>S 4021-2022</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45757</v>
+        <v>44755</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20708,24 +20708,24 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 35449-2024</t>
+          <t>S 3995-2024</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45531</v>
+        <v>45569</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>6.8</v>
+        <v>25.3</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20781,7 +20781,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>S 4021-2022</t>
+          <t>S 4404-2023</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20791,14 +20791,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>44755</v>
+        <v>45266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20810,8 +20810,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I268" t="n">
-        <v>0.9</v>
+        <v>16.6</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20854,7 +20859,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>S 3995-2024</t>
+          <t>S 6966-2022</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20864,14 +20869,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45569</v>
+        <v>44901</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20883,8 +20888,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I269" t="n">
-        <v>25.3</v>
+        <v>37.7</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -20927,7 +20937,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>S 4404-2023</t>
+          <t>S 4398-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -20944,7 +20954,7 @@
         <v>45266</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20962,7 +20972,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>16.6</v>
+        <v>22.4</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21005,7 +21015,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 6966-2022</t>
+          <t>S 2561-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21015,14 +21025,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>44901</v>
+        <v>45476</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21034,13 +21044,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I271" t="n">
-        <v>37.7</v>
+        <v>13.6</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21083,7 +21088,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 4398-2023</t>
+          <t>S 2562-2024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21093,14 +21098,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45266</v>
+        <v>45476</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21114,11 +21119,11 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I272" t="n">
-        <v>22.4</v>
+        <v>56.9</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21161,7 +21166,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 2561-2024</t>
+          <t>S 2877-2024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21175,10 +21180,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45476</v>
+        <v>45499</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21191,7 +21196,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>13.6</v>
+        <v>15.1</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21231,10 +21236,10 @@
       </c>
       <c r="V273" s="2" t="inlineStr"/>
     </row>
-    <row r="274" ht="15" customHeight="1">
+    <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>S 2562-2024</t>
+          <t>S 114-2026</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21244,14 +21249,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45476</v>
+        <v>46037</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21265,11 +21270,11 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I274" t="n">
-        <v>56.9</v>
+        <v>20.8</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21308,157 +21313,6 @@
         <v>0</v>
       </c>
       <c r="V274" s="2" t="inlineStr"/>
-    </row>
-    <row r="275" ht="15" customHeight="1">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>S 2877-2024</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D275" s="1" t="n">
-        <v>45499</v>
-      </c>
-      <c r="E275" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I275" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="J275" t="n">
-        <v>0</v>
-      </c>
-      <c r="K275" t="n">
-        <v>0</v>
-      </c>
-      <c r="L275" t="n">
-        <v>0</v>
-      </c>
-      <c r="M275" t="n">
-        <v>0</v>
-      </c>
-      <c r="N275" t="n">
-        <v>0</v>
-      </c>
-      <c r="O275" t="n">
-        <v>0</v>
-      </c>
-      <c r="P275" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
-      <c r="R275" t="n">
-        <v>0</v>
-      </c>
-      <c r="S275" t="n">
-        <v>0</v>
-      </c>
-      <c r="T275" t="n">
-        <v>0</v>
-      </c>
-      <c r="U275" t="n">
-        <v>0</v>
-      </c>
-      <c r="V275" s="2" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>S 114-2026</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D276" s="1" t="n">
-        <v>46037</v>
-      </c>
-      <c r="E276" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I276" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="J276" t="n">
-        <v>0</v>
-      </c>
-      <c r="K276" t="n">
-        <v>0</v>
-      </c>
-      <c r="L276" t="n">
-        <v>0</v>
-      </c>
-      <c r="M276" t="n">
-        <v>0</v>
-      </c>
-      <c r="N276" t="n">
-        <v>0</v>
-      </c>
-      <c r="O276" t="n">
-        <v>0</v>
-      </c>
-      <c r="P276" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
-      <c r="R276" t="n">
-        <v>0</v>
-      </c>
-      <c r="S276" t="n">
-        <v>0</v>
-      </c>
-      <c r="T276" t="n">
-        <v>0</v>
-      </c>
-      <c r="U276" t="n">
-        <v>0</v>
-      </c>
-      <c r="V276" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45093</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44809</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38039-2024</t>
+          <t>A 23794-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45544</v>
+        <v>45078</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1412,46 +1412,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8909-2025</t>
+          <t>A 54177-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45713</v>
+        <v>45232</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.6</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1514,49 +1514,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 54177-2023 artfynd.xlsx", "A 54177-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 54177-2023 karta.png", "A 54177-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 54177-2023 georefererad karta.tif", "A 54177-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 54177-2023 FSC-klagomål.docx", "A 54177-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 54177-2023 FSC-klagomål mail.docx", "A 54177-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 54177-2023 tillsynsbegäran.docx", "A 54177-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 54177-2023 tillsynsbegäran mail.docx", "A 54177-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 54177-2023</t>
+          <t>A 53498-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45232</v>
+        <v>45230</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1586,20 +1586,20 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
@@ -1610,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1626,42 +1626,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 54177-2023 artfynd.xlsx", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 54177-2023 karta.png", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 54177-2023 georefererad karta.tif", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 54177-2023 FSC-klagomål.docx", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 54177-2023 FSC-klagomål mail.docx", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 54177-2023 tillsynsbegäran.docx", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 54177-2023 tillsynsbegäran mail.docx", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 56642-2022</t>
+          <t>A 1320-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44893</v>
+        <v>44936</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1690,19 +1690,14 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1736,35 +1731,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
         <v/>
       </c>
     </row>
@@ -1788,7 +1783,7 @@
         <v>45907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53498-2023</t>
+          <t>A 40853-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1895,10 +1890,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45230</v>
+        <v>45558</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1911,10 +1906,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1923,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1935,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1947,46 +1942,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1320-2023</t>
+          <t>A 62010-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2000,10 +1995,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44936</v>
+        <v>44914</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2016,13 +2011,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2056,42 +2051,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 23794-2023</t>
+          <t>A 35453-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2105,10 +2100,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45078</v>
+        <v>45531</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2121,7 +2116,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2157,39 +2152,43 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
         <v/>
       </c>
     </row>
@@ -2213,7 +2212,7 @@
         <v>45371</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2305,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 62010-2022</t>
+          <t>A 8909-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2320,10 +2319,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44914</v>
+        <v>45713</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2336,17 +2335,17 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.8</v>
+        <v>22.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2360,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2369,49 +2368,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40853-2024</t>
+          <t>A 56642-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2425,10 +2424,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45558</v>
+        <v>44893</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2440,14 +2439,19 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2477,46 +2481,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 35453-2024</t>
+          <t>A 38039-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,10 +2534,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45531</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2549,10 +2553,10 @@
         <v>4</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2586,39 +2590,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44847</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44482</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44846</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44511</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2993-2022</t>
+          <t>A 1330-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44581</v>
+        <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3647,7 +3647,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1330-2022</t>
+          <t>A 2993-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3657,14 +3657,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44572</v>
+        <v>44581</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44483</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44511</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44820</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44474</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 73022-2021</t>
+          <t>A 56762-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44550</v>
+        <v>44481</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33907-2022</t>
+          <t>A 18336-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44790</v>
+        <v>45041</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4924,11 +4924,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4445-2022</t>
+          <t>A 73022-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44589</v>
+        <v>44550</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57065-2021</t>
+          <t>A 33907-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44482</v>
+        <v>44790</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5073,8 +5073,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5117,7 +5122,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52526-2021</t>
+          <t>A 57220-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5131,10 +5136,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44466</v>
+        <v>45629</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5147,7 +5152,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5190,7 +5195,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37962-2022</t>
+          <t>A 8910-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5200,14 +5205,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44811</v>
+        <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5220,7 +5225,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5263,7 +5268,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56762-2021</t>
+          <t>A 8916-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5277,10 +5282,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44481</v>
+        <v>45713</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5293,7 +5298,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5353,7 +5358,7 @@
         <v>44517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5409,7 +5414,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12280-2024</t>
+          <t>A 72073-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5423,10 +5428,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45378</v>
+        <v>44544</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5439,7 +5444,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>9.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5482,7 +5487,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59061-2023</t>
+          <t>A 4445-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5496,10 +5501,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45252</v>
+        <v>44589</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5512,7 +5517,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5555,7 +5560,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3-2023</t>
+          <t>A 57065-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5569,10 +5574,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44927</v>
+        <v>44482</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5585,7 +5590,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5628,7 +5633,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14651-2024</t>
+          <t>A 52526-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5642,10 +5647,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45397</v>
+        <v>44466</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5658,7 +5663,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5701,7 +5706,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46288-2022</t>
+          <t>A 5754-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5715,10 +5720,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44847</v>
+        <v>45694</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5731,7 +5736,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5774,7 +5779,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 46290-2022</t>
+          <t>A 59012-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5788,10 +5793,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44847</v>
+        <v>45636</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5804,7 +5809,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>8.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5847,7 +5852,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26270-2022</t>
+          <t>A 2-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5861,10 +5866,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44735</v>
+        <v>44927</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5877,7 +5882,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5920,7 +5925,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31032-2024</t>
+          <t>A 53416-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5934,10 +5939,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45501</v>
+        <v>45229</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5950,7 +5955,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5993,7 +5998,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31033-2024</t>
+          <t>A 37962-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6003,14 +6008,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45501</v>
+        <v>44811</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6023,7 +6028,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6066,7 +6071,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56641-2023</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6080,10 +6085,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45243</v>
+        <v>44489</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6096,7 +6101,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6139,7 +6144,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36971-2024</t>
+          <t>A 62807-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6153,10 +6158,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45538</v>
+        <v>45271</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6169,7 +6174,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>17.9</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6212,7 +6217,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36305-2022</t>
+          <t>A 34402-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6226,10 +6231,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44803</v>
+        <v>44792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6242,7 +6247,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6285,7 +6290,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 17816-2023</t>
+          <t>A 14675-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6299,10 +6304,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45037</v>
+        <v>45397</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6315,7 +6320,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6358,7 +6363,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15962-2025</t>
+          <t>A 12252-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6372,10 +6377,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45749</v>
+        <v>45378</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6388,7 +6393,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6431,7 +6436,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7586-2025</t>
+          <t>A 41074-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6445,10 +6450,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45705</v>
+        <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6461,7 +6466,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6504,7 +6509,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 242-2024</t>
+          <t>A 17946-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6518,10 +6523,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45294</v>
+        <v>45419</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6533,13 +6538,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29615-2022</t>
+          <t>A 2990-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44754</v>
+        <v>44581</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6611,13 +6611,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6660,7 +6655,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61210-2023</t>
+          <t>A 2994-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6674,10 +6669,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45264</v>
+        <v>44581</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6690,7 +6685,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6733,7 +6728,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17946-2024</t>
+          <t>A 59064-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6747,10 +6742,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45419</v>
+        <v>45252</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6763,7 +6758,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6802,11 +6797,31 @@
         <v>0</v>
       </c>
       <c r="V77" s="2" t="inlineStr"/>
+      <c r="Z77">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AA77">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AB77">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AC77">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AD77">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35611-2024</t>
+          <t>A 46117-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6820,10 +6835,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45531</v>
+        <v>44847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6836,7 +6851,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6879,7 +6894,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17806-2023</t>
+          <t>A 12652-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6893,10 +6908,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45037</v>
+        <v>45384</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6909,7 +6924,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6952,7 +6967,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38760-2023</t>
+          <t>A 14984-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6966,10 +6981,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45163</v>
+        <v>45399</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6982,7 +6997,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7025,7 +7040,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43285-2024</t>
+          <t>A 14987-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7039,10 +7054,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45568</v>
+        <v>45399</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7055,7 +7070,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7098,7 +7113,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6687-2023</t>
+          <t>A 249-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7112,10 +7127,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44966</v>
+        <v>44565</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7128,7 +7143,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7171,7 +7186,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 64193-2021</t>
+          <t>A 39055-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7185,10 +7200,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44510</v>
+        <v>45548</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7200,8 +7215,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7244,7 +7264,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38835-2024</t>
+          <t>A 46288-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7258,10 +7278,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45547</v>
+        <v>44847</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7274,7 +7294,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7317,7 +7337,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3851-2025</t>
+          <t>A 46290-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7331,10 +7351,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45683</v>
+        <v>44847</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7347,7 +7367,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7390,7 +7410,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59064-2023</t>
+          <t>A 52438-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7404,10 +7424,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45252</v>
+        <v>44874</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7420,7 +7440,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7459,31 +7479,11 @@
         <v>0</v>
       </c>
       <c r="V86" s="2" t="inlineStr"/>
-      <c r="Z86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AA86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AB86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AC86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AD86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39039-2024</t>
+          <t>A 3-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45548</v>
+        <v>44927</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7512,13 +7512,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7561,7 +7556,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 64140-2023</t>
+          <t>A 65008-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7575,10 +7570,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45279</v>
+        <v>45287</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7591,7 +7586,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7634,7 +7629,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 62669-2023</t>
+          <t>A 45599-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7648,10 +7643,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45271</v>
+        <v>45194</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7664,7 +7659,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7707,7 +7702,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10476-2025</t>
+          <t>A 10635-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7721,10 +7716,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45720</v>
+        <v>45367</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7736,13 +7731,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7785,7 +7775,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2309-2024</t>
+          <t>A 11558-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7799,10 +7789,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45310</v>
+        <v>45727</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7815,7 +7805,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7858,7 +7848,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15039-2022</t>
+          <t>A 14143-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7872,10 +7862,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44657</v>
+        <v>45392</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7888,7 +7878,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7931,7 +7921,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1847-2025</t>
+          <t>A 17806-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7945,10 +7935,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45671</v>
+        <v>45037</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7961,7 +7951,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8004,7 +7994,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20259-2026</t>
+          <t>A 29615-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8018,10 +8008,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46139</v>
+        <v>44754</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8033,8 +8023,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8077,7 +8072,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58244-2025</t>
+          <t>A 59944-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8091,10 +8086,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45985</v>
+        <v>45642</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8107,7 +8102,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8150,7 +8145,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24247-2025</t>
+          <t>A 59503-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8164,10 +8159,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45797</v>
+        <v>44907</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8180,7 +8175,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8223,7 +8218,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 65007-2023</t>
+          <t>A 30599-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8237,10 +8232,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45287</v>
+        <v>45112</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8253,7 +8248,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>14.2</v>
+        <v>10.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8296,7 +8291,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18049-2024</t>
+          <t>A 64518-2021</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8310,10 +8305,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45420</v>
+        <v>44511</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8326,7 +8321,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8369,7 +8364,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 41074-2022</t>
+          <t>A 62667-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8383,10 +8378,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44825</v>
+        <v>45271</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8399,7 +8394,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8442,7 +8437,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20184-2026</t>
+          <t>A 64193-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8456,10 +8451,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46139</v>
+        <v>44510</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8472,7 +8467,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8515,7 +8510,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 15472-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8529,10 +8524,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44489</v>
+        <v>45747</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8545,7 +8540,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8588,7 +8583,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30951-2022</t>
+          <t>A 242-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8602,10 +8597,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44768</v>
+        <v>45294</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8617,8 +8612,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8661,7 +8661,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 15472-2025</t>
+          <t>A 38760-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8675,10 +8675,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45747</v>
+        <v>45163</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8734,7 +8734,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 26438-2025</t>
+          <t>A 25409-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45807</v>
+        <v>45463</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8763,8 +8763,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8807,7 +8812,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 45672-2024</t>
+          <t>A 14651-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8821,10 +8826,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45579</v>
+        <v>45397</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8837,7 +8842,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8880,7 +8885,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 2077-2024</t>
+          <t>A 35611-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8894,10 +8899,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45309</v>
+        <v>45531</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8910,7 +8915,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8953,7 +8958,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 26910-2025</t>
+          <t>A 36971-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8967,10 +8972,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45811</v>
+        <v>45538</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8983,7 +8988,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>17.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9026,7 +9031,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 62807-2023</t>
+          <t>A 20745-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9040,10 +9045,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45271</v>
+        <v>45436</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9056,7 +9061,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9099,7 +9104,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 47786-2025</t>
+          <t>A 10910-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9113,10 +9118,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45931</v>
+        <v>44991</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9129,7 +9134,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9172,7 +9177,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 47801-2025</t>
+          <t>A 57967-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9186,10 +9191,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45931</v>
+        <v>44487</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9202,7 +9207,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9245,7 +9250,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47704-2025</t>
+          <t>A 56765-2021</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9259,10 +9264,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45931</v>
+        <v>44481</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9275,7 +9280,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9318,7 +9323,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 47722-2025</t>
+          <t>A 35084-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9332,10 +9337,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45931</v>
+        <v>45527</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9348,7 +9353,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9391,7 +9396,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 30599-2023</t>
+          <t>A 22798-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9405,10 +9410,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45112</v>
+        <v>45448</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9420,8 +9425,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>10.1</v>
+        <v>5.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9464,7 +9474,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 47798-2025</t>
+          <t>A 44660-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9478,10 +9488,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45931</v>
+        <v>45574</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9494,7 +9504,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9537,7 +9547,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 47804-2025</t>
+          <t>A 44666-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9551,10 +9561,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45931</v>
+        <v>45574</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,7 +9577,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9610,7 +9620,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 47784-2025</t>
+          <t>A 22566-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9624,10 +9634,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45931</v>
+        <v>45789</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,7 +9650,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9683,7 +9693,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 33475-2024</t>
+          <t>A 666-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9697,10 +9707,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45519</v>
+        <v>44930</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9723,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9756,7 +9766,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 57151-2023</t>
+          <t>A 45591-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9770,10 +9780,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45245</v>
+        <v>45194</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,7 +9796,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>11</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9829,7 +9839,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 48427-2025</t>
+          <t>A 47798-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9843,10 +9853,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45934</v>
+        <v>45931</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9859,7 +9869,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9902,7 +9912,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 43194-2025</t>
+          <t>A 47804-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9916,10 +9926,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45910</v>
+        <v>45931</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,7 +9942,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9975,7 +9985,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 22226-2026</t>
+          <t>A 3996-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9989,10 +9999,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46150</v>
+        <v>44587</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10005,7 +10015,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10048,7 +10058,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 2708-2023</t>
+          <t>A 47801-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10062,10 +10072,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44942</v>
+        <v>45931</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10078,7 +10088,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10121,7 +10131,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 52621-2025</t>
+          <t>A 47784-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10135,10 +10145,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45953</v>
+        <v>45931</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10151,7 +10161,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10194,7 +10204,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 52622-2025</t>
+          <t>A 36795-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10208,10 +10218,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45953</v>
+        <v>45538</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10224,7 +10234,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10267,7 +10277,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8541-2025</t>
+          <t>A 47722-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10281,10 +10291,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45709</v>
+        <v>45931</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10297,7 +10307,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10340,7 +10350,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 2990-2022</t>
+          <t>A 47704-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10354,10 +10364,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44581</v>
+        <v>45931</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10370,7 +10380,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10413,7 +10423,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 2994-2022</t>
+          <t>A 47786-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10427,10 +10437,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44581</v>
+        <v>45931</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10443,7 +10453,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10486,7 +10496,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 52697-2025</t>
+          <t>A 25435-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10500,10 +10510,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45956</v>
+        <v>45463</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10515,8 +10525,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10559,7 +10574,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 7822-2024</t>
+          <t>A 20476-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10573,10 +10588,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45349</v>
+        <v>45435</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10589,7 +10604,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10632,7 +10647,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 5753-2025</t>
+          <t>A 48427-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10646,10 +10661,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45694</v>
+        <v>45934</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10662,7 +10677,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10705,7 +10720,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 64374-2023</t>
+          <t>A 11929-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10719,10 +10734,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45280</v>
+        <v>44995</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10735,7 +10750,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10778,7 +10793,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24262-2025</t>
+          <t>A 14732-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10792,10 +10807,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45797</v>
+        <v>44655</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10808,7 +10823,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10851,7 +10866,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 53839-2025</t>
+          <t>A 57483-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10865,10 +10880,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45961</v>
+        <v>44896</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10880,8 +10895,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10924,7 +10944,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 53841-2025</t>
+          <t>A 8911-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10938,10 +10958,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45961</v>
+        <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10954,7 +10974,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10997,7 +11017,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 54593-2025</t>
+          <t>A 18049-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11011,10 +11031,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45965</v>
+        <v>45420</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11027,7 +11047,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11070,7 +11090,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 23327-2026</t>
+          <t>A 37620-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11084,10 +11104,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46162</v>
+        <v>45541</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11100,7 +11120,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.9</v>
+        <v>0.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11143,7 +11163,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 59944-2024</t>
+          <t>A 29698-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11153,14 +11173,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45642</v>
+        <v>45484</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11173,7 +11193,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11216,7 +11236,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 17635-2022</t>
+          <t>A 15721-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11230,10 +11250,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44680</v>
+        <v>45404</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11246,7 +11266,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11289,7 +11309,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 57011-2025</t>
+          <t>A 45672-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11303,10 +11323,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45978</v>
+        <v>45579</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11318,13 +11338,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11367,7 +11382,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 35084-2024</t>
+          <t>A 2708-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11381,10 +11396,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45527</v>
+        <v>44942</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11397,7 +11412,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11440,7 +11455,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 18948-2024</t>
+          <t>A 31032-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11454,10 +11469,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45427</v>
+        <v>45501</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11470,7 +11485,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11513,7 +11528,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 56957-2025</t>
+          <t>A 31033-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11523,14 +11538,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45978</v>
+        <v>45501</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11542,13 +11557,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11591,7 +11601,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 12252-2024</t>
+          <t>A 50461-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11605,10 +11615,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45378</v>
+        <v>45601</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11621,7 +11631,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11664,7 +11674,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24640-2026</t>
+          <t>A 10634-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11678,10 +11688,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46171</v>
+        <v>45367</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11694,7 +11704,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11737,7 +11747,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 41526-2023</t>
+          <t>A 39039-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11751,10 +11761,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45175</v>
+        <v>45548</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11772,7 +11782,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11815,7 +11825,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 46117-2022</t>
+          <t>A 52621-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11829,10 +11839,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44847</v>
+        <v>45953</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11845,7 +11855,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11888,7 +11898,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61436-2025</t>
+          <t>A 52622-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11902,10 +11912,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46001</v>
+        <v>45953</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11918,7 +11928,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11961,7 +11971,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 11929-2023</t>
+          <t>A 46445-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11975,10 +11985,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44995</v>
+        <v>45582</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11991,7 +12001,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12034,7 +12044,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 59871-2024</t>
+          <t>A 18948-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12048,10 +12058,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45640</v>
+        <v>45427</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12064,7 +12074,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12107,7 +12117,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 2314-2022</t>
+          <t>A 12272-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12121,10 +12131,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44578</v>
+        <v>45378</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12137,7 +12147,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12180,7 +12190,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 12281-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12194,10 +12204,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44489</v>
+        <v>45378</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12210,7 +12220,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12253,7 +12263,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 10910-2023</t>
+          <t>A 52697-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12267,10 +12277,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44991</v>
+        <v>45956</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12283,7 +12293,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12326,7 +12336,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 12652-2024</t>
+          <t>A 7586-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12340,10 +12350,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45384</v>
+        <v>45705</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12356,7 +12366,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12399,7 +12409,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 27792-2023</t>
+          <t>A 53841-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12413,10 +12423,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45098</v>
+        <v>45961</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12429,7 +12439,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12472,7 +12482,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 60201-2024</t>
+          <t>A 49604-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12486,10 +12496,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45642</v>
+        <v>45207</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12502,7 +12512,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12545,7 +12555,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 20476-2024</t>
+          <t>A 53839-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12559,10 +12569,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45435</v>
+        <v>45961</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12575,7 +12585,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12618,7 +12628,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 63811-2025</t>
+          <t>A 59938-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12632,10 +12642,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46020</v>
+        <v>45642</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12648,7 +12658,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12691,7 +12701,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 32839-2023</t>
+          <t>A 2688-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12705,10 +12715,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45109</v>
+        <v>44942</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12721,7 +12731,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12764,7 +12774,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 34408-2024</t>
+          <t>A 54593-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12774,14 +12784,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45525</v>
+        <v>45965</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12794,7 +12804,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12837,7 +12847,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 2688-2023</t>
+          <t>A 62669-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12851,10 +12861,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44942</v>
+        <v>45271</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12867,7 +12877,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12910,7 +12920,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 3174-2026</t>
+          <t>A 15039-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12924,10 +12934,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46041</v>
+        <v>44657</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12940,7 +12950,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12983,7 +12993,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 969-2022</t>
+          <t>A 5286-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12997,10 +13007,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44571</v>
+        <v>44959</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13013,7 +13023,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13056,7 +13066,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 15721-2024</t>
+          <t>A 7368-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13070,10 +13080,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45404</v>
+        <v>45704</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13086,7 +13096,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13129,7 +13139,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 27638-2026</t>
+          <t>A 23786-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13139,14 +13149,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46190</v>
+        <v>44722</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13158,13 +13168,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>2.7</v>
+        <v>7.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13207,7 +13212,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 73251-2021</t>
+          <t>A 21032-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13221,10 +13226,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44550</v>
+        <v>45061</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13237,7 +13242,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13280,7 +13285,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 14984-2024</t>
+          <t>A 55306-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13294,10 +13299,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45399</v>
+        <v>45621</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13310,7 +13315,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13353,7 +13358,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 14987-2024</t>
+          <t>A 26270-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13367,10 +13372,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45399</v>
+        <v>44735</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13383,7 +13388,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13426,7 +13431,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 10374-2022</t>
+          <t>A 57386-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13440,10 +13445,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44623</v>
+        <v>45629</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13456,7 +13461,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13499,7 +13504,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 12281-2024</t>
+          <t>A 57011-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13513,10 +13518,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45378</v>
+        <v>45978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13528,8 +13533,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13572,7 +13582,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 5286-2023</t>
+          <t>A 6015-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13586,10 +13596,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44959</v>
+        <v>44964</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13602,7 +13612,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13645,7 +13655,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 5754-2025</t>
+          <t>A 20743-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13659,10 +13669,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45694</v>
+        <v>45436</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13675,7 +13685,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13718,7 +13728,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 57386-2024</t>
+          <t>A 60201-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13732,10 +13742,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45629</v>
+        <v>45642</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13748,7 +13758,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>7.4</v>
+        <v>1.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13791,7 +13801,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 12272-2024</t>
+          <t>A 56957-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13801,14 +13811,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45378</v>
+        <v>45978</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13820,8 +13830,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13864,7 +13879,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 39055-2024</t>
+          <t>A 65007-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13878,10 +13893,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45548</v>
+        <v>45287</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13893,13 +13908,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.1</v>
+        <v>14.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13942,7 +13952,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 21032-2023</t>
+          <t>A 39492-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13956,10 +13966,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45061</v>
+        <v>45166</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13971,8 +13981,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>24.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14015,7 +14030,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 57483-2022</t>
+          <t>A 30260-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14029,10 +14044,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44896</v>
+        <v>45827</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14044,13 +14059,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14093,7 +14103,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 56765-2021</t>
+          <t>A 64140-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14107,10 +14117,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44481</v>
+        <v>45279</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14123,7 +14133,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14166,7 +14176,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 46998-2024</t>
+          <t>A 61436-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14180,10 +14190,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45586</v>
+        <v>46001</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14196,7 +14206,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14239,7 +14249,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 65008-2023</t>
+          <t>A 28195-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14253,10 +14263,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45287</v>
+        <v>44746</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14266,6 +14276,11 @@
       <c r="G179" t="inlineStr">
         <is>
           <t>KIL</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I179" t="n">
@@ -14312,7 +14327,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 2-2023</t>
+          <t>A 34408-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14322,14 +14337,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44927</v>
+        <v>45525</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14342,7 +14357,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14385,7 +14400,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 71728-2021</t>
+          <t>A 12280-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14399,10 +14414,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44543</v>
+        <v>45378</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14415,7 +14430,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14458,7 +14473,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 4832-2022</t>
+          <t>A 18117-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14472,10 +14487,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44592</v>
+        <v>45761</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14488,7 +14503,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14531,7 +14546,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 62667-2023</t>
+          <t>A 6687-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14545,10 +14560,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45271</v>
+        <v>44966</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14561,7 +14576,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14604,7 +14619,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 39492-2023</t>
+          <t>A 73251-2021</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14618,10 +14633,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45166</v>
+        <v>44550</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14633,13 +14648,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>24.9</v>
+        <v>1.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14682,7 +14692,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 13504-2026</t>
+          <t>A 969-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14696,10 +14706,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46094</v>
+        <v>44571</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14712,7 +14722,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14755,7 +14765,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 33266-2026</t>
+          <t>A 3174-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14769,10 +14779,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46246</v>
+        <v>46041</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14785,7 +14795,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14828,7 +14838,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 64518-2021</t>
+          <t>A 32982-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14842,10 +14852,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44511</v>
+        <v>45839</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14857,8 +14867,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14901,7 +14916,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 25409-2024</t>
+          <t>A 32410-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14915,10 +14930,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45463</v>
+        <v>45838</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14930,13 +14945,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14979,7 +14989,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 14036-2026</t>
+          <t>A 56641-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14993,10 +15003,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46098</v>
+        <v>45243</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15009,7 +15019,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15052,7 +15062,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 2263-2023</t>
+          <t>A 61229-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15066,10 +15076,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44941</v>
+        <v>44915</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15082,7 +15092,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15125,7 +15135,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 50461-2024</t>
+          <t>A 17635-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15139,10 +15149,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45601</v>
+        <v>44680</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15155,7 +15165,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15198,7 +15208,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 61229-2022</t>
+          <t>A 36296-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15212,10 +15222,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44915</v>
+        <v>44803</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15228,7 +15238,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15271,7 +15281,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 46445-2024</t>
+          <t>A 2077-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15285,10 +15295,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45582</v>
+        <v>45309</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15301,7 +15311,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15344,7 +15354,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 4069-2025</t>
+          <t>A 61210-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15358,10 +15368,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45684</v>
+        <v>45264</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15373,13 +15383,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>0.4</v>
+        <v>7.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15422,7 +15427,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 44660-2024</t>
+          <t>A 57151-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15436,10 +15441,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45574</v>
+        <v>45245</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15452,7 +15457,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15495,7 +15500,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 44666-2024</t>
+          <t>A 63811-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15509,10 +15514,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45574</v>
+        <v>46020</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15525,7 +15530,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15568,7 +15573,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 16585-2026</t>
+          <t>A 38489-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15582,10 +15587,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46112</v>
+        <v>46282</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15598,7 +15603,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15641,7 +15646,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 20745-2024</t>
+          <t>A 34846-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15655,10 +15660,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45436</v>
+        <v>46258</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15671,7 +15676,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15714,7 +15719,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 52438-2022</t>
+          <t>A 38517-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15728,10 +15733,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44874</v>
+        <v>46283</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15743,8 +15748,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15787,7 +15797,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 50252-2024</t>
+          <t>A 10476-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15801,10 +15811,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45600</v>
+        <v>45720</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15816,8 +15826,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15860,7 +15875,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 18101-2026</t>
+          <t>A 41526-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15874,10 +15889,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46125</v>
+        <v>45175</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15889,8 +15904,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15933,7 +15953,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 18096-2026</t>
+          <t>A 33037-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15947,10 +15967,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46125</v>
+        <v>46245</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15963,7 +15983,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16006,7 +16026,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 18117-2025</t>
+          <t>A 33233-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16020,10 +16040,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45761</v>
+        <v>46246</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16036,7 +16056,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16079,7 +16099,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 3996-2022</t>
+          <t>A 33266-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16093,10 +16113,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44587</v>
+        <v>46246</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16109,7 +16129,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16152,7 +16172,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 55306-2024</t>
+          <t>A 31621-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16166,10 +16186,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45621</v>
+        <v>44775</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16182,7 +16202,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16225,7 +16245,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 37620-2024</t>
+          <t>A 2314-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16239,10 +16259,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45541</v>
+        <v>44578</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16255,7 +16275,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16298,7 +16318,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37622-2024</t>
+          <t>A 46998-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16312,10 +16332,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45541</v>
+        <v>45586</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16328,7 +16348,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16371,7 +16391,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 53416-2023</t>
+          <t>A 2263-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16385,10 +16405,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45229</v>
+        <v>44941</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16401,7 +16421,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16444,7 +16464,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 29698-2024</t>
+          <t>A 17473-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16454,14 +16474,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45484</v>
+        <v>45757</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16474,7 +16494,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16517,7 +16537,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 23786-2022</t>
+          <t>A 13504-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16531,10 +16551,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44722</v>
+        <v>46094</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16547,7 +16567,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16590,7 +16610,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 33233-2026</t>
+          <t>A 35449-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16604,10 +16624,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46246</v>
+        <v>45531</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16620,7 +16640,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16663,7 +16683,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 666-2023</t>
+          <t>A 14036-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16677,10 +16697,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44930</v>
+        <v>46098</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16693,7 +16713,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16736,7 +16756,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 59012-2024</t>
+          <t>A 50252-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16750,10 +16770,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45636</v>
+        <v>45600</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16766,7 +16786,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16809,7 +16829,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 26263-2023</t>
+          <t>A 4832-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16823,10 +16843,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45091</v>
+        <v>44592</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16839,7 +16859,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16882,7 +16902,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 8910-2025</t>
+          <t>A 16585-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16896,10 +16916,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45713</v>
+        <v>46112</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16912,7 +16932,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16955,7 +16975,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 8916-2025</t>
+          <t>A 38835-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16969,10 +16989,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45713</v>
+        <v>45547</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16985,7 +17005,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17028,7 +17048,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 33566-2024</t>
+          <t>A 59871-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17042,10 +17062,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45520</v>
+        <v>45640</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17058,7 +17078,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17101,7 +17121,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 59503-2022</t>
+          <t>A 18096-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17115,10 +17135,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44907</v>
+        <v>46125</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17131,7 +17151,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17174,7 +17194,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 59200-2023</t>
+          <t>A 2309-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17188,10 +17208,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45253</v>
+        <v>45310</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17204,7 +17224,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17247,7 +17267,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 10634-2024</t>
+          <t>A 18101-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17261,10 +17281,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45367</v>
+        <v>46125</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17277,7 +17297,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17320,7 +17340,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 34402-2022</t>
+          <t>A 2306-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17334,10 +17354,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44792</v>
+        <v>45310</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17350,7 +17370,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17393,7 +17413,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 18336-2023</t>
+          <t>A 59200-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17407,10 +17427,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45041</v>
+        <v>45253</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17422,13 +17442,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17471,7 +17486,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 72073-2021</t>
+          <t>A 3851-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17485,10 +17500,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44544</v>
+        <v>45683</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17501,7 +17516,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>9.6</v>
+        <v>2.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17544,7 +17559,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 16596-2023</t>
+          <t>A 26263-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17558,10 +17573,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45030</v>
+        <v>45091</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17574,7 +17589,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17617,7 +17632,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 5758-2025</t>
+          <t>A 44646-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17631,10 +17646,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45694</v>
+        <v>45574</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17647,7 +17662,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17690,7 +17705,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 25435-2024</t>
+          <t>A 36305-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17704,10 +17719,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45463</v>
+        <v>44803</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17717,11 +17732,6 @@
       <c r="G226" t="inlineStr">
         <is>
           <t>KIL</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I226" t="n">
@@ -17768,7 +17778,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 22798-2024</t>
+          <t>A 58244-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17782,10 +17792,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45448</v>
+        <v>45985</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17797,13 +17807,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>5.9</v>
+        <v>2.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17846,7 +17851,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 7368-2025</t>
+          <t>A 10374-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17860,10 +17865,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45704</v>
+        <v>44623</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17919,7 +17924,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 14143-2024</t>
+          <t>A 4069-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17933,10 +17938,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45392</v>
+        <v>45684</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17948,8 +17953,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17992,7 +18002,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 14732-2022</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18006,10 +18016,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44655</v>
+        <v>44489</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18022,7 +18032,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18065,7 +18075,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 10635-2024</t>
+          <t>A 20184-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18079,10 +18089,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45367</v>
+        <v>46139</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18095,7 +18105,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18138,7 +18148,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 57967-2021</t>
+          <t>A 27792-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18152,10 +18162,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44487</v>
+        <v>45098</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18168,7 +18178,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18211,7 +18221,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 34846-2026</t>
+          <t>A 32839-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18225,10 +18235,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46258</v>
+        <v>45109</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18241,7 +18251,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18284,7 +18294,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 38499-2026</t>
+          <t>A 53956-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18298,10 +18308,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46282</v>
+        <v>45616</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18314,7 +18324,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18357,7 +18367,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 2306-2024</t>
+          <t>A 17816-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18371,10 +18381,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45310</v>
+        <v>45037</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18387,7 +18397,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18430,7 +18440,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 38494-2026</t>
+          <t>A 33566-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18444,10 +18454,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46282</v>
+        <v>45520</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18460,7 +18470,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18503,7 +18513,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 38489-2026</t>
+          <t>A 16596-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18517,10 +18527,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46282</v>
+        <v>45030</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18533,7 +18543,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18576,7 +18586,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 38517-2026</t>
+          <t>A 26438-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18590,10 +18600,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46283</v>
+        <v>45807</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18605,13 +18615,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18654,7 +18659,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 14675-2024</t>
+          <t>A 1847-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18668,10 +18673,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45397</v>
+        <v>45671</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18684,7 +18689,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18727,7 +18732,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 36296-2022</t>
+          <t>A 20259-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18741,10 +18746,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44803</v>
+        <v>46139</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18757,7 +18762,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18800,7 +18805,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 6015-2023</t>
+          <t>A 43285-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18814,10 +18819,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44964</v>
+        <v>45568</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18830,7 +18835,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18873,7 +18878,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 33037-2026</t>
+          <t>A 64374-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18887,10 +18892,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46245</v>
+        <v>45280</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18903,7 +18908,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18946,7 +18951,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 8911-2025</t>
+          <t>A 59061-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18960,10 +18965,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45713</v>
+        <v>45252</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18976,7 +18981,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19019,7 +19024,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 20743-2024</t>
+          <t>A 24247-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19033,10 +19038,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45436</v>
+        <v>45797</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19049,7 +19054,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19092,7 +19097,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 44646-2024</t>
+          <t>A 30951-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19106,10 +19111,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45574</v>
+        <v>44768</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19122,7 +19127,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19165,7 +19170,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 59938-2024</t>
+          <t>A 43194-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19179,10 +19184,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45642</v>
+        <v>45910</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19195,7 +19200,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19238,7 +19243,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 53956-2024</t>
+          <t>A 33475-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19252,10 +19257,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45616</v>
+        <v>45519</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19268,7 +19273,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19311,7 +19316,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 31621-2022</t>
+          <t>A 5758-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19325,10 +19330,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44775</v>
+        <v>45694</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19341,7 +19346,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19384,7 +19389,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 49604-2023</t>
+          <t>A 26910-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19398,10 +19403,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45207</v>
+        <v>45811</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19414,7 +19419,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19457,7 +19462,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 249-2022</t>
+          <t>A 5753-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19471,10 +19476,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44565</v>
+        <v>45694</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19487,7 +19492,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19530,7 +19535,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 28195-2022</t>
+          <t>A 15962-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19544,10 +19549,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44746</v>
+        <v>45749</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19557,11 +19562,6 @@
       <c r="G251" t="inlineStr">
         <is>
           <t>KIL</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I251" t="n">
@@ -19608,7 +19608,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 14954-2024</t>
+          <t>A 37622-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19622,10 +19622,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45398</v>
+        <v>45541</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19681,7 +19681,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 65002-2023</t>
+          <t>A 22226-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19695,10 +19695,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45287</v>
+        <v>46150</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>6.9</v>
+        <v>2.1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19771,7 +19771,7 @@
         <v>45784</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 57220-2024</t>
+          <t>A 14954-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19841,10 +19841,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45629</v>
+        <v>45398</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19900,7 +19900,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 45599-2023</t>
+          <t>A 65002-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19914,10 +19914,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45194</v>
+        <v>45287</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 11558-2025</t>
+          <t>A 7822-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19987,10 +19987,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45727</v>
+        <v>45349</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20046,7 +20046,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 36795-2024</t>
+          <t>A 8541-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20060,10 +20060,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45538</v>
+        <v>45709</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>9.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20119,7 +20119,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 45591-2023</t>
+          <t>A 24262-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20133,10 +20133,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45194</v>
+        <v>45797</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>11</v>
+        <v>1.2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20192,7 +20192,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 22566-2025</t>
+          <t>A 23327-2026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20206,10 +20206,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45789</v>
+        <v>46162</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20265,7 +20265,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 30260-2025</t>
+          <t>A 24640-2026</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20279,10 +20279,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45827</v>
+        <v>46171</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20338,7 +20338,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 32982-2025</t>
+          <t>A 27638-2026</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20348,14 +20348,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45839</v>
+        <v>46190</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20416,7 +20416,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 32410-2025</t>
+          <t>A 71728-2021</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20430,10 +20430,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45838</v>
+        <v>44543</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20489,7 +20489,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 17473-2025</t>
+          <t>A 38499-2026</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20503,10 +20503,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45757</v>
+        <v>46282</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20562,7 +20562,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 35449-2024</t>
+          <t>A 38494-2026</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20576,10 +20576,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45531</v>
+        <v>46282</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20652,7 +20652,7 @@
         <v>44755</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45569</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44901</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45266</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45476</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45476</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45499</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46037</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45093</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44809</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23794-2023</t>
+          <t>A 38039-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45078</v>
+        <v>45544</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1412,46 +1412,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 54177-2023</t>
+          <t>A 8909-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45232</v>
+        <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1481,17 +1481,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>22.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1514,154 +1514,154 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 54177-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45232</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Strutbräken</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 54177-2023 artfynd.xlsx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 54177-2023 karta.png", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 54177-2023 georefererad karta.tif", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 54177-2023 FSC-klagomål.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 54177-2023 FSC-klagomål mail.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 54177-2023 tillsynsbegäran.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 54177-2023 tillsynsbegäran mail.docx", "A 54177-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 53498-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45230</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1320-2023</t>
+          <t>A 56642-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44936</v>
+        <v>44893</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1690,14 +1690,19 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1731,35 +1736,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
     </row>
@@ -1783,7 +1788,7 @@
         <v>45907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 40853-2024</t>
+          <t>A 53498-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1890,10 +1895,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45558</v>
+        <v>45230</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1906,20 +1911,20 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -1930,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1942,46 +1947,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 62010-2022</t>
+          <t>A 1320-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1995,10 +2000,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44914</v>
+        <v>44936</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2011,13 +2016,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.8</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2051,42 +2056,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35453-2024</t>
+          <t>A 23794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2100,10 +2105,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45531</v>
+        <v>45078</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2116,7 +2121,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2152,43 +2157,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2212,7 +2213,7 @@
         <v>45371</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2305,7 +2306,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8909-2025</t>
+          <t>A 62010-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2319,10 +2320,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45713</v>
+        <v>44914</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2335,16 +2336,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>22.6</v>
+        <v>7.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2359,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2368,49 +2369,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 56642-2022</t>
+          <t>A 40853-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2424,10 +2425,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44893</v>
+        <v>45558</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2439,19 +2440,14 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2481,46 +2477,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38039-2024</t>
+          <t>A 35453-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2534,10 +2530,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45544</v>
+        <v>45531</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2553,10 +2549,10 @@
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2590,35 +2586,39 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
         <v/>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 46295-2022</t>
+          <t>A 57069-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44847</v>
+        <v>44482</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36302-2022</t>
+          <t>A 46295-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44803</v>
+        <v>44847</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 57069-2021</t>
+          <t>A 36302-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44482</v>
+        <v>44803</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         <v>44846</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44511</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1330-2022</t>
+          <t>A 2993-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44572</v>
+        <v>44581</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3647,7 +3647,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2993-2022</t>
+          <t>A 1330-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3657,14 +3657,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44581</v>
+        <v>44572</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44483</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44511</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44820</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44474</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56762-2021</t>
+          <t>A 73022-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44481</v>
+        <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18336-2023</t>
+          <t>A 33907-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45041</v>
+        <v>44790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4924,11 +4924,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 73022-2021</t>
+          <t>A 4445-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44550</v>
+        <v>44589</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33907-2022</t>
+          <t>A 57065-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44790</v>
+        <v>44482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5073,13 +5073,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5122,7 +5117,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57220-2024</t>
+          <t>A 52526-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5136,10 +5131,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45629</v>
+        <v>44466</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5152,7 +5147,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5195,7 +5190,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8910-2025</t>
+          <t>A 37962-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5205,14 +5200,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45713</v>
+        <v>44811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5225,7 +5220,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5268,7 +5263,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8916-2025</t>
+          <t>A 56762-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5282,10 +5277,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45713</v>
+        <v>44481</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5298,7 +5293,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5358,7 +5353,7 @@
         <v>44517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5414,7 +5409,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 72073-2021</t>
+          <t>A 12280-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5428,10 +5423,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44544</v>
+        <v>45378</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5444,7 +5439,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>9.6</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5487,7 +5482,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4445-2022</t>
+          <t>A 59061-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5501,10 +5496,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44589</v>
+        <v>45252</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5517,7 +5512,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5560,7 +5555,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57065-2021</t>
+          <t>A 3-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5574,10 +5569,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44482</v>
+        <v>44927</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5590,7 +5585,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5633,7 +5628,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52526-2021</t>
+          <t>A 14651-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5647,10 +5642,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44466</v>
+        <v>45397</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5663,7 +5658,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5706,7 +5701,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 5754-2025</t>
+          <t>A 46288-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5720,10 +5715,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45694</v>
+        <v>44847</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5736,7 +5731,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5779,7 +5774,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59012-2024</t>
+          <t>A 46290-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5793,10 +5788,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45636</v>
+        <v>44847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5809,7 +5804,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5852,7 +5847,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2-2023</t>
+          <t>A 26270-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5866,10 +5861,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44927</v>
+        <v>44735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5882,7 +5877,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5925,7 +5920,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53416-2023</t>
+          <t>A 31032-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5939,10 +5934,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45229</v>
+        <v>45501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5955,7 +5950,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5998,7 +5993,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37962-2022</t>
+          <t>A 31033-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6008,14 +6003,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44811</v>
+        <v>45501</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6028,7 +6023,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6071,7 +6066,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 56641-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6085,10 +6080,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44489</v>
+        <v>45243</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6101,7 +6096,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6144,7 +6139,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 62807-2023</t>
+          <t>A 36971-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6158,10 +6153,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45271</v>
+        <v>45538</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6174,7 +6169,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>17.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6217,7 +6212,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 34402-2022</t>
+          <t>A 36305-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6231,10 +6226,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44792</v>
+        <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6247,7 +6242,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6290,7 +6285,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14675-2024</t>
+          <t>A 17816-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6304,10 +6299,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45397</v>
+        <v>45037</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6320,7 +6315,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6363,7 +6358,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12252-2024</t>
+          <t>A 15962-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6377,10 +6372,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45378</v>
+        <v>45749</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6393,7 +6388,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6436,7 +6431,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 41074-2022</t>
+          <t>A 7586-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6450,10 +6445,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44825</v>
+        <v>45705</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6466,7 +6461,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6509,7 +6504,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17946-2024</t>
+          <t>A 242-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6523,10 +6518,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45419</v>
+        <v>45294</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6538,8 +6533,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2990-2022</t>
+          <t>A 29615-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44581</v>
+        <v>44754</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6611,8 +6611,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6655,7 +6660,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 2994-2022</t>
+          <t>A 61210-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6669,10 +6674,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44581</v>
+        <v>45264</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6685,7 +6690,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6728,616 +6733,611 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
+          <t>A 17946-2024</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>45419</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A 35611-2024</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>45531</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A 38760-2023</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A 17806-2023</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>45037</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>A 43285-2024</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>A 64193-2021</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>44510</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>A 38835-2024</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>45547</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>A 59064-2023</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="n">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="n">
         <v>45252</v>
       </c>
-      <c r="E77" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
+      <c r="E84" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
         <v>1.1</v>
       </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" s="2" t="inlineStr"/>
-      <c r="Z77">
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="Z84">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AA77">
+      <c r="AA84">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AB77">
+      <c r="AB84">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AC77">
+      <c r="AC84">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AD77">
+      <c r="AD84">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>A 46117-2022</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="n">
-        <v>44847</v>
-      </c>
-      <c r="E78" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>A 12652-2024</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="n">
-        <v>45384</v>
-      </c>
-      <c r="E79" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>A 14984-2024</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="n">
-        <v>45399</v>
-      </c>
-      <c r="E80" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>A 14987-2024</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="n">
-        <v>45399</v>
-      </c>
-      <c r="E81" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>A 249-2022</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="n">
-        <v>44565</v>
-      </c>
-      <c r="E82" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>A 39055-2024</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="n">
-        <v>45548</v>
-      </c>
-      <c r="E83" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>A 46288-2022</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="n">
-        <v>44847</v>
-      </c>
-      <c r="E84" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="2" t="inlineStr"/>
-    </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46290-2022</t>
+          <t>A 3851-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44847</v>
+        <v>45683</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.300000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7410,7 +7410,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52438-2022</t>
+          <t>A 6687-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44874</v>
+        <v>44966</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3-2023</t>
+          <t>A 2309-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44927</v>
+        <v>45310</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 65008-2023</t>
+          <t>A 39039-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45287</v>
+        <v>45548</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7585,8 +7585,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7629,7 +7634,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 45599-2023</t>
+          <t>A 62669-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7643,10 +7648,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45194</v>
+        <v>45271</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7659,7 +7664,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7702,7 +7707,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10635-2024</t>
+          <t>A 10476-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7716,10 +7721,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45367</v>
+        <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7731,8 +7736,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7775,7 +7785,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11558-2025</t>
+          <t>A 64140-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7789,10 +7799,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45727</v>
+        <v>45279</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7805,7 +7815,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7848,7 +7858,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14143-2024</t>
+          <t>A 15039-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7862,10 +7872,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45392</v>
+        <v>44657</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7878,7 +7888,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7921,7 +7931,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17806-2023</t>
+          <t>A 1847-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7935,10 +7945,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45037</v>
+        <v>45671</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7951,7 +7961,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7994,7 +8004,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 29615-2022</t>
+          <t>A 20259-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8008,10 +8018,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44754</v>
+        <v>46139</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8023,13 +8033,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8072,7 +8077,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59944-2024</t>
+          <t>A 58244-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8086,10 +8091,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45642</v>
+        <v>45985</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8102,7 +8107,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8145,7 +8150,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 59503-2022</t>
+          <t>A 24247-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8159,10 +8164,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44907</v>
+        <v>45797</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8175,7 +8180,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8218,7 +8223,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30599-2023</t>
+          <t>A 65007-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8232,10 +8237,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45112</v>
+        <v>45287</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8248,7 +8253,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>10.1</v>
+        <v>14.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8291,7 +8296,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 64518-2021</t>
+          <t>A 18049-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8305,10 +8310,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44511</v>
+        <v>45420</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8321,7 +8326,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8364,7 +8369,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62667-2023</t>
+          <t>A 41074-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8378,10 +8383,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45271</v>
+        <v>44825</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8394,7 +8399,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8437,7 +8442,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 64193-2021</t>
+          <t>A 30951-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8451,10 +8456,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44510</v>
+        <v>44768</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8467,7 +8472,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8527,7 +8532,7 @@
         <v>45747</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8583,7 +8588,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 242-2024</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8597,10 +8602,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45294</v>
+        <v>44489</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8612,13 +8617,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8661,7 +8661,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 38760-2023</t>
+          <t>A 45672-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8675,10 +8675,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45163</v>
+        <v>45579</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8734,7 +8734,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 25409-2024</t>
+          <t>A 2077-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45463</v>
+        <v>45309</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8763,13 +8763,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8812,7 +8807,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 14651-2024</t>
+          <t>A 62807-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8826,10 +8821,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45397</v>
+        <v>45271</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8842,7 +8837,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8885,7 +8880,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35611-2024</t>
+          <t>A 30599-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8899,10 +8894,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45531</v>
+        <v>45112</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8915,7 +8910,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8958,7 +8953,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 36971-2024</t>
+          <t>A 47786-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8972,10 +8967,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45538</v>
+        <v>45931</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8988,7 +8983,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>17.9</v>
+        <v>0.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9031,7 +9026,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20745-2024</t>
+          <t>A 47801-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9045,10 +9040,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45436</v>
+        <v>45931</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9061,7 +9056,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9104,7 +9099,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 10910-2023</t>
+          <t>A 20184-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9118,10 +9113,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44991</v>
+        <v>46139</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9134,7 +9129,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9177,7 +9172,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57967-2021</t>
+          <t>A 57151-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9191,10 +9186,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44487</v>
+        <v>45245</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9207,7 +9202,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9250,7 +9245,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 56765-2021</t>
+          <t>A 47704-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9264,10 +9259,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44481</v>
+        <v>45931</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9280,7 +9275,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9323,7 +9318,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 35084-2024</t>
+          <t>A 47722-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9337,10 +9332,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45527</v>
+        <v>45931</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9353,7 +9348,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9396,7 +9391,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 22798-2024</t>
+          <t>A 47798-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9410,10 +9405,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45448</v>
+        <v>45931</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9425,13 +9420,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>5.9</v>
+        <v>0.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9474,7 +9464,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 44660-2024</t>
+          <t>A 47804-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9488,10 +9478,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45574</v>
+        <v>45931</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9504,7 +9494,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9547,7 +9537,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 44666-2024</t>
+          <t>A 47784-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9561,10 +9551,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45574</v>
+        <v>45931</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9577,7 +9567,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9620,7 +9610,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 22566-2025</t>
+          <t>A 48427-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9634,10 +9624,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45789</v>
+        <v>45934</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9650,7 +9640,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9693,7 +9683,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 666-2023</t>
+          <t>A 2708-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9707,10 +9697,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44930</v>
+        <v>44942</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9723,7 +9713,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>8.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9766,7 +9756,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 45591-2023</t>
+          <t>A 26438-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9780,10 +9770,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45194</v>
+        <v>45807</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9796,7 +9786,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>11</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9839,7 +9829,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 47798-2025</t>
+          <t>A 2990-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9853,10 +9843,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45931</v>
+        <v>44581</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9869,7 +9859,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9912,7 +9902,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 47804-2025</t>
+          <t>A 2994-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9926,10 +9916,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45931</v>
+        <v>44581</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9942,7 +9932,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9985,7 +9975,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 3996-2022</t>
+          <t>A 52621-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9999,10 +9989,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44587</v>
+        <v>45953</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10015,7 +10005,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10058,7 +10048,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 47801-2025</t>
+          <t>A 52622-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10072,10 +10062,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45931</v>
+        <v>45953</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10088,7 +10078,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10131,7 +10121,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 47784-2025</t>
+          <t>A 5753-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10145,10 +10135,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45931</v>
+        <v>45694</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10161,7 +10151,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10204,7 +10194,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 36795-2024</t>
+          <t>A 64374-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10218,10 +10208,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45538</v>
+        <v>45280</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10234,7 +10224,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>9.300000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10277,7 +10267,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 47722-2025</t>
+          <t>A 52697-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10291,10 +10281,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45931</v>
+        <v>45956</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10307,7 +10297,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10350,7 +10340,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 47704-2025</t>
+          <t>A 26910-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10364,10 +10354,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45931</v>
+        <v>45811</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10380,7 +10370,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10423,7 +10413,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 47786-2025</t>
+          <t>A 59944-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10437,10 +10427,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45931</v>
+        <v>45642</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10453,7 +10443,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10496,7 +10486,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25435-2024</t>
+          <t>A 17635-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10510,10 +10500,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45463</v>
+        <v>44680</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10525,13 +10515,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10574,7 +10559,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 20476-2024</t>
+          <t>A 53839-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10588,10 +10573,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45435</v>
+        <v>45961</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10604,7 +10589,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10647,7 +10632,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 48427-2025</t>
+          <t>A 53841-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10661,10 +10646,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45934</v>
+        <v>45961</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10677,7 +10662,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10720,7 +10705,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 11929-2023</t>
+          <t>A 54593-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10734,10 +10719,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44995</v>
+        <v>45965</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10793,7 +10778,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 14732-2022</t>
+          <t>A 33475-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10807,10 +10792,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44655</v>
+        <v>45519</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10823,7 +10808,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10866,7 +10851,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 57483-2022</t>
+          <t>A 43194-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10880,10 +10865,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44896</v>
+        <v>45910</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10895,13 +10880,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10944,7 +10924,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 8911-2025</t>
+          <t>A 35084-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10958,10 +10938,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45713</v>
+        <v>45527</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10974,7 +10954,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11017,7 +10997,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 18049-2024</t>
+          <t>A 18948-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11031,10 +11011,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45420</v>
+        <v>45427</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11047,7 +11027,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11090,7 +11070,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 37620-2024</t>
+          <t>A 57011-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11104,10 +11084,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45541</v>
+        <v>45978</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11119,8 +11099,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11163,7 +11148,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 29698-2024</t>
+          <t>A 12252-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11173,14 +11158,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45484</v>
+        <v>45378</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11236,7 +11221,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 15721-2024</t>
+          <t>A 41526-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11250,10 +11235,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45404</v>
+        <v>45175</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11265,8 +11250,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11309,7 +11299,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 45672-2024</t>
+          <t>A 56957-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11319,14 +11309,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45579</v>
+        <v>45978</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11338,8 +11328,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11382,7 +11377,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 2708-2023</t>
+          <t>A 46117-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11396,10 +11391,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44942</v>
+        <v>44847</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11412,7 +11407,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11455,7 +11450,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 31032-2024</t>
+          <t>A 22226-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11469,10 +11464,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45501</v>
+        <v>46150</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11485,7 +11480,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11528,7 +11523,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31033-2024</t>
+          <t>A 11929-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11542,10 +11537,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45501</v>
+        <v>44995</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11558,7 +11553,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11601,7 +11596,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 50461-2024</t>
+          <t>A 59871-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11615,10 +11610,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45601</v>
+        <v>45640</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11631,7 +11626,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11674,7 +11669,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 10634-2024</t>
+          <t>A 2314-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11688,10 +11683,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45367</v>
+        <v>44578</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11704,7 +11699,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11747,7 +11742,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 39039-2024</t>
+          <t>A 61436-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11761,10 +11756,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45548</v>
+        <v>46001</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11776,13 +11771,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11825,7 +11815,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 52621-2025</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11839,10 +11829,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45953</v>
+        <v>44489</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11855,7 +11845,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11898,7 +11888,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 52622-2025</t>
+          <t>A 10910-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11912,10 +11902,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45953</v>
+        <v>44991</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11928,7 +11918,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11971,7 +11961,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 46445-2024</t>
+          <t>A 12652-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11985,10 +11975,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45582</v>
+        <v>45384</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12001,7 +11991,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12044,7 +12034,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 18948-2024</t>
+          <t>A 27792-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12058,10 +12048,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45427</v>
+        <v>45098</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12074,7 +12064,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12117,7 +12107,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 12272-2024</t>
+          <t>A 60201-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12131,10 +12121,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45378</v>
+        <v>45642</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12147,7 +12137,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12190,7 +12180,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 12281-2024</t>
+          <t>A 8541-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12204,10 +12194,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45378</v>
+        <v>45709</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12220,7 +12210,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12263,7 +12253,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 52697-2025</t>
+          <t>A 20476-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12277,10 +12267,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45956</v>
+        <v>45435</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12336,7 +12326,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7586-2025</t>
+          <t>A 7822-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12350,10 +12340,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45705</v>
+        <v>45349</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12366,7 +12356,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12409,7 +12399,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 53841-2025</t>
+          <t>A 24262-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12423,10 +12413,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45961</v>
+        <v>45797</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12439,7 +12429,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12482,7 +12472,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 49604-2023</t>
+          <t>A 32839-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12496,10 +12486,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45207</v>
+        <v>45109</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12512,7 +12502,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12555,7 +12545,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 53839-2025</t>
+          <t>A 34408-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12565,14 +12555,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45961</v>
+        <v>45525</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12585,7 +12575,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12628,7 +12618,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59938-2024</t>
+          <t>A 2688-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12642,10 +12632,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45642</v>
+        <v>44942</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12658,7 +12648,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12701,7 +12691,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 2688-2023</t>
+          <t>A 63811-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12715,10 +12705,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44942</v>
+        <v>46020</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12731,7 +12721,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12774,7 +12764,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 54593-2025</t>
+          <t>A 15721-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12788,10 +12778,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45965</v>
+        <v>45404</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12804,7 +12794,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12847,7 +12837,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 62669-2023</t>
+          <t>A 23327-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12861,10 +12851,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45271</v>
+        <v>46162</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12877,7 +12867,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12920,7 +12910,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 15039-2022</t>
+          <t>A 3174-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12934,10 +12924,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44657</v>
+        <v>46041</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12950,7 +12940,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12993,7 +12983,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 5286-2023</t>
+          <t>A 73251-2021</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13007,10 +12997,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44959</v>
+        <v>44550</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13023,7 +13013,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13066,7 +13056,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 7368-2025</t>
+          <t>A 14984-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13080,10 +13070,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45704</v>
+        <v>45399</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13096,7 +13086,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13139,7 +13129,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 23786-2022</t>
+          <t>A 14987-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13153,10 +13143,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44722</v>
+        <v>45399</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13169,7 +13159,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7.3</v>
+        <v>3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13212,7 +13202,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 21032-2023</t>
+          <t>A 969-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13226,10 +13216,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45061</v>
+        <v>44571</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13242,7 +13232,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>7.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13285,7 +13275,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 55306-2024</t>
+          <t>A 10374-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13299,10 +13289,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45621</v>
+        <v>44623</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13315,7 +13305,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13358,7 +13348,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 26270-2022</t>
+          <t>A 12281-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13372,10 +13362,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44735</v>
+        <v>45378</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13388,7 +13378,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13431,7 +13421,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 57386-2024</t>
+          <t>A 5286-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13445,10 +13435,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45629</v>
+        <v>44959</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13461,7 +13451,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13504,7 +13494,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 57011-2025</t>
+          <t>A 5754-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13518,10 +13508,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45978</v>
+        <v>45694</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13533,13 +13523,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13582,7 +13567,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 6015-2023</t>
+          <t>A 57386-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13596,10 +13581,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44964</v>
+        <v>45629</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13612,7 +13597,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>7.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13655,7 +13640,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 20743-2024</t>
+          <t>A 12272-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13669,10 +13654,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45436</v>
+        <v>45378</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13685,7 +13670,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13728,7 +13713,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 60201-2024</t>
+          <t>A 39055-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13742,10 +13727,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45642</v>
+        <v>45548</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13757,8 +13742,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13801,7 +13791,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 56957-2025</t>
+          <t>A 21032-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13811,14 +13801,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45978</v>
+        <v>45061</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13830,13 +13820,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13879,7 +13864,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 65007-2023</t>
+          <t>A 57483-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13893,10 +13878,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45287</v>
+        <v>44896</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13908,8 +13893,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>14.2</v>
+        <v>1.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13952,7 +13942,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 39492-2023</t>
+          <t>A 56765-2021</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13966,10 +13956,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45166</v>
+        <v>44481</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13981,13 +13971,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>24.9</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14030,7 +14015,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 30260-2025</t>
+          <t>A 46998-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14044,10 +14029,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45827</v>
+        <v>45586</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14060,7 +14045,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14103,7 +14088,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 64140-2023</t>
+          <t>A 65008-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14117,10 +14102,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45279</v>
+        <v>45287</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14133,7 +14118,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14176,7 +14161,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 61436-2025</t>
+          <t>A 2-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14190,10 +14175,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46001</v>
+        <v>44927</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14206,7 +14191,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14249,7 +14234,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 28195-2022</t>
+          <t>A 4832-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14263,10 +14248,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44746</v>
+        <v>44592</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14278,13 +14263,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14327,7 +14307,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34408-2024</t>
+          <t>A 62667-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14337,14 +14317,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45525</v>
+        <v>45271</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14357,7 +14337,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14400,7 +14380,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 12280-2024</t>
+          <t>A 24640-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14414,10 +14394,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45378</v>
+        <v>46171</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14430,7 +14410,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14473,7 +14453,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 18117-2025</t>
+          <t>A 39492-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14487,10 +14467,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45761</v>
+        <v>45166</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14502,8 +14482,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>24.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14546,7 +14531,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 6687-2023</t>
+          <t>A 64518-2021</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14560,10 +14545,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44966</v>
+        <v>44511</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14576,7 +14561,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14619,7 +14604,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 73251-2021</t>
+          <t>A 25409-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14633,10 +14618,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44550</v>
+        <v>45463</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14648,8 +14633,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14692,7 +14682,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 969-2022</t>
+          <t>A 2263-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14706,10 +14696,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44571</v>
+        <v>44941</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14722,7 +14712,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14765,7 +14755,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 3174-2026</t>
+          <t>A 13504-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14779,10 +14769,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46041</v>
+        <v>46094</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14838,7 +14828,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 32982-2025</t>
+          <t>A 50461-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14852,10 +14842,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45839</v>
+        <v>45601</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14867,13 +14857,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14916,7 +14901,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 32410-2025</t>
+          <t>A 61229-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14930,10 +14915,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45838</v>
+        <v>44915</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14946,7 +14931,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14989,7 +14974,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 56641-2023</t>
+          <t>A 46445-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15003,10 +14988,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45243</v>
+        <v>45582</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15019,7 +15004,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15062,7 +15047,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 61229-2022</t>
+          <t>A 4069-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15076,10 +15061,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44915</v>
+        <v>45684</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15091,8 +15076,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15135,7 +15125,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 17635-2022</t>
+          <t>A 44660-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15149,10 +15139,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44680</v>
+        <v>45574</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15165,7 +15155,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15208,7 +15198,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 36296-2022</t>
+          <t>A 44666-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15222,10 +15212,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44803</v>
+        <v>45574</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15238,7 +15228,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15281,7 +15271,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 2077-2024</t>
+          <t>A 14036-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15295,10 +15285,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45309</v>
+        <v>46098</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15311,7 +15301,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15354,7 +15344,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 61210-2023</t>
+          <t>A 20745-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15368,10 +15358,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45264</v>
+        <v>45436</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15384,7 +15374,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>7.7</v>
+        <v>1.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15427,7 +15417,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 57151-2023</t>
+          <t>A 52438-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15441,10 +15431,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45245</v>
+        <v>44874</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15457,7 +15447,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15500,7 +15490,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 63811-2025</t>
+          <t>A 50252-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15514,10 +15504,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46020</v>
+        <v>45600</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15530,7 +15520,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15573,7 +15563,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 38489-2026</t>
+          <t>A 16585-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15587,10 +15577,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46282</v>
+        <v>46112</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15603,7 +15593,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15646,7 +15636,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 34846-2026</t>
+          <t>A 27638-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15656,14 +15646,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46258</v>
+        <v>46190</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15675,8 +15665,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15719,7 +15714,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 38517-2026</t>
+          <t>A 18117-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15733,10 +15728,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46283</v>
+        <v>45761</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15748,13 +15743,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15797,7 +15787,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 10476-2025</t>
+          <t>A 3996-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15811,10 +15801,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45720</v>
+        <v>44587</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15826,13 +15816,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15875,7 +15860,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 41526-2023</t>
+          <t>A 18101-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15889,10 +15874,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45175</v>
+        <v>46125</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15904,13 +15889,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15953,7 +15933,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 33037-2026</t>
+          <t>A 18096-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15967,10 +15947,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46245</v>
+        <v>46125</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15983,7 +15963,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16026,7 +16006,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 33233-2026</t>
+          <t>A 55306-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16040,10 +16020,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46246</v>
+        <v>45621</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16056,7 +16036,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16099,7 +16079,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 33266-2026</t>
+          <t>A 37620-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16113,10 +16093,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46246</v>
+        <v>45541</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16129,7 +16109,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>5.2</v>
+        <v>0.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16172,7 +16152,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31621-2022</t>
+          <t>A 37622-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16186,10 +16166,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44775</v>
+        <v>45541</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16202,7 +16182,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16245,7 +16225,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 2314-2022</t>
+          <t>A 53416-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16259,10 +16239,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44578</v>
+        <v>45229</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16275,7 +16255,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16318,7 +16298,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 46998-2024</t>
+          <t>A 29698-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16328,14 +16308,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45586</v>
+        <v>45484</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16348,7 +16328,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16391,7 +16371,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 2263-2023</t>
+          <t>A 23786-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16405,10 +16385,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44941</v>
+        <v>44722</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16421,7 +16401,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16464,7 +16444,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 17473-2025</t>
+          <t>A 71728-2021</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16478,10 +16458,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45757</v>
+        <v>44543</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16494,7 +16474,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16537,7 +16517,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 13504-2026</t>
+          <t>A 666-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16551,10 +16531,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46094</v>
+        <v>44930</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16567,7 +16547,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16610,7 +16590,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35449-2024</t>
+          <t>A 59012-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16624,10 +16604,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45531</v>
+        <v>45636</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16640,7 +16620,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16683,7 +16663,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 14036-2026</t>
+          <t>A 26263-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16697,10 +16677,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46098</v>
+        <v>45091</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16713,7 +16693,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16756,7 +16736,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 50252-2024</t>
+          <t>A 8910-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16770,10 +16750,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45600</v>
+        <v>45713</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16786,7 +16766,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16829,7 +16809,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 4832-2022</t>
+          <t>A 8916-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16843,10 +16823,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44592</v>
+        <v>45713</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16859,7 +16839,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16902,7 +16882,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 16585-2026</t>
+          <t>A 33566-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16916,10 +16896,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46112</v>
+        <v>45520</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16932,7 +16912,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16975,7 +16955,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 38835-2024</t>
+          <t>A 59503-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16989,10 +16969,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45547</v>
+        <v>44907</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17005,7 +16985,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17048,7 +17028,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 59871-2024</t>
+          <t>A 59200-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17062,10 +17042,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45640</v>
+        <v>45253</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17078,7 +17058,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17121,7 +17101,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 18096-2026</t>
+          <t>A 10634-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17135,10 +17115,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46125</v>
+        <v>45367</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17151,7 +17131,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17194,7 +17174,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 2309-2024</t>
+          <t>A 34402-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17208,10 +17188,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45310</v>
+        <v>44792</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17224,7 +17204,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17267,7 +17247,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 18101-2026</t>
+          <t>A 18336-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17281,10 +17261,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46125</v>
+        <v>45041</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17296,8 +17276,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17340,7 +17325,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 2306-2024</t>
+          <t>A 72073-2021</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17354,10 +17339,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45310</v>
+        <v>44544</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17370,7 +17355,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17413,7 +17398,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 59200-2023</t>
+          <t>A 16596-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17427,10 +17412,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45253</v>
+        <v>45030</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17443,7 +17428,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17486,7 +17471,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 3851-2025</t>
+          <t>A 5758-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17500,10 +17485,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45683</v>
+        <v>45694</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17516,7 +17501,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17559,7 +17544,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 26263-2023</t>
+          <t>A 25435-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17573,10 +17558,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45091</v>
+        <v>45463</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17588,8 +17573,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17632,7 +17622,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 44646-2024</t>
+          <t>A 22798-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17646,10 +17636,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45574</v>
+        <v>45448</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17661,8 +17651,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17705,7 +17700,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 36305-2022</t>
+          <t>A 7368-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17719,10 +17714,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44803</v>
+        <v>45704</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17735,7 +17730,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17778,7 +17773,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 58244-2025</t>
+          <t>A 14143-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17792,10 +17787,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45985</v>
+        <v>45392</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17808,7 +17803,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17851,7 +17846,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 10374-2022</t>
+          <t>A 14732-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17865,10 +17860,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44623</v>
+        <v>44655</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17881,7 +17876,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17924,7 +17919,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 4069-2025</t>
+          <t>A 10635-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17938,10 +17933,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45684</v>
+        <v>45367</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17953,13 +17948,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18002,7 +17992,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 57967-2021</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18016,10 +18006,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44489</v>
+        <v>44487</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18032,7 +18022,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18075,7 +18065,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 20184-2026</t>
+          <t>A 2306-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18089,10 +18079,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46139</v>
+        <v>45310</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18105,7 +18095,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18148,7 +18138,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 27792-2023</t>
+          <t>A 14675-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18162,10 +18152,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45098</v>
+        <v>45397</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18178,7 +18168,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18221,7 +18211,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 32839-2023</t>
+          <t>A 36296-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18235,10 +18225,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45109</v>
+        <v>44803</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18251,7 +18241,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18294,7 +18284,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 53956-2024</t>
+          <t>A 6015-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18308,10 +18298,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45616</v>
+        <v>44964</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18324,7 +18314,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18367,7 +18357,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 17816-2023</t>
+          <t>A 8911-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18381,10 +18371,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45037</v>
+        <v>45713</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18397,7 +18387,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18440,7 +18430,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 33566-2024</t>
+          <t>A 20743-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18454,10 +18444,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45520</v>
+        <v>45436</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18470,7 +18460,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18513,7 +18503,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 16596-2023</t>
+          <t>A 44646-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18527,10 +18517,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45030</v>
+        <v>45574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18543,7 +18533,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18586,7 +18576,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 26438-2025</t>
+          <t>A 59938-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18600,10 +18590,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45807</v>
+        <v>45642</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18659,7 +18649,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 1847-2025</t>
+          <t>A 53956-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18673,10 +18663,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45671</v>
+        <v>45616</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18689,7 +18679,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18732,7 +18722,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 20259-2026</t>
+          <t>A 31621-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18746,10 +18736,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46139</v>
+        <v>44775</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18762,7 +18752,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18805,7 +18795,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 43285-2024</t>
+          <t>A 49604-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18819,10 +18809,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45568</v>
+        <v>45207</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18835,7 +18825,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18878,7 +18868,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 64374-2023</t>
+          <t>A 34846-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18892,10 +18882,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45280</v>
+        <v>46258</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18908,7 +18898,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18951,7 +18941,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 59061-2023</t>
+          <t>A 38499-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18965,10 +18955,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45252</v>
+        <v>46282</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18981,7 +18971,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19024,7 +19014,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 24247-2025</t>
+          <t>A 249-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19038,10 +19028,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45797</v>
+        <v>44565</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19054,7 +19044,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19097,7 +19087,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 30951-2022</t>
+          <t>A 28195-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19111,10 +19101,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44768</v>
+        <v>44746</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19126,8 +19116,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19170,7 +19165,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 43194-2025</t>
+          <t>A 38494-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19184,10 +19179,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45910</v>
+        <v>46282</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19200,7 +19195,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19243,7 +19238,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 33475-2024</t>
+          <t>A 38489-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19257,10 +19252,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45519</v>
+        <v>46282</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19273,7 +19268,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19316,7 +19311,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 5758-2025</t>
+          <t>A 38517-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19330,10 +19325,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45694</v>
+        <v>46283</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19345,8 +19340,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19389,7 +19389,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 26910-2025</t>
+          <t>A 14954-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19403,10 +19403,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45811</v>
+        <v>45398</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19462,7 +19462,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 5753-2025</t>
+          <t>A 65002-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19476,10 +19476,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45694</v>
+        <v>45287</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19535,7 +19535,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 15962-2025</t>
+          <t>A 22008-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19549,10 +19549,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45749</v>
+        <v>45784</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19608,7 +19608,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 37622-2024</t>
+          <t>A 57220-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19622,10 +19622,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45541</v>
+        <v>45629</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19681,7 +19681,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 22226-2026</t>
+          <t>A 45599-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19695,10 +19695,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46150</v>
+        <v>45194</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19754,7 +19754,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 22008-2025</t>
+          <t>A 33266-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19768,10 +19768,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45784</v>
+        <v>46246</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19827,7 +19827,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 14954-2024</t>
+          <t>A 11558-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19841,10 +19841,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45398</v>
+        <v>45727</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19900,7 +19900,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 65002-2023</t>
+          <t>A 33037-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19914,10 +19914,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45287</v>
+        <v>46245</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 7822-2024</t>
+          <t>A 33233-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19987,10 +19987,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45349</v>
+        <v>46246</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20046,7 +20046,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 8541-2025</t>
+          <t>A 36795-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20060,10 +20060,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45709</v>
+        <v>45538</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20119,7 +20119,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 24262-2025</t>
+          <t>A 45591-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20133,10 +20133,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45797</v>
+        <v>45194</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1.2</v>
+        <v>11</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20192,7 +20192,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 23327-2026</t>
+          <t>A 22566-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20206,10 +20206,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46162</v>
+        <v>45789</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20265,7 +20265,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 24640-2026</t>
+          <t>A 30260-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20279,10 +20279,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46171</v>
+        <v>45827</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20338,7 +20338,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 27638-2026</t>
+          <t>A 32982-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20348,14 +20348,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46190</v>
+        <v>45839</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20416,7 +20416,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 71728-2021</t>
+          <t>A 32410-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20430,10 +20430,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44543</v>
+        <v>45838</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20489,7 +20489,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 38499-2026</t>
+          <t>A 17473-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20503,10 +20503,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>46282</v>
+        <v>45757</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20562,7 +20562,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 38494-2026</t>
+          <t>A 35449-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20576,10 +20576,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>46282</v>
+        <v>45531</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20652,7 +20652,7 @@
         <v>44755</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45569</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44901</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45266</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45476</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45476</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45499</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46037</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26849-2023</t>
+          <t>A 37408-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45093</v>
+        <v>44809</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -881,153 +881,153 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 37408-2022 artfynd.xlsx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 37408-2022 karta.png", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 37408-2022 georefererad karta.tif", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 37408-2022 FSC-klagomål.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 37408-2022 FSC-klagomål mail.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 37408-2022 tillsynsbegäran.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 37408-2022 tillsynsbegäran mail.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 37408-2022 prioriterade fågelarter.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 26849-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45093</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Gullklöver
 Skogsklocka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 26849-2023 artfynd.xlsx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 26849-2023 karta.png", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 26849-2023 georefererad karta.tif", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 26849-2023 FSC-klagomål.docx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 26849-2023 FSC-klagomål mail.docx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 26849-2023 tillsynsbegäran.docx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 26849-2023 tillsynsbegäran mail.docx", "A 26849-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 37408-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44809</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 37408-2022 artfynd.xlsx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 37408-2022 karta.png", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 37408-2022 georefererad karta.tif", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 37408-2022 FSC-klagomål.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 37408-2022 FSC-klagomål mail.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 37408-2022 tillsynsbegäran.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 37408-2022 tillsynsbegäran mail.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 37408-2022 prioriterade fågelarter.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38039-2024</t>
+          <t>A 62010-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45544</v>
+        <v>44914</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1416,42 +1416,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8909-2025</t>
+          <t>A 42668-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45713</v>
+        <v>45907</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1480,17 +1480,22 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>22.6</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1505,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1514,49 +1519,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 42668-2025 artfynd.xlsx", "A 42668-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 42668-2025 karta.png", "A 42668-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 42668-2025 georefererad karta.tif", "A 42668-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 42668-2025 FSC-klagomål.docx", "A 42668-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 42668-2025 FSC-klagomål mail.docx", "A 42668-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 42668-2025 tillsynsbegäran.docx", "A 42668-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 42668-2025 tillsynsbegäran mail.docx", "A 42668-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 54177-2023</t>
+          <t>A 35453-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1570,10 +1575,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45232</v>
+        <v>45531</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1586,13 +1591,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1626,258 +1631,252 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 23794-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 54177-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45232</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Strutbräken</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 54177-2023 artfynd.xlsx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 54177-2023 karta.png", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 54177-2023 georefererad karta.tif", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 54177-2023 FSC-klagomål.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 54177-2023 FSC-klagomål mail.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 54177-2023 tillsynsbegäran.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 54177-2023 tillsynsbegäran mail.docx", "A 54177-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 56642-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44893</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 42668-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45907</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>11</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Kambräken</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 42668-2025 artfynd.xlsx", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 42668-2025 karta.png", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 42668-2025 georefererad karta.tif", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 42668-2025 FSC-klagomål.docx", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 42668-2025 FSC-klagomål mail.docx", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 42668-2025 tillsynsbegäran.docx", "A 42668-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 42668-2025 tillsynsbegäran mail.docx", "A 42668-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1898,7 +1897,7 @@
         <v>45230</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,7 +2002,7 @@
         <v>44936</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2091,7 +2090,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 23794-2023</t>
+          <t>A 40853-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2105,10 +2104,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45078</v>
+        <v>45558</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2121,7 +2120,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2165,31 +2164,31 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
     </row>
@@ -2213,7 +2212,7 @@
         <v>45371</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2305,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 62010-2022</t>
+          <t>A 8909-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2320,10 +2319,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44914</v>
+        <v>45713</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2336,17 +2335,17 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.8</v>
+        <v>22.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2360,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2369,49 +2368,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40853-2024</t>
+          <t>A 56642-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2425,10 +2424,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45558</v>
+        <v>44893</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2440,14 +2439,19 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2477,46 +2481,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 35453-2024</t>
+          <t>A 38039-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,10 +2534,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45531</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2549,10 +2553,10 @@
         <v>4</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2586,39 +2590,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 57069-2021</t>
+          <t>A 46295-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44482</v>
+        <v>44847</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 46295-2022</t>
+          <t>A 36302-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44847</v>
+        <v>44803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36302-2022</t>
+          <t>A 57069-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44803</v>
+        <v>44482</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         <v>44846</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44511</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2993-2022</t>
+          <t>A 1330-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44581</v>
+        <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3647,7 +3647,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1330-2022</t>
+          <t>A 2993-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3657,14 +3657,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44572</v>
+        <v>44581</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4450-2022</t>
+          <t>A 57314-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44589</v>
+        <v>44483</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57314-2021</t>
+          <t>A 4450-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44483</v>
+        <v>44589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44511</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44820</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44474</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44589</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44466</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44481</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12280-2024</t>
+          <t>A 53416-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45378</v>
+        <v>45229</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59061-2023</t>
+          <t>A 62807-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45252</v>
+        <v>45271</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3-2023</t>
+          <t>A 14675-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44927</v>
+        <v>45397</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14651-2024</t>
+          <t>A 41074-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45397</v>
+        <v>44825</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46288-2022</t>
+          <t>A 17946-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44847</v>
+        <v>45419</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5774,7 +5774,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 46290-2022</t>
+          <t>A 59064-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44847</v>
+        <v>45252</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>8.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5843,11 +5843,31 @@
         <v>0</v>
       </c>
       <c r="V64" s="2" t="inlineStr"/>
+      <c r="Z64">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AA64">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AB64">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AC64">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AD64">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26270-2022</t>
+          <t>A 12652-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5861,10 +5881,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44735</v>
+        <v>45384</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5877,7 +5897,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5920,7 +5940,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31032-2024</t>
+          <t>A 14984-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5934,10 +5954,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45501</v>
+        <v>45399</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5950,7 +5970,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5993,7 +6013,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31033-2024</t>
+          <t>A 14987-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6007,10 +6027,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45501</v>
+        <v>45399</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6023,7 +6043,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6066,7 +6086,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56641-2023</t>
+          <t>A 46288-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6080,10 +6100,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45243</v>
+        <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6096,7 +6116,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6139,7 +6159,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36971-2024</t>
+          <t>A 46290-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6153,10 +6173,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45538</v>
+        <v>44847</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6169,7 +6189,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>17.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6212,7 +6232,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36305-2022</t>
+          <t>A 3-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6226,10 +6246,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44803</v>
+        <v>44927</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6242,7 +6262,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6285,7 +6305,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 17816-2023</t>
+          <t>A 65008-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6299,10 +6319,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45037</v>
+        <v>45287</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6315,7 +6335,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6358,7 +6378,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15962-2025</t>
+          <t>A 10635-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6372,10 +6392,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45749</v>
+        <v>45367</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6388,7 +6408,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6431,7 +6451,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7586-2025</t>
+          <t>A 46117-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6445,10 +6465,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45705</v>
+        <v>44847</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6461,7 +6481,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6504,7 +6524,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 242-2024</t>
+          <t>A 63811-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6518,10 +6538,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45294</v>
+        <v>46020</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6533,13 +6553,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6582,7 +6597,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29615-2022</t>
+          <t>A 62667-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6596,10 +6611,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44754</v>
+        <v>45271</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6611,13 +6626,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6660,7 +6670,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61210-2023</t>
+          <t>A 45599-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6674,10 +6684,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45264</v>
+        <v>45194</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6690,7 +6700,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.7</v>
+        <v>3.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6733,7 +6743,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17946-2024</t>
+          <t>A 11558-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6747,10 +6757,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45419</v>
+        <v>45727</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6763,7 +6773,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6806,7 +6816,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35611-2024</t>
+          <t>A 242-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6820,10 +6830,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45531</v>
+        <v>45294</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6835,8 +6845,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6879,7 +6894,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38760-2023</t>
+          <t>A 35611-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6893,10 +6908,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45163</v>
+        <v>45531</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6909,7 +6924,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6952,7 +6967,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17806-2023</t>
+          <t>A 20745-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6966,10 +6981,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45037</v>
+        <v>45436</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6982,7 +6997,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7025,7 +7040,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43285-2024</t>
+          <t>A 969-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7039,10 +7054,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45568</v>
+        <v>44571</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7055,7 +7070,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>7.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7098,7 +7113,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 64193-2021</t>
+          <t>A 3174-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7112,10 +7127,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44510</v>
+        <v>46041</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7128,7 +7143,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7171,7 +7186,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38835-2024</t>
+          <t>A 57967-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7185,10 +7200,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45547</v>
+        <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7201,7 +7216,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7244,7 +7259,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59064-2023</t>
+          <t>A 56765-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7258,10 +7273,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45252</v>
+        <v>44481</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7274,7 +7289,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7313,31 +7328,11 @@
         <v>0</v>
       </c>
       <c r="V84" s="2" t="inlineStr"/>
-      <c r="Z84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3851-2025</t>
+          <t>A 22798-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7351,10 +7346,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45683</v>
+        <v>45448</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7366,8 +7361,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7410,7 +7410,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 6687-2023</t>
+          <t>A 15472-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44966</v>
+        <v>45747</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 2309-2024</t>
+          <t>A 666-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45310</v>
+        <v>44930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7556,7 +7556,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39039-2024</t>
+          <t>A 3996-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45548</v>
+        <v>44587</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7585,13 +7585,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7634,7 +7629,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 62669-2023</t>
+          <t>A 20476-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7648,10 +7643,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45271</v>
+        <v>45435</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7664,7 +7659,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7707,7 +7702,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10476-2025</t>
+          <t>A 57483-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7721,10 +7716,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45720</v>
+        <v>44896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7738,7 +7733,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -7785,7 +7780,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 64140-2023</t>
+          <t>A 47798-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7799,10 +7794,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45279</v>
+        <v>45931</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7815,7 +7810,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7858,7 +7853,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15039-2022</t>
+          <t>A 47804-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7872,10 +7867,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44657</v>
+        <v>45931</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7888,7 +7883,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7931,7 +7926,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1847-2025</t>
+          <t>A 47801-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7945,10 +7940,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45671</v>
+        <v>45931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7961,7 +7956,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8004,7 +7999,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20259-2026</t>
+          <t>A 47784-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8018,10 +8013,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46139</v>
+        <v>45931</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8077,7 +8072,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58244-2025</t>
+          <t>A 47722-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8091,10 +8086,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45985</v>
+        <v>45931</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8107,7 +8102,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8150,7 +8145,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24247-2025</t>
+          <t>A 22566-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8164,10 +8159,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45797</v>
+        <v>45789</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8180,7 +8175,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8223,7 +8218,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 65007-2023</t>
+          <t>A 45591-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8237,10 +8232,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45287</v>
+        <v>45194</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8253,7 +8248,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>14.2</v>
+        <v>11</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8296,7 +8291,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18049-2024</t>
+          <t>A 47704-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8310,10 +8305,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45420</v>
+        <v>45931</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8369,7 +8364,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 41074-2022</t>
+          <t>A 47786-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8383,10 +8378,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44825</v>
+        <v>45931</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8399,7 +8394,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.8</v>
+        <v>0.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8442,7 +8437,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30951-2022</t>
+          <t>A 37620-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8456,10 +8451,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44768</v>
+        <v>45541</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8472,7 +8467,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8515,7 +8510,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15472-2025</t>
+          <t>A 48427-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8529,10 +8524,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45747</v>
+        <v>45934</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8545,7 +8540,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8588,7 +8583,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 15721-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8602,10 +8597,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44489</v>
+        <v>45404</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8618,7 +8613,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8661,7 +8656,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 45672-2024</t>
+          <t>A 2708-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8675,10 +8670,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45579</v>
+        <v>44942</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8691,7 +8686,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8734,7 +8729,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 2077-2024</t>
+          <t>A 36795-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8748,10 +8743,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45309</v>
+        <v>45538</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8764,7 +8759,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8807,7 +8802,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 62807-2023</t>
+          <t>A 10634-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8821,10 +8816,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45271</v>
+        <v>45367</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8837,7 +8832,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8880,7 +8875,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 30599-2023</t>
+          <t>A 39039-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8894,10 +8889,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45112</v>
+        <v>45548</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8909,8 +8904,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>10.1</v>
+        <v>2.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47786-2025</t>
+          <t>A 46445-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8967,10 +8967,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45931</v>
+        <v>45582</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9026,7 +9026,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 47801-2025</t>
+          <t>A 13504-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9040,10 +9040,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45931</v>
+        <v>46094</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9099,7 +9099,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20184-2026</t>
+          <t>A 12272-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9113,10 +9113,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46139</v>
+        <v>45378</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9172,7 +9172,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57151-2023</t>
+          <t>A 12281-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9186,10 +9186,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45245</v>
+        <v>45378</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9245,7 +9245,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47704-2025</t>
+          <t>A 7586-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45931</v>
+        <v>45705</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9318,7 +9318,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 47722-2025</t>
+          <t>A 14036-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45931</v>
+        <v>46098</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 47798-2025</t>
+          <t>A 2688-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9405,10 +9405,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45931</v>
+        <v>44942</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9464,7 +9464,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 47804-2025</t>
+          <t>A 52621-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9478,10 +9478,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45931</v>
+        <v>45953</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9537,7 +9537,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 47784-2025</t>
+          <t>A 52622-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9551,10 +9551,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45931</v>
+        <v>45953</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9610,7 +9610,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 48427-2025</t>
+          <t>A 62669-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45934</v>
+        <v>45271</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9683,7 +9683,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 2708-2023</t>
+          <t>A 15039-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9697,10 +9697,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44942</v>
+        <v>44657</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9756,7 +9756,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 26438-2025</t>
+          <t>A 52697-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45807</v>
+        <v>45956</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9829,7 +9829,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 2990-2022</t>
+          <t>A 5286-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44581</v>
+        <v>44959</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9902,7 +9902,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 2994-2022</t>
+          <t>A 16585-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44581</v>
+        <v>46112</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9975,7 +9975,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 52621-2025</t>
+          <t>A 53841-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9989,10 +9989,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45953</v>
+        <v>45961</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10048,7 +10048,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 52622-2025</t>
+          <t>A 53839-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10062,10 +10062,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45953</v>
+        <v>45961</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10121,7 +10121,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 5753-2025</t>
+          <t>A 18096-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45694</v>
+        <v>46125</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10194,7 +10194,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 64374-2023</t>
+          <t>A 18101-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10208,10 +10208,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45280</v>
+        <v>46125</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10267,7 +10267,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 52697-2025</t>
+          <t>A 54593-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10281,10 +10281,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45956</v>
+        <v>45965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10340,7 +10340,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 26910-2025</t>
+          <t>A 6015-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45811</v>
+        <v>44964</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10413,7 +10413,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 59944-2024</t>
+          <t>A 20743-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45642</v>
+        <v>45436</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10486,7 +10486,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 17635-2022</t>
+          <t>A 39492-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10500,10 +10500,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44680</v>
+        <v>45166</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10515,8 +10515,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>0.9</v>
+        <v>24.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10559,7 +10564,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 53839-2025</t>
+          <t>A 57011-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10573,10 +10578,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45961</v>
+        <v>45978</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10588,8 +10593,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10632,7 +10642,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 53841-2025</t>
+          <t>A 18336-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10646,10 +10656,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45961</v>
+        <v>45041</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10661,8 +10671,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10705,7 +10720,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 54593-2025</t>
+          <t>A 56957-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10715,14 +10730,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45965</v>
+        <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10734,8 +10749,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10778,7 +10798,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 33475-2024</t>
+          <t>A 58244-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10792,10 +10812,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45519</v>
+        <v>45985</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10808,7 +10828,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10851,7 +10871,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 43194-2025</t>
+          <t>A 20184-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10865,10 +10885,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45910</v>
+        <v>46139</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10881,7 +10901,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10924,7 +10944,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 35084-2024</t>
+          <t>A 8910-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10938,10 +10958,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45527</v>
+        <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10954,7 +10974,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10997,7 +11017,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 18948-2024</t>
+          <t>A 8916-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11011,10 +11031,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45427</v>
+        <v>45713</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11027,7 +11047,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11070,7 +11090,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 57011-2025</t>
+          <t>A 72073-2021</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11084,10 +11104,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45978</v>
+        <v>44544</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11099,13 +11119,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>9.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11148,7 +11163,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12252-2024</t>
+          <t>A 61436-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11162,10 +11177,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45378</v>
+        <v>46001</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11178,7 +11193,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11221,7 +11236,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 41526-2023</t>
+          <t>A 5754-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11235,10 +11250,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45175</v>
+        <v>45694</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11250,13 +11265,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11299,7 +11309,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 56957-2025</t>
+          <t>A 59012-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11309,14 +11319,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45978</v>
+        <v>45636</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11328,13 +11338,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11377,7 +11382,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 46117-2022</t>
+          <t>A 2-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11391,10 +11396,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44847</v>
+        <v>44927</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11407,7 +11412,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11450,7 +11455,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22226-2026</t>
+          <t>A 26438-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11464,10 +11469,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46150</v>
+        <v>45807</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11480,7 +11485,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11523,7 +11528,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 11929-2023</t>
+          <t>A 1847-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11537,10 +11542,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44995</v>
+        <v>45671</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11553,7 +11558,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11596,7 +11601,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 59871-2024</t>
+          <t>A 20259-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11610,10 +11615,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45640</v>
+        <v>46139</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11626,7 +11631,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11669,7 +11674,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 2314-2022</t>
+          <t>A 34402-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11683,10 +11688,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44578</v>
+        <v>44792</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11699,7 +11704,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11742,7 +11747,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 61436-2025</t>
+          <t>A 12252-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11756,10 +11761,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46001</v>
+        <v>45378</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11772,7 +11777,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11815,7 +11820,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 24247-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11829,10 +11834,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44489</v>
+        <v>45797</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11845,7 +11850,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11888,7 +11893,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 10910-2023</t>
+          <t>A 43194-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11902,10 +11907,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44991</v>
+        <v>45910</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11918,7 +11923,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11961,7 +11966,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 12652-2024</t>
+          <t>A 33475-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11975,10 +11980,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45384</v>
+        <v>45519</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11991,7 +11996,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12034,7 +12039,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 27792-2023</t>
+          <t>A 26910-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12048,10 +12053,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45098</v>
+        <v>45811</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12064,7 +12069,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12107,7 +12112,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 60201-2024</t>
+          <t>A 2990-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12121,10 +12126,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45642</v>
+        <v>44581</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12137,7 +12142,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12180,7 +12185,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 8541-2025</t>
+          <t>A 2994-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12194,10 +12199,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45709</v>
+        <v>44581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12210,7 +12215,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12253,7 +12258,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 20476-2024</t>
+          <t>A 30260-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12267,10 +12272,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45435</v>
+        <v>45827</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12283,7 +12288,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12326,7 +12331,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7822-2024</t>
+          <t>A 249-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12340,10 +12345,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45349</v>
+        <v>44565</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12356,7 +12361,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12399,7 +12404,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 24262-2025</t>
+          <t>A 22226-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12413,10 +12418,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45797</v>
+        <v>46150</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12429,7 +12434,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12472,7 +12477,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 32839-2023</t>
+          <t>A 39055-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12486,10 +12491,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45109</v>
+        <v>45548</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12501,8 +12506,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12545,7 +12555,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 34408-2024</t>
+          <t>A 52438-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12555,14 +12565,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45525</v>
+        <v>44874</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12575,7 +12585,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12618,7 +12628,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 2688-2023</t>
+          <t>A 14143-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12632,10 +12642,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44942</v>
+        <v>45392</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12648,7 +12658,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12691,7 +12701,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 63811-2025</t>
+          <t>A 7822-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12705,10 +12715,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46020</v>
+        <v>45349</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12721,7 +12731,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12764,7 +12774,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 15721-2024</t>
+          <t>A 8541-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12778,10 +12788,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45404</v>
+        <v>45709</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12794,7 +12804,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12837,7 +12847,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 23327-2026</t>
+          <t>A 17806-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12851,10 +12861,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46162</v>
+        <v>45037</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12867,7 +12877,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12910,7 +12920,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 3174-2026</t>
+          <t>A 29615-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12924,10 +12934,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46041</v>
+        <v>44754</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12939,8 +12949,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12983,7 +12998,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 73251-2021</t>
+          <t>A 24262-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12997,10 +13012,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44550</v>
+        <v>45797</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13056,7 +13071,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 14984-2024</t>
+          <t>A 32982-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13070,10 +13085,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45399</v>
+        <v>45839</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13085,8 +13100,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13129,7 +13149,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 14987-2024</t>
+          <t>A 32410-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13143,10 +13163,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45399</v>
+        <v>45838</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13159,7 +13179,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13202,7 +13222,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 969-2022</t>
+          <t>A 59944-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13216,10 +13236,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44571</v>
+        <v>45642</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13232,7 +13252,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13275,7 +13295,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 10374-2022</t>
+          <t>A 59503-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13289,10 +13309,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44623</v>
+        <v>44907</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13305,7 +13325,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13348,7 +13368,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 12281-2024</t>
+          <t>A 23327-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13362,10 +13382,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45378</v>
+        <v>46162</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13378,7 +13398,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13421,7 +13441,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 5286-2023</t>
+          <t>A 30599-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13435,10 +13455,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44959</v>
+        <v>45112</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13451,7 +13471,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5.3</v>
+        <v>10.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13494,7 +13514,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 5754-2025</t>
+          <t>A 64518-2021</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13508,10 +13528,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45694</v>
+        <v>44511</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13524,7 +13544,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13567,7 +13587,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 57386-2024</t>
+          <t>A 17473-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13581,10 +13601,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45629</v>
+        <v>45757</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13597,7 +13617,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13640,7 +13660,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 12272-2024</t>
+          <t>A 35449-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13654,10 +13674,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45378</v>
+        <v>45531</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13670,7 +13690,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13713,7 +13733,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 39055-2024</t>
+          <t>A 64193-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13727,10 +13747,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45548</v>
+        <v>44510</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13742,13 +13762,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13791,7 +13806,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 21032-2023</t>
+          <t>A 24640-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13805,10 +13820,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45061</v>
+        <v>46171</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13864,7 +13879,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 57483-2022</t>
+          <t>A 38760-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13878,10 +13893,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44896</v>
+        <v>45163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13893,13 +13908,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13942,7 +13952,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 56765-2021</t>
+          <t>A 25409-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13956,10 +13966,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44481</v>
+        <v>45463</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13971,8 +13981,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14015,7 +14030,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 46998-2024</t>
+          <t>A 14651-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14029,10 +14044,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45586</v>
+        <v>45397</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14045,7 +14060,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14088,7 +14103,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 65008-2023</t>
+          <t>A 36971-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14102,10 +14117,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45287</v>
+        <v>45538</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14118,7 +14133,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.1</v>
+        <v>17.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14161,7 +14176,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 2-2023</t>
+          <t>A 10910-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14175,10 +14190,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44927</v>
+        <v>44991</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14191,7 +14206,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14234,7 +14249,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 4832-2022</t>
+          <t>A 35084-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14248,10 +14263,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44592</v>
+        <v>45527</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14264,7 +14279,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14307,7 +14322,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 62667-2023</t>
+          <t>A 44660-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14321,10 +14336,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45271</v>
+        <v>45574</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14337,7 +14352,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14380,7 +14395,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 24640-2026</t>
+          <t>A 44666-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14394,10 +14409,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46171</v>
+        <v>45574</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14410,7 +14425,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14453,7 +14468,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 39492-2023</t>
+          <t>A 25435-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14467,10 +14482,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45166</v>
+        <v>45463</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14488,7 +14503,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>24.9</v>
+        <v>2.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14531,7 +14546,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 64518-2021</t>
+          <t>A 11929-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14545,10 +14560,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44511</v>
+        <v>44995</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14561,7 +14576,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14604,7 +14619,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 25409-2024</t>
+          <t>A 27638-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14614,14 +14629,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45463</v>
+        <v>46190</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14639,7 +14654,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14682,7 +14697,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 2263-2023</t>
+          <t>A 14732-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14696,10 +14711,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44941</v>
+        <v>44655</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14712,7 +14727,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14755,7 +14770,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 13504-2026</t>
+          <t>A 8911-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14769,10 +14784,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46094</v>
+        <v>45713</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14785,7 +14800,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14828,7 +14843,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 50461-2024</t>
+          <t>A 18049-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14842,10 +14857,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45601</v>
+        <v>45420</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14858,7 +14873,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14901,7 +14916,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 61229-2022</t>
+          <t>A 71728-2021</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14915,10 +14930,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44915</v>
+        <v>44543</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14931,7 +14946,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14974,7 +14989,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 46445-2024</t>
+          <t>A 29698-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14984,14 +14999,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45582</v>
+        <v>45484</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15004,7 +15019,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15047,7 +15062,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 4069-2025</t>
+          <t>A 45672-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15061,10 +15076,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45684</v>
+        <v>45579</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15076,13 +15091,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15125,7 +15135,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 44660-2024</t>
+          <t>A 31032-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15139,10 +15149,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45574</v>
+        <v>45501</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15155,7 +15165,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15198,7 +15208,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 44666-2024</t>
+          <t>A 31033-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15212,10 +15222,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45574</v>
+        <v>45501</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15228,7 +15238,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15271,7 +15281,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 14036-2026</t>
+          <t>A 50461-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15285,10 +15295,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46098</v>
+        <v>45601</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15301,7 +15311,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15344,7 +15354,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 20745-2024</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15358,10 +15368,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45436</v>
+        <v>44489</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15374,7 +15384,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15417,7 +15427,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 52438-2022</t>
+          <t>A 18948-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15431,10 +15441,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44874</v>
+        <v>45427</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15447,7 +15457,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15490,7 +15500,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 50252-2024</t>
+          <t>A 49604-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15504,10 +15514,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45600</v>
+        <v>45207</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15520,7 +15530,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15563,7 +15573,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 16585-2026</t>
+          <t>A 59938-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15577,10 +15587,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46112</v>
+        <v>45642</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15593,7 +15603,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15636,7 +15646,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 27638-2026</t>
+          <t>A 7368-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15646,14 +15656,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46190</v>
+        <v>45704</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15665,13 +15675,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15714,7 +15719,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 18117-2025</t>
+          <t>A 23786-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15728,10 +15733,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45761</v>
+        <v>44722</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15744,7 +15749,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15787,7 +15792,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 3996-2022</t>
+          <t>A 21032-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15801,10 +15806,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44587</v>
+        <v>45061</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15817,7 +15822,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15860,7 +15865,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 18101-2026</t>
+          <t>A 55306-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15874,10 +15879,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46125</v>
+        <v>45621</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15890,7 +15895,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15933,7 +15938,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 18096-2026</t>
+          <t>A 26270-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15947,10 +15952,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46125</v>
+        <v>44735</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15963,7 +15968,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16006,7 +16011,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 55306-2024</t>
+          <t>A 57386-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16020,10 +16025,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45621</v>
+        <v>45629</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16036,7 +16041,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16079,7 +16084,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37620-2024</t>
+          <t>A 60201-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16093,10 +16098,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45541</v>
+        <v>45642</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16109,7 +16114,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16152,7 +16157,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37622-2024</t>
+          <t>A 65007-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16166,10 +16171,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45541</v>
+        <v>45287</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16182,7 +16187,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.4</v>
+        <v>14.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16225,7 +16230,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 53416-2023</t>
+          <t>A 64140-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16239,10 +16244,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45229</v>
+        <v>45279</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16255,7 +16260,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16298,7 +16303,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 29698-2024</t>
+          <t>A 28195-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16308,14 +16313,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45484</v>
+        <v>44746</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16327,8 +16332,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16371,7 +16381,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 23786-2022</t>
+          <t>A 34408-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16381,14 +16391,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44722</v>
+        <v>45525</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16401,7 +16411,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>7.3</v>
+        <v>0.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16444,7 +16454,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 71728-2021</t>
+          <t>A 12280-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16458,10 +16468,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44543</v>
+        <v>45378</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16474,7 +16484,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16517,7 +16527,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 666-2023</t>
+          <t>A 18117-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16531,10 +16541,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44930</v>
+        <v>45761</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16547,7 +16557,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>8.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16590,7 +16600,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 59012-2024</t>
+          <t>A 6687-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16604,10 +16614,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45636</v>
+        <v>44966</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16620,7 +16630,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16663,7 +16673,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 26263-2023</t>
+          <t>A 73251-2021</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16677,10 +16687,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45091</v>
+        <v>44550</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16693,7 +16703,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16736,7 +16746,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 8910-2025</t>
+          <t>A 56641-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16750,10 +16760,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45713</v>
+        <v>45243</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16766,7 +16776,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16809,7 +16819,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 8916-2025</t>
+          <t>A 61229-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16823,10 +16833,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45713</v>
+        <v>44915</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16839,7 +16849,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16882,7 +16892,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 33566-2024</t>
+          <t>A 17635-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16896,10 +16906,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45520</v>
+        <v>44680</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16912,7 +16922,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16955,7 +16965,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 59503-2022</t>
+          <t>A 36296-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16969,10 +16979,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44907</v>
+        <v>44803</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16985,7 +16995,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17028,7 +17038,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 59200-2023</t>
+          <t>A 2077-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17042,10 +17052,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45253</v>
+        <v>45309</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17058,7 +17068,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17101,7 +17111,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 10634-2024</t>
+          <t>A 61210-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17115,10 +17125,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45367</v>
+        <v>45264</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17131,7 +17141,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.6</v>
+        <v>7.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17174,7 +17184,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 34402-2022</t>
+          <t>A 57151-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17188,10 +17198,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44792</v>
+        <v>45245</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17204,7 +17214,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17247,7 +17257,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 18336-2023</t>
+          <t>A 38499-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17261,10 +17271,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45041</v>
+        <v>46282</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17276,13 +17286,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17325,7 +17330,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 72073-2021</t>
+          <t>A 38494-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17339,10 +17344,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44544</v>
+        <v>46282</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17355,7 +17360,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>9.6</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17398,7 +17403,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 16596-2023</t>
+          <t>A 38489-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17412,10 +17417,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45030</v>
+        <v>46282</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17428,7 +17433,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17471,7 +17476,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 5758-2025</t>
+          <t>A 34846-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17485,10 +17490,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45694</v>
+        <v>46258</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17544,7 +17549,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 25435-2024</t>
+          <t>A 10476-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17558,10 +17563,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45463</v>
+        <v>45720</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17579,7 +17584,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17622,7 +17627,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 22798-2024</t>
+          <t>A 41526-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17636,10 +17641,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45448</v>
+        <v>45175</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17657,7 +17662,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17700,7 +17705,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 7368-2025</t>
+          <t>A 38517-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17714,10 +17719,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45704</v>
+        <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17729,8 +17734,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17773,7 +17783,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 14143-2024</t>
+          <t>A 33037-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17787,10 +17797,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45392</v>
+        <v>46245</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17803,7 +17813,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17846,7 +17856,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 14732-2022</t>
+          <t>A 31621-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17860,10 +17870,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44655</v>
+        <v>44775</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17876,7 +17886,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17919,7 +17929,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 10635-2024</t>
+          <t>A 2314-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17933,10 +17943,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45367</v>
+        <v>44578</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17949,7 +17959,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17992,7 +18002,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 57967-2021</t>
+          <t>A 46998-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18006,10 +18016,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44487</v>
+        <v>45586</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18022,7 +18032,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18065,7 +18075,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 2306-2024</t>
+          <t>A 33233-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18079,10 +18089,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45310</v>
+        <v>46246</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18095,7 +18105,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18138,7 +18148,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 14675-2024</t>
+          <t>A 2263-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18152,10 +18162,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45397</v>
+        <v>44941</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18168,7 +18178,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18211,7 +18221,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 36296-2022</t>
+          <t>A 33266-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18225,10 +18235,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44803</v>
+        <v>46246</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18241,7 +18251,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18284,7 +18294,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 6015-2023</t>
+          <t>A 50252-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18298,10 +18308,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44964</v>
+        <v>45600</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18314,7 +18324,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18357,7 +18367,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 8911-2025</t>
+          <t>A 4832-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18371,10 +18381,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45713</v>
+        <v>44592</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18387,7 +18397,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18430,7 +18440,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 20743-2024</t>
+          <t>A 38835-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18444,10 +18454,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45436</v>
+        <v>45547</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18460,7 +18470,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18503,7 +18513,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 44646-2024</t>
+          <t>A 59871-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18517,10 +18527,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45574</v>
+        <v>45640</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18533,7 +18543,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18576,7 +18586,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 59938-2024</t>
+          <t>A 2309-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18590,10 +18600,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45642</v>
+        <v>45310</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18606,7 +18616,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18649,7 +18659,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 53956-2024</t>
+          <t>A 2306-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18663,10 +18673,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45616</v>
+        <v>45310</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18679,7 +18689,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18722,7 +18732,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 31621-2022</t>
+          <t>A 59200-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18736,10 +18746,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44775</v>
+        <v>45253</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18752,7 +18762,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18795,7 +18805,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 49604-2023</t>
+          <t>A 3851-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18809,10 +18819,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45207</v>
+        <v>45683</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18825,7 +18835,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18868,7 +18878,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 34846-2026</t>
+          <t>A 26263-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18882,10 +18892,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46258</v>
+        <v>45091</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18941,7 +18951,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 38499-2026</t>
+          <t>A 44646-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18955,10 +18965,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46282</v>
+        <v>45574</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18971,7 +18981,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19014,7 +19024,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 249-2022</t>
+          <t>A 36305-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19028,10 +19038,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44565</v>
+        <v>44803</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19044,7 +19054,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19087,7 +19097,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 28195-2022</t>
+          <t>A 10374-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19101,10 +19111,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44746</v>
+        <v>44623</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19116,13 +19126,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I245" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19165,7 +19170,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 38494-2026</t>
+          <t>A 4069-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19179,10 +19184,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46282</v>
+        <v>45684</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19194,8 +19199,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19238,7 +19248,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 38489-2026</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19252,10 +19262,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46282</v>
+        <v>44489</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19268,7 +19278,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19311,7 +19321,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 38517-2026</t>
+          <t>A 27792-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19325,10 +19335,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46283</v>
+        <v>45098</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19340,13 +19350,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I248" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19389,7 +19394,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 14954-2024</t>
+          <t>A 32839-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19403,10 +19408,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45398</v>
+        <v>45109</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19419,7 +19424,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19462,7 +19467,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 65002-2023</t>
+          <t>A 53956-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19476,10 +19481,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45287</v>
+        <v>45616</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19492,7 +19497,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19535,7 +19540,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 22008-2025</t>
+          <t>A 17816-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19549,10 +19554,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45784</v>
+        <v>45037</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19565,7 +19570,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19608,7 +19613,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 57220-2024</t>
+          <t>A 33566-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19622,10 +19627,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45629</v>
+        <v>45520</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19638,7 +19643,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19681,7 +19686,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 45599-2023</t>
+          <t>A 16596-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19695,10 +19700,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45194</v>
+        <v>45030</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19711,7 +19716,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19754,7 +19759,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 33266-2026</t>
+          <t>A 43285-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19768,10 +19773,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46246</v>
+        <v>45568</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19784,7 +19789,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19827,7 +19832,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 11558-2025</t>
+          <t>A 64374-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19841,10 +19846,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45727</v>
+        <v>45280</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19857,7 +19862,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19900,7 +19905,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 33037-2026</t>
+          <t>A 59061-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19914,10 +19919,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46245</v>
+        <v>45252</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19930,7 +19935,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19973,7 +19978,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 33233-2026</t>
+          <t>A 30951-2022</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19987,10 +19992,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46246</v>
+        <v>44768</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20003,7 +20008,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20046,7 +20051,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 36795-2024</t>
+          <t>A 5758-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20060,10 +20065,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45538</v>
+        <v>45694</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20076,7 +20081,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>9.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20119,7 +20124,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 45591-2023</t>
+          <t>A 5753-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20133,10 +20138,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45194</v>
+        <v>45694</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20149,7 +20154,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>11</v>
+        <v>1.5</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20192,7 +20197,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 22566-2025</t>
+          <t>A 15962-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20206,10 +20211,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45789</v>
+        <v>45749</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20222,7 +20227,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20265,7 +20270,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 30260-2025</t>
+          <t>A 37622-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20279,10 +20284,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45827</v>
+        <v>45541</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20295,7 +20300,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20338,7 +20343,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 32982-2025</t>
+          <t>A 22008-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20352,10 +20357,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45839</v>
+        <v>45784</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20367,13 +20372,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I262" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20416,7 +20416,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 32410-2025</t>
+          <t>A 14954-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20430,10 +20430,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45838</v>
+        <v>45398</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20489,7 +20489,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 17473-2025</t>
+          <t>A 65002-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20503,10 +20503,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45757</v>
+        <v>45287</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20562,7 +20562,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 35449-2024</t>
+          <t>A 57220-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20576,10 +20576,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45531</v>
+        <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20652,7 +20652,7 @@
         <v>44755</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45569</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44901</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45266</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45476</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45476</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45499</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46037</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44809</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45093</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>44914</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45907</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45531</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>45078</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>45232</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>45230</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44936</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45558</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45371</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45713</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>44893</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44847</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44482</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44846</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44511</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44581</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44483</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44511</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44820</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44474</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44589</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44466</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44481</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>45229</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45271</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45397</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44825</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45419</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>45252</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>45384</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>45399</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>45399</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>44847</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44927</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45287</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45367</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44847</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>46020</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45271</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>45194</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>45727</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>45294</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>45531</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>45436</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>44571</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>46041</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>44481</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>45448</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45747</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>44930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>44587</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>45435</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45931</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45931</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45931</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>45931</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45789</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45194</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45931</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>45931</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>45541</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>45934</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45404</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44942</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45538</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>45367</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45548</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>45582</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>46094</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>45378</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>45378</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>45705</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>46098</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44942</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45953</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>45953</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45271</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44657</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45956</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44959</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>46112</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>45961</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>45961</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>46125</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>46125</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>45965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44964</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>45436</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45166</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>45978</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>45041</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45985</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>46139</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>45713</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44544</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>46001</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45694</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45636</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44927</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45807</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45671</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>46139</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>44792</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45378</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45797</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45910</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45519</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>45811</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>44581</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>44581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>45827</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>44565</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>46150</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45548</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44874</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45392</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45349</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45709</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45037</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>44754</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>45797</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>45839</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45838</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45642</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44907</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46162</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45112</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>44511</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45757</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45531</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>44510</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>46171</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>45163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45463</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>45397</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>45538</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44991</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>45527</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>45574</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45574</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>45463</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>44995</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>46190</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>44655</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45713</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45420</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44543</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45484</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45579</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45501</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45501</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45601</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44489</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45427</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45207</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45642</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45704</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44722</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45061</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45621</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44735</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45629</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45642</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45287</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45279</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44746</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45525</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45378</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45761</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44966</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>44550</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45243</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44915</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>44680</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>44803</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45309</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45264</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45245</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>46282</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>46282</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>46282</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>46258</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45720</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45175</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>46245</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44775</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44578</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45586</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>46246</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44941</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>46246</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45600</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44592</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45547</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45640</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45310</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45310</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>45253</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45683</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45091</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>45574</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44803</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>44623</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45684</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44489</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45098</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>45109</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45616</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45037</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45520</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>45030</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>45568</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45280</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>45252</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>44768</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45694</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>45694</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45749</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45541</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45784</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>45398</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45287</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>44755</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45569</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44901</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45266</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45476</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45476</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45499</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46037</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44809</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45093</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>44914</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45907</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45531</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>45078</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>45232</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>45230</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44936</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45558</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45371</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45713</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>44893</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44847</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44482</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44846</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44511</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44581</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44483</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44511</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44820</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44474</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44589</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44466</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44481</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>45229</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45271</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45397</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44825</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45419</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>45252</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>45384</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>45399</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>45399</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>44847</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44927</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45287</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45367</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44847</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>46020</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45271</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>45194</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>45727</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>45294</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>45531</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>45436</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>44571</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>46041</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>44481</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>45448</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45747</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>44930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>44587</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>45435</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45931</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45931</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45931</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>45931</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45789</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45194</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45931</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>45931</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>45541</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>45934</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45404</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44942</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45538</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>45367</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45548</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>45582</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>46094</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>45378</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>45378</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>45705</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>46098</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44942</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45953</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>45953</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45271</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44657</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45956</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44959</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>46112</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>45961</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>45961</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>46125</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>46125</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>45965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44964</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>45436</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45166</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>45978</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>45041</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45985</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>46139</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>45713</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44544</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>46001</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45694</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45636</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44927</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45807</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45671</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>46139</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>44792</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45378</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45797</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45910</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45519</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>45811</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>44581</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>44581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>45827</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>44565</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>46150</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45548</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44874</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45392</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45349</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45709</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45037</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>44754</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>45797</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>45839</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45838</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45642</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44907</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46162</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45112</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>44511</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45757</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45531</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>44510</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>46171</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>45163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45463</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>45397</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>45538</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44991</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>45527</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>45574</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45574</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>45463</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>44995</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>46190</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>44655</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45713</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45420</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44543</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45484</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45579</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45501</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45501</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45601</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44489</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45427</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45207</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45642</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45704</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44722</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45061</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45621</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44735</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45629</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45642</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45287</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45279</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44746</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45525</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45378</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45761</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44966</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>44550</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45243</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44915</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>44680</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>44803</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45309</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45264</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45245</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>46282</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>46282</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>46282</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>46258</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45720</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45175</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>46245</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44775</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44578</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45586</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>46246</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44941</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>46246</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45600</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44592</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45547</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45640</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45310</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45310</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>45253</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45683</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45091</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>45574</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44803</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>44623</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45684</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44489</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45098</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>45109</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45616</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45037</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45520</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>45030</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>45568</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45280</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>45252</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>44768</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45694</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>45694</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45749</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45541</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45784</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>45398</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45287</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>44755</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45569</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44901</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45266</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45476</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45476</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45499</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46037</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26849-2023</t>
+          <t>A 37408-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45093</v>
+        <v>44809</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -881,153 +881,153 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 37408-2022 artfynd.xlsx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 37408-2022 karta.png", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 37408-2022 georefererad karta.tif", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 37408-2022 FSC-klagomål.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 37408-2022 FSC-klagomål mail.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 37408-2022 tillsynsbegäran.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 37408-2022 tillsynsbegäran mail.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 37408-2022 prioriterade fågelarter.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 26849-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45093</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Gullklöver
 Skogsklocka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 26849-2023 artfynd.xlsx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 26849-2023 karta.png", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 26849-2023 georefererad karta.tif", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 26849-2023 FSC-klagomål.docx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 26849-2023 FSC-klagomål mail.docx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 26849-2023 tillsynsbegäran.docx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 26849-2023 tillsynsbegäran mail.docx", "A 26849-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 37408-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44809</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 37408-2022 artfynd.xlsx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 37408-2022 karta.png", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 37408-2022 georefererad karta.tif", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 37408-2022 FSC-klagomål.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 37408-2022 FSC-klagomål mail.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 37408-2022 tillsynsbegäran.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 37408-2022 tillsynsbegäran mail.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 37408-2022 prioriterade fågelarter.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38039-2024</t>
+          <t>A 62010-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45544</v>
+        <v>44914</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1416,35 +1416,35 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
         <v>45531</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45907</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 8909-2025</t>
+          <t>A 23794-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45713</v>
+        <v>45078</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>22.6</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1733,42 +1733,42 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
         <v>45232</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56642-2022</t>
+          <t>A 53498-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44893</v>
+        <v>45230</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1909,26 +1909,21 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -1939,10 +1934,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1955,572 +1950,577 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 1320-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44936</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 40853-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 11330-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45371</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 11330-2024 artfynd.xlsx", "A 11330-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 11330-2024 karta.png", "A 11330-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 11330-2024 georefererad karta.tif", "A 11330-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 11330-2024 FSC-klagomål.docx", "A 11330-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 11330-2024 FSC-klagomål mail.docx", "A 11330-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 11330-2024 tillsynsbegäran.docx", "A 11330-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 11330-2024 tillsynsbegäran mail.docx", "A 11330-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 8909-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45713</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 56642-2022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44893</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>Svart trolldruva</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 53498-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45230</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 1320-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44936</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 23794-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 11330-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45371</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 11330-2024 artfynd.xlsx", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 11330-2024 karta.png", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 11330-2024 georefererad karta.tif", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 11330-2024 FSC-klagomål.docx", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 11330-2024 FSC-klagomål mail.docx", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 11330-2024 tillsynsbegäran.docx", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 11330-2024 tillsynsbegäran mail.docx", "A 11330-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 62010-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44914</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 40853-2024</t>
+          <t>A 38039-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45558</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2586,39 +2586,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 46295-2022</t>
+          <t>A 55070-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44847</v>
+        <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 55070-2021</t>
+          <t>A 46295-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44474</v>
+        <v>44847</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>44803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44482</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44846</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44511</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44581</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44572</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44483</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44511</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44820</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44474</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44589</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44811</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44481</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12280-2024</t>
+          <t>A 53416-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45378</v>
+        <v>45229</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59061-2023</t>
+          <t>A 62807-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45252</v>
+        <v>45271</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3-2023</t>
+          <t>A 14675-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44927</v>
+        <v>45397</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14651-2024</t>
+          <t>A 41074-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45397</v>
+        <v>44825</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 46288-2022</t>
+          <t>A 17946-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44847</v>
+        <v>45419</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46290-2022</t>
+          <t>A 59064-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44847</v>
+        <v>45252</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5770,11 +5770,31 @@
         <v>0</v>
       </c>
       <c r="V63" s="2" t="inlineStr"/>
+      <c r="Z63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AA63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AB63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AC63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AD63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61436-2025</t>
+          <t>A 46117-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5788,10 +5808,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46001</v>
+        <v>44847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5804,7 +5824,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5847,7 +5867,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26270-2022</t>
+          <t>A 12652-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5861,10 +5881,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44735</v>
+        <v>45384</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5877,7 +5897,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5920,7 +5940,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 45599-2023</t>
+          <t>A 14984-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5934,10 +5954,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45194</v>
+        <v>45399</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5950,7 +5970,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5993,7 +6013,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31032-2024</t>
+          <t>A 14987-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6007,10 +6027,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45501</v>
+        <v>45399</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6023,7 +6043,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6066,7 +6086,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31033-2024</t>
+          <t>A 46288-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6080,10 +6100,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45501</v>
+        <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6096,7 +6116,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6139,7 +6159,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56641-2023</t>
+          <t>A 46290-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6153,10 +6173,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45243</v>
+        <v>44847</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6169,7 +6189,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6212,7 +6232,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11558-2025</t>
+          <t>A 3-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6226,10 +6246,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45727</v>
+        <v>44927</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6242,7 +6262,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6285,7 +6305,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36305-2022</t>
+          <t>A 65008-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6299,10 +6319,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44803</v>
+        <v>45287</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6315,7 +6335,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6358,7 +6378,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36795-2024</t>
+          <t>A 10635-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6372,10 +6392,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45538</v>
+        <v>45367</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6388,7 +6408,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>9.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6431,7 +6451,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36971-2024</t>
+          <t>A 63811-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6445,10 +6465,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45538</v>
+        <v>46020</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6461,7 +6481,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>17.9</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6504,7 +6524,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 45591-2023</t>
+          <t>A 62667-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6518,10 +6538,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45194</v>
+        <v>45271</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6534,7 +6554,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6577,7 +6597,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17816-2023</t>
+          <t>A 45599-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6591,10 +6611,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45037</v>
+        <v>45194</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6607,7 +6627,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6650,7 +6670,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22566-2025</t>
+          <t>A 11558-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6664,10 +6684,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45789</v>
+        <v>45727</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6680,7 +6700,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6723,7 +6743,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15472-2025</t>
+          <t>A 242-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6737,10 +6757,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45747</v>
+        <v>45294</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6752,8 +6772,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>8.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6796,7 +6821,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 15962-2025</t>
+          <t>A 35611-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6810,10 +6835,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45749</v>
+        <v>45531</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6826,7 +6851,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6869,7 +6894,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7586-2025</t>
+          <t>A 20745-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6883,10 +6908,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45705</v>
+        <v>45436</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6899,7 +6924,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6942,7 +6967,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30260-2025</t>
+          <t>A 57967-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6956,10 +6981,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45827</v>
+        <v>44487</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7015,7 +7040,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 242-2024</t>
+          <t>A 56765-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7029,10 +7054,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45294</v>
+        <v>44481</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7044,13 +7069,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7093,7 +7113,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29615-2022</t>
+          <t>A 22566-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7107,10 +7127,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44754</v>
+        <v>45789</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7122,13 +7142,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7171,7 +7186,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61210-2023</t>
+          <t>A 45591-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7185,10 +7200,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45264</v>
+        <v>45194</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7201,7 +7216,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.7</v>
+        <v>11</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7244,7 +7259,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47786-2025</t>
+          <t>A 15472-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7258,10 +7273,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45931</v>
+        <v>45747</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7274,7 +7289,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7317,7 +7332,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47801-2025</t>
+          <t>A 22798-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7331,10 +7346,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45931</v>
+        <v>45448</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7346,8 +7361,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7390,7 +7410,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17946-2024</t>
+          <t>A 36795-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7404,10 +7424,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45419</v>
+        <v>45538</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7420,7 +7440,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7463,7 +7483,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47704-2025</t>
+          <t>A 666-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7477,10 +7497,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45931</v>
+        <v>44930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7493,7 +7513,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7536,7 +7556,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47722-2025</t>
+          <t>A 3996-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7550,10 +7570,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45931</v>
+        <v>44587</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7566,7 +7586,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7609,7 +7629,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47798-2025</t>
+          <t>A 20476-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7623,10 +7643,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45931</v>
+        <v>45435</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7639,7 +7659,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7682,7 +7702,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47804-2025</t>
+          <t>A 969-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7696,10 +7716,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45931</v>
+        <v>44571</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7712,7 +7732,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.3</v>
+        <v>7.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7755,7 +7775,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47784-2025</t>
+          <t>A 30260-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7769,10 +7789,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45931</v>
+        <v>45827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7785,7 +7805,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7828,7 +7848,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35611-2024</t>
+          <t>A 57483-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7842,10 +7862,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45531</v>
+        <v>44896</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7857,8 +7877,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7901,7 +7926,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32982-2025</t>
+          <t>A 3174-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7915,10 +7940,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45839</v>
+        <v>46041</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7930,13 +7955,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7979,7 +7999,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48427-2025</t>
+          <t>A 32982-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7993,10 +8013,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45934</v>
+        <v>45839</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8008,8 +8028,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8069,7 +8094,7 @@
         <v>45838</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8125,7 +8150,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38760-2023</t>
+          <t>A 47798-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8139,10 +8164,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45163</v>
+        <v>45931</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8155,7 +8180,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8198,7 +8223,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17806-2023</t>
+          <t>A 47804-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8212,10 +8237,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45037</v>
+        <v>45931</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8228,7 +8253,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8271,7 +8296,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17473-2025</t>
+          <t>A 47801-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8285,10 +8310,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45757</v>
+        <v>45931</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8301,7 +8326,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8344,7 +8369,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 63811-2025</t>
+          <t>A 47784-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8358,10 +8383,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46020</v>
+        <v>45931</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8374,7 +8399,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8417,7 +8442,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 35449-2024</t>
+          <t>A 47722-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8431,10 +8456,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45531</v>
+        <v>45931</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8447,7 +8472,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.8</v>
+        <v>0.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8490,7 +8515,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 52621-2025</t>
+          <t>A 47704-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8504,10 +8529,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45953</v>
+        <v>45931</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8520,7 +8545,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8563,7 +8588,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 52622-2025</t>
+          <t>A 37620-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8577,10 +8602,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45953</v>
+        <v>45541</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8593,7 +8618,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8636,7 +8661,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 43285-2024</t>
+          <t>A 47786-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8650,10 +8675,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45568</v>
+        <v>45931</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8666,7 +8691,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8709,7 +8734,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 52697-2025</t>
+          <t>A 48427-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8723,10 +8748,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45956</v>
+        <v>45934</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8739,7 +8764,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8782,7 +8807,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 6687-2023</t>
+          <t>A 15721-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8796,10 +8821,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44966</v>
+        <v>45404</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8812,7 +8837,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8855,7 +8880,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 64193-2021</t>
+          <t>A 2708-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8869,10 +8894,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44510</v>
+        <v>44942</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8885,7 +8910,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8928,7 +8953,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 59064-2023</t>
+          <t>A 17473-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8942,10 +8967,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45252</v>
+        <v>45757</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8958,7 +8983,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8997,31 +9022,11 @@
         <v>0</v>
       </c>
       <c r="V107" s="2" t="inlineStr"/>
-      <c r="Z107">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AA107">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AB107">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AC107">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AD107">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 53839-2025</t>
+          <t>A 10634-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9035,10 +9040,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45961</v>
+        <v>45367</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9051,7 +9056,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9094,7 +9099,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53841-2025</t>
+          <t>A 39039-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9108,10 +9113,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45961</v>
+        <v>45548</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9123,8 +9128,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9167,7 +9177,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 54593-2025</t>
+          <t>A 35449-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9181,10 +9191,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45965</v>
+        <v>45531</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9197,7 +9207,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9240,7 +9250,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 38835-2024</t>
+          <t>A 46445-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9254,10 +9264,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45547</v>
+        <v>45582</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9270,7 +9280,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9313,7 +9323,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 3851-2025</t>
+          <t>A 12272-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9327,10 +9337,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45683</v>
+        <v>45378</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9343,7 +9353,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9386,7 +9396,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 3174-2026</t>
+          <t>A 12281-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9400,10 +9410,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46041</v>
+        <v>45378</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9416,7 +9426,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9459,7 +9469,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 39039-2024</t>
+          <t>A 7586-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9473,10 +9483,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45548</v>
+        <v>45705</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9488,13 +9498,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9537,7 +9542,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 64140-2023</t>
+          <t>A 2688-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9551,10 +9556,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45279</v>
+        <v>44942</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,7 +9572,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9610,7 +9615,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62669-2023</t>
+          <t>A 52621-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9624,10 +9629,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45271</v>
+        <v>45953</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,7 +9645,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9683,7 +9688,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 969-2022</t>
+          <t>A 52622-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9697,10 +9702,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44571</v>
+        <v>45953</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9718,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>7.1</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9756,7 +9761,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 57011-2025</t>
+          <t>A 62669-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9770,10 +9775,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45978</v>
+        <v>45271</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9785,13 +9790,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9834,7 +9834,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 10476-2025</t>
+          <t>A 15039-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45720</v>
+        <v>44657</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9863,13 +9863,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9912,7 +9907,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 2309-2024</t>
+          <t>A 52697-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9926,10 +9921,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45310</v>
+        <v>45956</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9942,7 +9937,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9985,7 +9980,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 5286-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9999,10 +9994,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44489</v>
+        <v>44959</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10015,7 +10010,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10058,7 +10053,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56957-2025</t>
+          <t>A 53841-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10068,14 +10063,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45978</v>
+        <v>45961</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10087,13 +10082,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10136,7 +10126,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 15039-2022</t>
+          <t>A 53839-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10150,10 +10140,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44657</v>
+        <v>45961</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10166,7 +10156,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10209,7 +10199,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 65007-2023</t>
+          <t>A 54593-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10223,10 +10213,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45287</v>
+        <v>45965</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10239,7 +10229,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>14.2</v>
+        <v>2.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10282,7 +10272,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 18049-2024</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10296,10 +10286,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45420</v>
+        <v>44489</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10312,7 +10302,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10355,7 +10345,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 41074-2022</t>
+          <t>A 6015-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10369,10 +10359,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44825</v>
+        <v>44964</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10385,7 +10375,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10428,7 +10418,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 30951-2022</t>
+          <t>A 20743-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10442,10 +10432,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44768</v>
+        <v>45436</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10458,7 +10448,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10501,7 +10491,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 45672-2024</t>
+          <t>A 39492-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10515,10 +10505,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45579</v>
+        <v>45166</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10530,8 +10520,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>24.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10574,7 +10569,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2077-2024</t>
+          <t>A 57011-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10588,10 +10583,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45309</v>
+        <v>45978</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10603,8 +10598,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10647,7 +10647,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 62807-2023</t>
+          <t>A 18336-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10661,10 +10661,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45271</v>
+        <v>45041</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10676,8 +10676,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10720,7 +10725,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 30599-2023</t>
+          <t>A 56957-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10730,14 +10735,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45112</v>
+        <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10749,8 +10754,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>10.1</v>
+        <v>0.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10793,7 +10803,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 57151-2023</t>
+          <t>A 8910-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10807,10 +10817,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45245</v>
+        <v>45713</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10823,7 +10833,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10866,7 +10876,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 2708-2023</t>
+          <t>A 8916-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10880,10 +10890,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44942</v>
+        <v>45713</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10896,7 +10906,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10939,7 +10949,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 13504-2026</t>
+          <t>A 72073-2021</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10953,10 +10963,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46094</v>
+        <v>44544</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10969,7 +10979,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11012,7 +11022,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14036-2026</t>
+          <t>A 5754-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11026,10 +11036,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46098</v>
+        <v>45694</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11042,7 +11052,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11085,7 +11095,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 2990-2022</t>
+          <t>A 59012-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11099,10 +11109,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44581</v>
+        <v>45636</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11115,7 +11125,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11158,7 +11168,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 2994-2022</t>
+          <t>A 61436-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11172,10 +11182,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44581</v>
+        <v>46001</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11188,7 +11198,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11231,7 +11241,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 5753-2025</t>
+          <t>A 2-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11245,10 +11255,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45694</v>
+        <v>44927</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11261,7 +11271,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11304,7 +11314,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 64374-2023</t>
+          <t>A 13504-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11318,10 +11328,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45280</v>
+        <v>46094</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11334,7 +11344,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11377,7 +11387,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 16585-2026</t>
+          <t>A 14036-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11391,10 +11401,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46112</v>
+        <v>46098</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11407,7 +11417,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11450,7 +11460,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 59944-2024</t>
+          <t>A 34402-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11464,10 +11474,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45642</v>
+        <v>44792</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11480,7 +11490,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11523,7 +11533,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 17635-2022</t>
+          <t>A 12252-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11537,10 +11547,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44680</v>
+        <v>45378</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11553,7 +11563,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11596,7 +11606,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 18101-2026</t>
+          <t>A 2990-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11610,10 +11620,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46125</v>
+        <v>44581</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11626,7 +11636,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11669,7 +11679,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 18096-2026</t>
+          <t>A 2994-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11683,10 +11693,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46125</v>
+        <v>44581</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11699,7 +11709,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11742,7 +11752,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 35084-2024</t>
+          <t>A 16585-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11756,10 +11766,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45527</v>
+        <v>46112</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11772,7 +11782,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11815,7 +11825,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 18948-2024</t>
+          <t>A 18096-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11829,10 +11839,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45427</v>
+        <v>46125</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11845,7 +11855,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11888,7 +11898,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 12252-2024</t>
+          <t>A 249-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11902,10 +11912,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45378</v>
+        <v>44565</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11918,7 +11928,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11961,7 +11971,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 41526-2023</t>
+          <t>A 39055-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11975,10 +11985,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45175</v>
+        <v>45548</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12039,7 +12049,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 1847-2025</t>
+          <t>A 18101-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12053,10 +12063,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45671</v>
+        <v>46125</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12069,7 +12079,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12112,7 +12122,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 46117-2022</t>
+          <t>A 52438-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12126,10 +12136,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44847</v>
+        <v>44874</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12142,7 +12152,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12185,7 +12195,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 20259-2026</t>
+          <t>A 14143-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12199,10 +12209,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46139</v>
+        <v>45392</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12258,7 +12268,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 58244-2025</t>
+          <t>A 17806-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12272,10 +12282,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45985</v>
+        <v>45037</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12288,7 +12298,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12331,7 +12341,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 24247-2025</t>
+          <t>A 29615-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12345,10 +12355,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45797</v>
+        <v>44754</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12360,8 +12370,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12404,7 +12419,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 11929-2023</t>
+          <t>A 59944-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12418,10 +12433,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44995</v>
+        <v>45642</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12434,7 +12449,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12477,7 +12492,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 59871-2024</t>
+          <t>A 59503-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12491,10 +12506,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45640</v>
+        <v>44907</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12507,7 +12522,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12550,7 +12565,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 2314-2022</t>
+          <t>A 30599-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12564,10 +12579,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44578</v>
+        <v>45112</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12580,7 +12595,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12623,7 +12638,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 64518-2021</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12637,10 +12652,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44489</v>
+        <v>44511</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12653,7 +12668,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12696,7 +12711,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 10910-2023</t>
+          <t>A 58244-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12710,10 +12725,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44991</v>
+        <v>45985</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12726,7 +12741,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12769,7 +12784,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 12652-2024</t>
+          <t>A 64193-2021</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12783,10 +12798,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45384</v>
+        <v>44510</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12799,7 +12814,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12842,7 +12857,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27792-2023</t>
+          <t>A 20184-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12856,10 +12871,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45098</v>
+        <v>46139</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12872,7 +12887,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.3</v>
+        <v>6.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12915,7 +12930,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 20184-2026</t>
+          <t>A 38760-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12929,10 +12944,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46139</v>
+        <v>45163</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12945,7 +12960,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12988,7 +13003,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 60201-2024</t>
+          <t>A 25409-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13002,10 +13017,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45642</v>
+        <v>45463</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13017,8 +13032,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13061,7 +13081,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20476-2024</t>
+          <t>A 14651-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13075,10 +13095,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45435</v>
+        <v>45397</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13091,7 +13111,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13134,7 +13154,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 26438-2025</t>
+          <t>A 36971-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13148,10 +13168,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45807</v>
+        <v>45538</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13164,7 +13184,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.9</v>
+        <v>17.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13207,7 +13227,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 32839-2023</t>
+          <t>A 26438-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13221,10 +13241,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45109</v>
+        <v>45807</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13237,7 +13257,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13280,7 +13300,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 34408-2024</t>
+          <t>A 1847-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13290,14 +13310,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45525</v>
+        <v>45671</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13310,7 +13330,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13353,7 +13373,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 2688-2023</t>
+          <t>A 20259-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13367,10 +13387,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44942</v>
+        <v>46139</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13383,7 +13403,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13426,7 +13446,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 26910-2025</t>
+          <t>A 10910-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13440,10 +13460,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45811</v>
+        <v>44991</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13456,7 +13476,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13499,7 +13519,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 33475-2024</t>
+          <t>A 35084-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13513,10 +13533,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45519</v>
+        <v>45527</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13529,7 +13549,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13572,7 +13592,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 15721-2024</t>
+          <t>A 44660-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13586,10 +13606,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45404</v>
+        <v>45574</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13645,7 +13665,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 43194-2025</t>
+          <t>A 44666-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13659,10 +13679,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45910</v>
+        <v>45574</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13675,7 +13695,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13718,7 +13738,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 73251-2021</t>
+          <t>A 24247-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13732,10 +13752,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44550</v>
+        <v>45797</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13748,7 +13768,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13791,7 +13811,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 14984-2024</t>
+          <t>A 43194-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13805,10 +13825,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45399</v>
+        <v>45910</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13821,7 +13841,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13864,7 +13884,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 14987-2024</t>
+          <t>A 33475-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13878,10 +13898,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45399</v>
+        <v>45519</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13894,7 +13914,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13937,7 +13957,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 10374-2022</t>
+          <t>A 25435-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13951,10 +13971,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44623</v>
+        <v>45463</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13966,8 +13986,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14010,7 +14035,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 12281-2024</t>
+          <t>A 26910-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14024,10 +14049,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45378</v>
+        <v>45811</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14040,7 +14065,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14083,7 +14108,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 5286-2023</t>
+          <t>A 11929-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14097,10 +14122,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44959</v>
+        <v>44995</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14113,7 +14138,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14156,7 +14181,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 5754-2025</t>
+          <t>A 14732-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14170,10 +14195,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45694</v>
+        <v>44655</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14186,7 +14211,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14229,7 +14254,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 57386-2024</t>
+          <t>A 8911-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14243,10 +14268,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45629</v>
+        <v>45713</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14259,7 +14284,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14302,7 +14327,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 12272-2024</t>
+          <t>A 18049-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14316,10 +14341,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45378</v>
+        <v>45420</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14332,7 +14357,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14375,7 +14400,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 39055-2024</t>
+          <t>A 22226-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14389,10 +14414,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45548</v>
+        <v>46150</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14404,13 +14429,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14453,7 +14473,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 21032-2023</t>
+          <t>A 29698-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14463,14 +14483,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45061</v>
+        <v>45484</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14483,7 +14503,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14526,7 +14546,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 57483-2022</t>
+          <t>A 45672-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14540,10 +14560,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44896</v>
+        <v>45579</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14555,13 +14575,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14604,7 +14619,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 56765-2021</t>
+          <t>A 31032-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14618,10 +14633,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44481</v>
+        <v>45501</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14634,7 +14649,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14677,7 +14692,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 22226-2026</t>
+          <t>A 31033-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14691,10 +14706,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46150</v>
+        <v>45501</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14707,7 +14722,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14750,7 +14765,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 46998-2024</t>
+          <t>A 50461-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14764,10 +14779,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45586</v>
+        <v>45601</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14780,7 +14795,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14823,7 +14838,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 65008-2023</t>
+          <t>A 18948-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14837,10 +14852,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45287</v>
+        <v>45427</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14853,7 +14868,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14896,7 +14911,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 2-2023</t>
+          <t>A 7822-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14910,10 +14925,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44927</v>
+        <v>45349</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14926,7 +14941,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14969,7 +14984,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 4832-2022</t>
+          <t>A 8541-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14983,10 +14998,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44592</v>
+        <v>45709</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14999,7 +15014,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15042,7 +15057,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 62667-2023</t>
+          <t>A 49604-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15056,10 +15071,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45271</v>
+        <v>45207</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15072,7 +15087,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15115,7 +15130,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 8541-2025</t>
+          <t>A 59938-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15129,10 +15144,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45709</v>
+        <v>45642</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15145,7 +15160,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15188,7 +15203,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 7822-2024</t>
+          <t>A 24262-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15202,10 +15217,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45349</v>
+        <v>45797</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15218,7 +15233,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15261,7 +15276,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 24262-2025</t>
+          <t>A 23327-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15275,10 +15290,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45797</v>
+        <v>46162</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15291,7 +15306,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15334,7 +15349,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 39492-2023</t>
+          <t>A 7368-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15348,10 +15363,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45166</v>
+        <v>45704</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15363,13 +15378,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>24.9</v>
+        <v>1.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15412,7 +15422,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 23327-2026</t>
+          <t>A 23786-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15426,10 +15436,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46162</v>
+        <v>44722</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15442,7 +15452,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15485,7 +15495,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 64518-2021</t>
+          <t>A 21032-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15499,10 +15509,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44511</v>
+        <v>45061</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15515,7 +15525,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15558,7 +15568,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 25409-2024</t>
+          <t>A 55306-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15572,10 +15582,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45463</v>
+        <v>45621</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15587,13 +15597,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15636,7 +15641,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 2263-2023</t>
+          <t>A 26270-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15650,10 +15655,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44941</v>
+        <v>44735</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15666,7 +15671,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15709,7 +15714,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 50461-2024</t>
+          <t>A 57386-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15723,10 +15728,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45601</v>
+        <v>45629</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15739,7 +15744,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15782,7 +15787,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 61229-2022</t>
+          <t>A 24640-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15796,10 +15801,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44915</v>
+        <v>46171</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15855,7 +15860,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 46445-2024</t>
+          <t>A 60201-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15869,10 +15874,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45582</v>
+        <v>45642</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15885,7 +15890,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15928,7 +15933,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 4069-2025</t>
+          <t>A 65007-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15942,10 +15947,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45684</v>
+        <v>45287</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15957,13 +15962,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>0.4</v>
+        <v>14.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16006,7 +16006,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 44660-2024</t>
+          <t>A 64140-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16020,10 +16020,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45574</v>
+        <v>45279</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16079,7 +16079,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 44666-2024</t>
+          <t>A 28195-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16093,10 +16093,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45574</v>
+        <v>44746</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16108,8 +16108,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16152,7 +16157,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 20745-2024</t>
+          <t>A 34408-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16162,14 +16167,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45436</v>
+        <v>45525</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16182,7 +16187,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16225,7 +16230,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 24640-2026</t>
+          <t>A 12280-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16239,10 +16244,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46171</v>
+        <v>45378</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16255,7 +16260,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16298,7 +16303,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 52438-2022</t>
+          <t>A 18117-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16312,10 +16317,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44874</v>
+        <v>45761</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16328,7 +16333,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16371,7 +16376,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 50252-2024</t>
+          <t>A 6687-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16385,10 +16390,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45600</v>
+        <v>44966</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16401,7 +16406,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16444,7 +16449,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 18117-2025</t>
+          <t>A 73251-2021</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16458,10 +16463,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45761</v>
+        <v>44550</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16474,7 +16479,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16517,7 +16522,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 3996-2022</t>
+          <t>A 56641-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16531,10 +16536,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44587</v>
+        <v>45243</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16547,7 +16552,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16590,7 +16595,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 55306-2024</t>
+          <t>A 61229-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16604,10 +16609,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45621</v>
+        <v>44915</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16620,7 +16625,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16663,7 +16668,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37620-2024</t>
+          <t>A 17635-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16677,10 +16682,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45541</v>
+        <v>44680</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16693,7 +16698,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16736,7 +16741,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 37622-2024</t>
+          <t>A 36296-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16750,10 +16755,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45541</v>
+        <v>44803</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16766,7 +16771,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16809,7 +16814,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 53416-2023</t>
+          <t>A 2077-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16823,10 +16828,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45229</v>
+        <v>45309</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16839,7 +16844,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16882,7 +16887,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 29698-2024</t>
+          <t>A 61210-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16892,14 +16897,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45484</v>
+        <v>45264</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16912,7 +16917,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.4</v>
+        <v>7.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16955,7 +16960,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 23786-2022</t>
+          <t>A 27638-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16965,14 +16970,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44722</v>
+        <v>46190</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16984,8 +16989,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>7.3</v>
+        <v>2.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17028,7 +17038,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 27638-2026</t>
+          <t>A 57151-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17038,14 +17048,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46190</v>
+        <v>45245</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17057,13 +17067,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17106,7 +17111,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 666-2023</t>
+          <t>A 71728-2021</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17120,10 +17125,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44930</v>
+        <v>44543</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17136,7 +17141,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17179,7 +17184,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 59012-2024</t>
+          <t>A 10476-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17193,10 +17198,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45636</v>
+        <v>45720</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17206,6 +17211,11 @@
       <c r="G219" t="inlineStr">
         <is>
           <t>KIL</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I219" t="n">
@@ -17252,7 +17262,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 26263-2023</t>
+          <t>A 41526-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17266,10 +17276,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45091</v>
+        <v>45175</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17281,8 +17291,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17325,7 +17340,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 8910-2025</t>
+          <t>A 31621-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17339,10 +17354,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45713</v>
+        <v>44775</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17355,7 +17370,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17398,7 +17413,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 8916-2025</t>
+          <t>A 2314-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17412,10 +17427,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45713</v>
+        <v>44578</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17428,7 +17443,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17471,7 +17486,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 71728-2021</t>
+          <t>A 46998-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17485,10 +17500,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44543</v>
+        <v>45586</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17501,7 +17516,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17544,7 +17559,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 33566-2024</t>
+          <t>A 2263-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17558,10 +17573,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45520</v>
+        <v>44941</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17574,7 +17589,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17617,7 +17632,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 59503-2022</t>
+          <t>A 50252-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17631,10 +17646,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44907</v>
+        <v>45600</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17647,7 +17662,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17690,7 +17705,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 59200-2023</t>
+          <t>A 4832-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17704,10 +17719,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45253</v>
+        <v>44592</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17720,7 +17735,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17763,7 +17778,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 10634-2024</t>
+          <t>A 38835-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17777,10 +17792,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45367</v>
+        <v>45547</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17793,7 +17808,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17836,7 +17851,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 34402-2022</t>
+          <t>A 59871-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17850,10 +17865,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44792</v>
+        <v>45640</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17866,7 +17881,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17909,7 +17924,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 18336-2023</t>
+          <t>A 2309-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17923,10 +17938,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45041</v>
+        <v>45310</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17938,13 +17953,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17987,7 +17997,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 72073-2021</t>
+          <t>A 2306-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18001,10 +18011,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44544</v>
+        <v>45310</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18017,7 +18027,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18060,7 +18070,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 16596-2023</t>
+          <t>A 59200-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18074,10 +18084,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45030</v>
+        <v>45253</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18090,7 +18100,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18133,7 +18143,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 5758-2025</t>
+          <t>A 3851-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18147,10 +18157,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45694</v>
+        <v>45683</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18163,7 +18173,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18206,7 +18216,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 25435-2024</t>
+          <t>A 26263-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18220,10 +18230,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45463</v>
+        <v>45091</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18235,13 +18245,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18284,7 +18289,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 22798-2024</t>
+          <t>A 44646-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18298,10 +18303,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45448</v>
+        <v>45574</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18313,13 +18318,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18362,7 +18362,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 7368-2025</t>
+          <t>A 36305-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18376,10 +18376,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45704</v>
+        <v>44803</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18435,7 +18435,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 14143-2024</t>
+          <t>A 10374-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18449,10 +18449,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45392</v>
+        <v>44623</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18508,7 +18508,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 14732-2022</t>
+          <t>A 4069-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18522,10 +18522,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44655</v>
+        <v>45684</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18537,8 +18537,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18581,7 +18586,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 10635-2024</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18595,10 +18600,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45367</v>
+        <v>44489</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18611,7 +18616,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18654,7 +18659,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 57967-2021</t>
+          <t>A 27792-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18668,10 +18673,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44487</v>
+        <v>45098</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18684,7 +18689,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18727,7 +18732,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 2306-2024</t>
+          <t>A 32839-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18741,10 +18746,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45310</v>
+        <v>45109</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18757,7 +18762,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18800,7 +18805,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 14675-2024</t>
+          <t>A 53956-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18814,10 +18819,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45397</v>
+        <v>45616</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18830,7 +18835,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18873,7 +18878,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 36296-2022</t>
+          <t>A 17816-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18887,10 +18892,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44803</v>
+        <v>45037</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18903,7 +18908,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18946,7 +18951,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 6015-2023</t>
+          <t>A 33566-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18960,10 +18965,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44964</v>
+        <v>45520</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18976,7 +18981,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19019,7 +19024,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 8911-2025</t>
+          <t>A 16596-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19033,10 +19038,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45713</v>
+        <v>45030</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19049,7 +19054,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19092,7 +19097,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 20743-2024</t>
+          <t>A 38499-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19106,10 +19111,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45436</v>
+        <v>46282</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19122,7 +19127,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19165,7 +19170,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 44646-2024</t>
+          <t>A 38494-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19179,10 +19184,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45574</v>
+        <v>46282</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19195,7 +19200,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19238,7 +19243,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 59938-2024</t>
+          <t>A 38489-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19252,10 +19257,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45642</v>
+        <v>46282</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19268,7 +19273,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19311,7 +19316,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 53956-2024</t>
+          <t>A 34846-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19325,10 +19330,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45616</v>
+        <v>46258</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19341,7 +19346,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19384,7 +19389,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 31621-2022</t>
+          <t>A 43285-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19398,10 +19403,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44775</v>
+        <v>45568</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19414,7 +19419,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19457,7 +19462,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 49604-2023</t>
+          <t>A 64374-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19471,10 +19476,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45207</v>
+        <v>45280</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19487,7 +19492,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19530,7 +19535,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 249-2022</t>
+          <t>A 59061-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19544,10 +19549,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44565</v>
+        <v>45252</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19560,7 +19565,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19603,7 +19608,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 28195-2022</t>
+          <t>A 38517-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19617,10 +19622,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>44746</v>
+        <v>46283</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19634,11 +19639,11 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19681,7 +19686,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 34846-2026</t>
+          <t>A 30951-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19695,10 +19700,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46258</v>
+        <v>44768</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19711,7 +19716,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19754,7 +19759,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 38499-2026</t>
+          <t>A 5758-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19768,10 +19773,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46282</v>
+        <v>45694</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19784,7 +19789,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19827,7 +19832,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 14954-2024</t>
+          <t>A 33037-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19841,10 +19846,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45398</v>
+        <v>46245</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19857,7 +19862,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19900,7 +19905,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 65002-2023</t>
+          <t>A 5753-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19914,10 +19919,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45287</v>
+        <v>45694</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19930,7 +19935,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>6.9</v>
+        <v>1.5</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19973,7 +19978,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 22008-2025</t>
+          <t>A 15962-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19987,10 +19992,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45784</v>
+        <v>45749</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20003,7 +20008,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20046,7 +20051,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 57220-2024</t>
+          <t>A 37622-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20060,10 +20065,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45629</v>
+        <v>45541</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20076,7 +20081,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20119,7 +20124,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 38494-2026</t>
+          <t>A 33233-2026</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20133,10 +20138,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46282</v>
+        <v>46246</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20149,7 +20154,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20192,7 +20197,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 38489-2026</t>
+          <t>A 33266-2026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20206,10 +20211,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46282</v>
+        <v>46246</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20222,7 +20227,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20265,7 +20270,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 38517-2026</t>
+          <t>A 22008-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20279,10 +20284,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46283</v>
+        <v>45784</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20294,13 +20299,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I261" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 33266-2026</t>
+          <t>A 14954-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20357,10 +20357,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46246</v>
+        <v>45398</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20416,7 +20416,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 33037-2026</t>
+          <t>A 65002-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20430,10 +20430,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>46245</v>
+        <v>45287</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>5.4</v>
+        <v>6.9</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20489,7 +20489,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 33233-2026</t>
+          <t>A 57220-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20503,10 +20503,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>46246</v>
+        <v>45629</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20579,7 +20579,7 @@
         <v>44755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45569</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45266</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45266</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45476</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45476</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45499</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46037</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26849-2023</t>
+          <t>A 37408-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45093</v>
+        <v>44809</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -881,153 +881,153 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 37408-2022 artfynd.xlsx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 37408-2022 karta.png", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 37408-2022 georefererad karta.tif", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 37408-2022 FSC-klagomål.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 37408-2022 FSC-klagomål mail.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 37408-2022 tillsynsbegäran.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 37408-2022 tillsynsbegäran mail.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 37408-2022 prioriterade fågelarter.docx", "A 37408-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 26849-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45093</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Gullklöver
 Skogsklocka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 26849-2023 artfynd.xlsx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 26849-2023 karta.png", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 26849-2023 georefererad karta.tif", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 26849-2023 FSC-klagomål.docx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 26849-2023 FSC-klagomål mail.docx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 26849-2023 tillsynsbegäran.docx", "A 26849-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 26849-2023 tillsynsbegäran mail.docx", "A 26849-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 37408-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44809</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 37408-2022 artfynd.xlsx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 37408-2022 karta.png", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 37408-2022 georefererad karta.tif", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 37408-2022 FSC-klagomål.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 37408-2022 FSC-klagomål mail.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 37408-2022 tillsynsbegäran.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 37408-2022 tillsynsbegäran mail.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 37408-2022 prioriterade fågelarter.docx", "A 37408-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 54177-2023</t>
+          <t>A 42668-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45232</v>
+        <v>45907</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1375,8 +1375,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1409,899 +1414,894 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 42668-2025 artfynd.xlsx", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 42668-2025 karta.png", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 42668-2025 georefererad karta.tif", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 42668-2025 FSC-klagomål.docx", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 42668-2025 FSC-klagomål mail.docx", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 42668-2025 tillsynsbegäran.docx", "A 42668-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 42668-2025 tillsynsbegäran mail.docx", "A 42668-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 62010-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44914</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 35453-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45531</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 23794-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 54177-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45232</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Strutbräken</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 54177-2023 artfynd.xlsx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 54177-2023 karta.png", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 54177-2023 georefererad karta.tif", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 54177-2023 FSC-klagomål.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 54177-2023 FSC-klagomål mail.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 54177-2023 tillsynsbegäran.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 54177-2023 tillsynsbegäran mail.docx", "A 54177-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 53498-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45230</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 1320-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44936</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 40853-2024</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>45558</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>1.7</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 56642-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44893</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 11330-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45371</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T17" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 53498-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45230</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 38039-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45544</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 1320-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44936</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 23794-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 11330-2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45371</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Vanlig groda</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 11330-2024 artfynd.xlsx", "A 11330-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 11330-2024 karta.png", "A 11330-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 11330-2024 georefererad karta.tif", "A 11330-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 11330-2024 FSC-klagomål.docx", "A 11330-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 11330-2024 FSC-klagomål mail.docx", "A 11330-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 11330-2024 tillsynsbegäran.docx", "A 11330-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 11330-2024 tillsynsbegäran mail.docx", "A 11330-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 35453-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45531</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Trana</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45713</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 62010-2022</t>
+          <t>A 56642-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44914</v>
+        <v>44893</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2439,8 +2439,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>7.8</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2480,42 +2485,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 42668-2025</t>
+          <t>A 38039-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2529,10 +2534,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45907</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2544,13 +2549,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2583,42 +2583,42 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 42668-2025 artfynd.xlsx", "A 42668-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 42668-2025 karta.png", "A 42668-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 42668-2025 georefererad karta.tif", "A 42668-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 42668-2025 FSC-klagomål.docx", "A 42668-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 42668-2025 FSC-klagomål mail.docx", "A 42668-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 42668-2025 tillsynsbegäran.docx", "A 42668-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 42668-2025 tillsynsbegäran mail.docx", "A 42668-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44847</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36302-2022</t>
+          <t>A 57069-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44803</v>
+        <v>44482</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 57069-2021</t>
+          <t>A 36302-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44482</v>
+        <v>44803</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         <v>44846</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44511</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44581</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44572</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 55059-2021</t>
+          <t>A 65904-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44474</v>
+        <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3939,7 +3939,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64552-2021</t>
+          <t>A 4450-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44511</v>
+        <v>44589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 65904-2021</t>
+          <t>A 57314-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44517</v>
+        <v>44483</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62135-2021</t>
+          <t>A 64543-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44502</v>
+        <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4158,7 +4158,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 65900-2021</t>
+          <t>A 64559-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44517</v>
+        <v>44511</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 73022-2021</t>
+          <t>A 65900-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44550</v>
+        <v>44517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4321,7 +4321,7 @@
         <v>44820</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 66809-2021</t>
+          <t>A 4448-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44522</v>
+        <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>13.7</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4455,7 +4455,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 4448-2022</t>
+          <t>A 55059-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44589</v>
+        <v>44474</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4528,7 +4528,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4450-2022</t>
+          <t>A 64552-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44589</v>
+        <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57314-2021</t>
+          <t>A 62135-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44483</v>
+        <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 4445-2022</t>
+          <t>A 66809-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44589</v>
+        <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>13.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33907-2022</t>
+          <t>A 48787-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44790</v>
+        <v>44859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4776,13 +4776,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4825,7 +4820,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 64543-2021</t>
+          <t>A 73022-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4839,10 +4834,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44511</v>
+        <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4855,7 +4850,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4898,7 +4893,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 64559-2021</t>
+          <t>A 33907-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4912,10 +4907,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44511</v>
+        <v>44790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4927,8 +4922,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57065-2021</t>
+          <t>A 4445-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44482</v>
+        <v>44589</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37962-2022</t>
+          <t>A 57065-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5054,14 +5054,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44811</v>
+        <v>44482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>44481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48787-2022</t>
+          <t>A 37962-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5200,14 +5200,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44859</v>
+        <v>44811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
         <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 73251-2021</t>
+          <t>A 53416-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44550</v>
+        <v>45229</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38835-2024</t>
+          <t>A 62807-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45547</v>
+        <v>45271</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14984-2024</t>
+          <t>A 14675-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45399</v>
+        <v>45397</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14987-2024</t>
+          <t>A 41074-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45399</v>
+        <v>44825</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22798-2024</t>
+          <t>A 46117-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45448</v>
+        <v>44847</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5657,13 +5657,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5706,7 +5701,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3851-2025</t>
+          <t>A 59064-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5720,10 +5715,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45683</v>
+        <v>45252</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5736,7 +5731,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5775,11 +5770,31 @@
         <v>0</v>
       </c>
       <c r="V63" s="2" t="inlineStr"/>
+      <c r="Z63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AA63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AB63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AC63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AD63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7368-2025</t>
+          <t>A 17946-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5793,10 +5808,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45704</v>
+        <v>45419</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5809,7 +5824,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5852,7 +5867,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10374-2022</t>
+          <t>A 12652-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5866,10 +5881,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44623</v>
+        <v>45384</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5882,7 +5897,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>5.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5925,7 +5940,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12281-2024</t>
+          <t>A 14984-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5939,10 +5954,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45378</v>
+        <v>45399</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5955,7 +5970,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5998,7 +6013,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5286-2023</t>
+          <t>A 14987-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6012,10 +6027,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44959</v>
+        <v>45399</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6028,7 +6043,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6071,7 +6086,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5754-2025</t>
+          <t>A 46288-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6085,10 +6100,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45694</v>
+        <v>44847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6101,7 +6116,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6144,7 +6159,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57386-2024</t>
+          <t>A 46290-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6158,10 +6173,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45629</v>
+        <v>44847</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6174,7 +6189,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6217,7 +6232,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12272-2024</t>
+          <t>A 3-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6231,10 +6246,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45378</v>
+        <v>44927</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6247,7 +6262,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6290,7 +6305,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12280-2024</t>
+          <t>A 65008-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6304,10 +6319,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45378</v>
+        <v>45287</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6320,7 +6335,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6363,7 +6378,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39055-2024</t>
+          <t>A 10635-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6377,10 +6392,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45548</v>
+        <v>45367</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6392,13 +6407,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6441,7 +6451,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14143-2024</t>
+          <t>A 63811-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6455,10 +6465,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45392</v>
+        <v>46020</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6471,7 +6481,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6514,7 +6524,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39039-2024</t>
+          <t>A 62667-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6528,10 +6538,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45548</v>
+        <v>45271</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6543,13 +6553,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6592,7 +6597,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 21032-2023</t>
+          <t>A 969-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6606,10 +6611,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45061</v>
+        <v>44571</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6622,7 +6627,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>7.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6665,7 +6670,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 57483-2022</t>
+          <t>A 3174-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6679,10 +6684,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44896</v>
+        <v>46041</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6694,13 +6699,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6743,7 +6743,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 64140-2023</t>
+          <t>A 242-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45279</v>
+        <v>45294</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6772,8 +6772,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6816,7 +6821,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14732-2022</t>
+          <t>A 45599-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6830,10 +6835,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44655</v>
+        <v>45194</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6846,7 +6851,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6889,7 +6894,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 62669-2023</t>
+          <t>A 11558-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6903,10 +6908,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45271</v>
+        <v>45727</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6919,7 +6924,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6962,7 +6967,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10476-2025</t>
+          <t>A 35611-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6976,10 +6981,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45720</v>
+        <v>45531</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6991,13 +6996,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7040,7 +7040,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56765-2021</t>
+          <t>A 20745-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7054,10 +7054,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44481</v>
+        <v>45436</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7113,7 +7113,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2309-2024</t>
+          <t>A 15472-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45310</v>
+        <v>45747</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7186,7 +7186,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10635-2024</t>
+          <t>A 57967-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45367</v>
+        <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46998-2024</t>
+          <t>A 56765-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7273,10 +7273,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45586</v>
+        <v>44481</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7332,7 +7332,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57967-2021</t>
+          <t>A 22798-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7346,10 +7346,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44487</v>
+        <v>45448</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7361,8 +7361,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7405,7 +7410,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 65008-2023</t>
+          <t>A 666-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7419,10 +7424,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45287</v>
+        <v>44930</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7435,7 +7440,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7478,7 +7483,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15039-2022</t>
+          <t>A 3996-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7492,10 +7497,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44657</v>
+        <v>44587</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7508,7 +7513,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7551,7 +7556,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2-2023</t>
+          <t>A 20476-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7565,10 +7570,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44927</v>
+        <v>45435</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7581,7 +7586,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7624,7 +7629,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4832-2022</t>
+          <t>A 47798-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7638,10 +7643,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44592</v>
+        <v>45931</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7654,7 +7659,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7697,7 +7702,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62667-2023</t>
+          <t>A 47804-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7711,10 +7716,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45271</v>
+        <v>45931</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7727,7 +7732,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7770,7 +7775,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2306-2024</t>
+          <t>A 47801-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7784,10 +7789,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45310</v>
+        <v>45931</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7800,7 +7805,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7843,7 +7848,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 65007-2023</t>
+          <t>A 47784-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7857,10 +7862,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45287</v>
+        <v>45931</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7873,7 +7878,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>14.2</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7916,7 +7921,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59061-2023</t>
+          <t>A 47722-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7930,10 +7935,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45252</v>
+        <v>45931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7946,7 +7951,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.2</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7989,7 +7994,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18049-2024</t>
+          <t>A 47704-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8003,10 +8008,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45420</v>
+        <v>45931</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8062,7 +8067,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39492-2023</t>
+          <t>A 47786-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8076,10 +8081,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45166</v>
+        <v>45931</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8091,13 +8096,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>24.9</v>
+        <v>0.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8140,7 +8140,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41074-2022</t>
+          <t>A 48427-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8154,10 +8154,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44825</v>
+        <v>45934</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8213,7 +8213,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 64518-2021</t>
+          <t>A 57483-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44511</v>
+        <v>44896</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8242,8 +8242,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8286,7 +8291,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 25409-2024</t>
+          <t>A 22566-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8300,10 +8305,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45463</v>
+        <v>45789</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8315,13 +8320,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8364,7 +8364,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30951-2022</t>
+          <t>A 45591-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8378,10 +8378,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44768</v>
+        <v>45194</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8437,7 +8437,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 2263-2023</t>
+          <t>A 37620-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44941</v>
+        <v>45541</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8510,7 +8510,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 14675-2024</t>
+          <t>A 13504-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8524,10 +8524,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45397</v>
+        <v>46094</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8583,7 +8583,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 36296-2022</t>
+          <t>A 15721-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44803</v>
+        <v>45404</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8656,7 +8656,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 45672-2024</t>
+          <t>A 36795-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8670,10 +8670,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45579</v>
+        <v>45538</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8729,7 +8729,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 2077-2024</t>
+          <t>A 14036-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45309</v>
+        <v>46098</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8802,7 +8802,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 50461-2024</t>
+          <t>A 2708-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8816,10 +8816,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45601</v>
+        <v>44942</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61229-2022</t>
+          <t>A 10634-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44915</v>
+        <v>45367</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8948,7 +8948,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 6015-2023</t>
+          <t>A 39039-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44964</v>
+        <v>45548</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8977,8 +8977,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9021,7 +9026,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 46445-2024</t>
+          <t>A 52621-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9035,10 +9040,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45582</v>
+        <v>45953</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9051,7 +9056,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9094,7 +9099,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 8911-2025</t>
+          <t>A 52622-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9108,10 +9113,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45713</v>
+        <v>45953</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9124,7 +9129,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9167,7 +9172,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20743-2024</t>
+          <t>A 46445-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9181,10 +9186,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45436</v>
+        <v>45582</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9197,7 +9202,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9240,7 +9245,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 4069-2025</t>
+          <t>A 52697-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9254,10 +9259,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45684</v>
+        <v>45956</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9269,13 +9274,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9318,7 +9318,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 44660-2024</t>
+          <t>A 12272-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45574</v>
+        <v>45378</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 44666-2024</t>
+          <t>A 12281-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9405,10 +9405,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45574</v>
+        <v>45378</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9464,7 +9464,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 44646-2024</t>
+          <t>A 7586-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9478,10 +9478,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45574</v>
+        <v>45705</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9537,7 +9537,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 62807-2023</t>
+          <t>A 53841-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9551,10 +9551,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45271</v>
+        <v>45961</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9610,7 +9610,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20745-2024</t>
+          <t>A 53839-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45436</v>
+        <v>45961</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9683,7 +9683,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 3-2023</t>
+          <t>A 54593-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9697,10 +9697,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44927</v>
+        <v>45965</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9756,7 +9756,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 14651-2024</t>
+          <t>A 2688-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45397</v>
+        <v>44942</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9829,7 +9829,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 46288-2022</t>
+          <t>A 16585-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44847</v>
+        <v>46112</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9902,7 +9902,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 46290-2022</t>
+          <t>A 62669-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44847</v>
+        <v>45271</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9975,7 +9975,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 52438-2022</t>
+          <t>A 15039-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9989,10 +9989,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44874</v>
+        <v>44657</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10048,7 +10048,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 59938-2024</t>
+          <t>A 5286-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10062,10 +10062,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45642</v>
+        <v>44959</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10121,7 +10121,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 53956-2024</t>
+          <t>A 18096-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45616</v>
+        <v>46125</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10194,7 +10194,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 31621-2022</t>
+          <t>A 18101-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10208,10 +10208,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44775</v>
+        <v>46125</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10267,7 +10267,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 50252-2024</t>
+          <t>A 57011-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10281,10 +10281,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45600</v>
+        <v>45978</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10296,8 +10296,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10340,7 +10345,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30599-2023</t>
+          <t>A 56957-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10350,14 +10355,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45112</v>
+        <v>45978</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10369,8 +10374,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>10.1</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10413,7 +10423,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 18117-2025</t>
+          <t>A 6015-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10427,10 +10437,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45761</v>
+        <v>44964</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10486,7 +10496,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 49604-2023</t>
+          <t>A 20743-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10500,10 +10510,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45207</v>
+        <v>45436</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10516,7 +10526,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10559,7 +10569,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 57151-2023</t>
+          <t>A 39492-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10573,10 +10583,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45245</v>
+        <v>45166</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10588,8 +10598,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>24.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10632,7 +10647,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 3996-2022</t>
+          <t>A 58244-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10646,10 +10661,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44587</v>
+        <v>45985</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10662,7 +10677,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10705,7 +10720,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 249-2022</t>
+          <t>A 20184-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10719,10 +10734,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44565</v>
+        <v>46139</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10735,7 +10750,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10778,7 +10793,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 28195-2022</t>
+          <t>A 18336-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10792,10 +10807,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44746</v>
+        <v>45041</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10813,7 +10828,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10856,7 +10871,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 55306-2024</t>
+          <t>A 61436-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10870,10 +10885,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45621</v>
+        <v>46001</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10886,7 +10901,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10929,7 +10944,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 14954-2024</t>
+          <t>A 8910-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10943,10 +10958,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45398</v>
+        <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10959,7 +10974,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11002,7 +11017,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 65002-2023</t>
+          <t>A 8916-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11016,10 +11031,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45287</v>
+        <v>45713</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11032,7 +11047,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.9</v>
+        <v>2.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11075,7 +11090,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 22008-2025</t>
+          <t>A 72073-2021</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11089,10 +11104,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45784</v>
+        <v>44544</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11105,7 +11120,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>9.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11148,7 +11163,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 37620-2024</t>
+          <t>A 26438-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11162,10 +11177,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45541</v>
+        <v>45807</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11178,7 +11193,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11221,7 +11236,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 37622-2024</t>
+          <t>A 1847-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11235,10 +11250,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45541</v>
+        <v>45671</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11251,7 +11266,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11294,7 +11309,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 2708-2023</t>
+          <t>A 5754-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11308,10 +11323,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44942</v>
+        <v>45694</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11324,7 +11339,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11367,7 +11382,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 57220-2024</t>
+          <t>A 59012-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11381,10 +11396,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45629</v>
+        <v>45636</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11397,7 +11412,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11440,7 +11455,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 2990-2022</t>
+          <t>A 30260-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11454,10 +11469,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44581</v>
+        <v>45827</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11470,7 +11485,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11513,7 +11528,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 2994-2022</t>
+          <t>A 2-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11527,10 +11542,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44581</v>
+        <v>44927</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11543,7 +11558,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11586,7 +11601,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 53416-2023</t>
+          <t>A 20259-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11600,10 +11615,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45229</v>
+        <v>46139</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11616,7 +11631,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11659,7 +11674,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 29698-2024</t>
+          <t>A 32982-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11669,14 +11684,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45484</v>
+        <v>45839</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11688,8 +11703,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11732,7 +11752,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 5753-2025</t>
+          <t>A 32410-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11746,10 +11766,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45694</v>
+        <v>45838</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11762,7 +11782,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11805,7 +11825,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 64374-2023</t>
+          <t>A 17473-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11819,10 +11839,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45280</v>
+        <v>45757</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11835,7 +11855,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11878,7 +11898,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 23786-2022</t>
+          <t>A 35449-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11892,10 +11912,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44722</v>
+        <v>45531</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11908,7 +11928,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11951,7 +11971,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 26270-2022</t>
+          <t>A 34402-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11965,10 +11985,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44735</v>
+        <v>44792</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11981,7 +12001,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12024,7 +12044,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 45599-2023</t>
+          <t>A 12252-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12038,10 +12058,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45194</v>
+        <v>45378</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12054,7 +12074,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12097,7 +12117,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 31032-2024</t>
+          <t>A 24247-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12111,10 +12131,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45501</v>
+        <v>45797</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12127,7 +12147,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12170,7 +12190,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 31033-2024</t>
+          <t>A 43194-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12184,10 +12204,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45501</v>
+        <v>45910</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12200,7 +12220,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12243,7 +12263,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 59944-2024</t>
+          <t>A 33475-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12257,10 +12277,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45642</v>
+        <v>45519</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12273,7 +12293,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12316,7 +12336,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 666-2023</t>
+          <t>A 2990-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12330,10 +12350,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44930</v>
+        <v>44581</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12346,7 +12366,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12389,7 +12409,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 56641-2023</t>
+          <t>A 2994-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12403,10 +12423,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45243</v>
+        <v>44581</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12419,7 +12439,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12462,7 +12482,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 17635-2022</t>
+          <t>A 26910-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12476,10 +12496,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44680</v>
+        <v>45811</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12492,7 +12512,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12535,7 +12555,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59012-2024</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12549,10 +12569,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45636</v>
+        <v>44489</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12565,7 +12585,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12608,7 +12628,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 26263-2023</t>
+          <t>A 249-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12622,10 +12642,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45091</v>
+        <v>44565</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12638,7 +12658,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12681,7 +12701,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36305-2022</t>
+          <t>A 39055-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12695,10 +12715,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44803</v>
+        <v>45548</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12710,8 +12730,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12754,7 +12779,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36971-2024</t>
+          <t>A 22226-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12768,10 +12793,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45538</v>
+        <v>46150</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12784,7 +12809,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>17.9</v>
+        <v>2.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12827,7 +12852,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 11558-2025</t>
+          <t>A 52438-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12841,10 +12866,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45727</v>
+        <v>44874</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12857,7 +12882,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12900,7 +12925,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 17816-2023</t>
+          <t>A 14143-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12914,10 +12939,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45037</v>
+        <v>45392</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12930,7 +12955,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12973,7 +12998,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 8910-2025</t>
+          <t>A 17806-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12987,10 +13012,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45713</v>
+        <v>45037</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13003,7 +13028,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13046,7 +13071,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 8916-2025</t>
+          <t>A 29615-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13060,10 +13085,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45713</v>
+        <v>44754</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13075,8 +13100,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13119,7 +13149,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 15962-2025</t>
+          <t>A 59944-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13133,10 +13163,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45749</v>
+        <v>45642</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13149,7 +13179,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13192,7 +13222,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 33566-2024</t>
+          <t>A 59503-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13206,10 +13236,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45520</v>
+        <v>44907</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13222,7 +13252,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13265,7 +13295,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 35084-2024</t>
+          <t>A 30599-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13279,10 +13309,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45527</v>
+        <v>45112</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13295,7 +13325,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.6</v>
+        <v>10.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13338,7 +13368,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18948-2024</t>
+          <t>A 64518-2021</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13352,10 +13382,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45427</v>
+        <v>44511</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13368,7 +13398,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13411,7 +13441,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 36795-2024</t>
+          <t>A 7822-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13425,10 +13455,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45538</v>
+        <v>45349</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13441,7 +13471,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>9.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13484,7 +13514,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 45591-2023</t>
+          <t>A 8541-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13498,10 +13528,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45194</v>
+        <v>45709</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13514,7 +13544,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13557,7 +13587,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 12252-2024</t>
+          <t>A 64193-2021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13571,10 +13601,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45378</v>
+        <v>44510</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13587,7 +13617,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13630,7 +13660,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 22566-2025</t>
+          <t>A 24262-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13644,10 +13674,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45789</v>
+        <v>45797</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13703,7 +13733,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 41526-2023</t>
+          <t>A 23327-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13717,10 +13747,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45175</v>
+        <v>46162</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13732,13 +13762,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13781,7 +13806,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 7586-2025</t>
+          <t>A 38760-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13795,10 +13820,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45705</v>
+        <v>45163</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13811,7 +13836,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13854,7 +13879,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 46117-2022</t>
+          <t>A 25409-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13868,10 +13893,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44847</v>
+        <v>45463</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13883,8 +13908,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13927,7 +13957,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 242-2024</t>
+          <t>A 14651-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13941,10 +13971,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45294</v>
+        <v>45397</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13956,13 +13986,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14005,7 +14030,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 59503-2022</t>
+          <t>A 36971-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14019,10 +14044,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44907</v>
+        <v>45538</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14035,7 +14060,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>17.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14078,7 +14103,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 29615-2022</t>
+          <t>A 10910-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14092,10 +14117,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44754</v>
+        <v>44991</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14107,13 +14132,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14156,7 +14176,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 59200-2023</t>
+          <t>A 35084-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14170,10 +14190,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45253</v>
+        <v>45527</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14186,7 +14206,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14229,7 +14249,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 10634-2024</t>
+          <t>A 24640-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14243,10 +14263,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45367</v>
+        <v>46171</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14259,7 +14279,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14302,7 +14322,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34402-2022</t>
+          <t>A 44660-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14316,10 +14336,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44792</v>
+        <v>45574</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14332,7 +14352,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14375,7 +14395,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 11929-2023</t>
+          <t>A 44666-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14389,10 +14409,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44995</v>
+        <v>45574</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14405,7 +14425,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14448,7 +14468,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 18336-2023</t>
+          <t>A 25435-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14462,10 +14482,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45041</v>
+        <v>45463</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14479,11 +14499,11 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14526,7 +14546,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 61210-2023</t>
+          <t>A 11929-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14540,10 +14560,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45264</v>
+        <v>44995</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14556,7 +14576,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>7.7</v>
+        <v>2.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14599,7 +14619,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 17946-2024</t>
+          <t>A 14732-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14613,10 +14633,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45419</v>
+        <v>44655</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14629,7 +14649,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14672,7 +14692,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 30260-2025</t>
+          <t>A 8911-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14686,10 +14706,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45827</v>
+        <v>45713</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14702,7 +14722,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14745,7 +14765,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 59871-2024</t>
+          <t>A 18049-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14759,10 +14779,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45640</v>
+        <v>45420</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14775,7 +14795,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14818,7 +14838,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 2314-2022</t>
+          <t>A 29698-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14828,14 +14848,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44578</v>
+        <v>45484</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14848,7 +14868,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14891,7 +14911,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 35611-2024</t>
+          <t>A 45672-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14905,10 +14925,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45531</v>
+        <v>45579</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14921,7 +14941,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14964,7 +14984,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 31032-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14978,10 +14998,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44489</v>
+        <v>45501</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14994,7 +15014,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15037,7 +15057,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 72073-2021</t>
+          <t>A 31033-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15051,10 +15071,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44544</v>
+        <v>45501</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15067,7 +15087,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>9.6</v>
+        <v>1.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15110,7 +15130,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 10910-2023</t>
+          <t>A 50461-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15124,10 +15144,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44991</v>
+        <v>45601</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15183,7 +15203,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 12652-2024</t>
+          <t>A 18948-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15197,10 +15217,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45384</v>
+        <v>45427</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15213,7 +15233,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15256,7 +15276,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 27792-2023</t>
+          <t>A 27638-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15266,14 +15286,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45098</v>
+        <v>46190</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15285,8 +15305,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15329,7 +15354,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 32982-2025</t>
+          <t>A 49604-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15343,10 +15368,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45839</v>
+        <v>45207</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15358,13 +15383,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15407,7 +15427,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 16596-2023</t>
+          <t>A 59938-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15421,10 +15441,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45030</v>
+        <v>45642</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15437,7 +15457,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15480,7 +15500,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 32410-2025</t>
+          <t>A 71728-2021</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15494,10 +15514,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45838</v>
+        <v>44543</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15510,7 +15530,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15553,7 +15573,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 60201-2024</t>
+          <t>A 7368-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15567,10 +15587,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45642</v>
+        <v>45704</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15583,7 +15603,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15626,7 +15646,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 20476-2024</t>
+          <t>A 23786-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15640,10 +15660,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45435</v>
+        <v>44722</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15656,7 +15676,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>7.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15699,7 +15719,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 5758-2025</t>
+          <t>A 21032-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15713,10 +15733,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45694</v>
+        <v>45061</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15729,7 +15749,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15772,7 +15792,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 38760-2023</t>
+          <t>A 55306-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15786,10 +15806,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45163</v>
+        <v>45621</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15802,7 +15822,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15845,7 +15865,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 17473-2025</t>
+          <t>A 26270-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15859,10 +15879,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45757</v>
+        <v>44735</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15875,7 +15895,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15918,7 +15938,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 25435-2024</t>
+          <t>A 57386-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15932,10 +15952,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45463</v>
+        <v>45629</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15947,13 +15967,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15996,7 +16011,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 32839-2023</t>
+          <t>A 60201-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16010,10 +16025,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45109</v>
+        <v>45642</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16069,7 +16084,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34408-2024</t>
+          <t>A 65007-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16079,14 +16094,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45525</v>
+        <v>45287</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16099,7 +16114,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.4</v>
+        <v>14.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16142,7 +16157,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 2688-2023</t>
+          <t>A 64140-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16156,10 +16171,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44942</v>
+        <v>45279</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16172,7 +16187,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16215,7 +16230,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 35449-2024</t>
+          <t>A 28195-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16229,10 +16244,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45531</v>
+        <v>44746</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16244,8 +16259,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16288,7 +16308,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 34408-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16298,14 +16318,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44489</v>
+        <v>45525</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16318,7 +16338,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16361,7 +16381,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 17806-2023</t>
+          <t>A 12280-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16375,10 +16395,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45037</v>
+        <v>45378</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16391,7 +16411,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16434,7 +16454,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 15721-2024</t>
+          <t>A 18117-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16448,10 +16468,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45404</v>
+        <v>45761</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16464,7 +16484,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16507,7 +16527,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 43285-2024</t>
+          <t>A 6687-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16521,10 +16541,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45568</v>
+        <v>44966</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16537,7 +16557,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16580,7 +16600,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 6687-2023</t>
+          <t>A 73251-2021</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16594,10 +16614,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44966</v>
+        <v>44550</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16653,7 +16673,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 64193-2021</t>
+          <t>A 56641-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16667,10 +16687,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44510</v>
+        <v>45243</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16683,7 +16703,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16726,7 +16746,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 48427-2025</t>
+          <t>A 61229-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16740,10 +16760,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45934</v>
+        <v>44915</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16756,7 +16776,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16799,7 +16819,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 59064-2023</t>
+          <t>A 17635-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16813,10 +16833,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45252</v>
+        <v>44680</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16829,7 +16849,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16868,31 +16888,11 @@
         <v>0</v>
       </c>
       <c r="V214" s="2" t="inlineStr"/>
-      <c r="Z214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AA214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AB214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AC214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AD214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 52621-2025</t>
+          <t>A 36296-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16906,10 +16906,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45953</v>
+        <v>44803</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16965,7 +16965,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 52622-2025</t>
+          <t>A 2077-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16979,10 +16979,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45953</v>
+        <v>45309</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17038,7 +17038,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 52697-2025</t>
+          <t>A 61210-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17052,10 +17052,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45956</v>
+        <v>45264</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.8</v>
+        <v>7.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17111,7 +17111,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 15472-2025</t>
+          <t>A 57151-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17125,10 +17125,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45747</v>
+        <v>45245</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17184,7 +17184,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 53839-2025</t>
+          <t>A 10476-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17198,10 +17198,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45961</v>
+        <v>45720</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17213,8 +17213,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17257,7 +17262,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 53841-2025</t>
+          <t>A 41526-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17271,10 +17276,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45961</v>
+        <v>45175</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17286,8 +17291,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17330,7 +17340,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 54593-2025</t>
+          <t>A 31621-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17344,10 +17354,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45965</v>
+        <v>44775</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17360,7 +17370,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17403,7 +17413,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 47786-2025</t>
+          <t>A 2314-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17417,10 +17427,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45931</v>
+        <v>44578</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17433,7 +17443,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17476,7 +17486,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 47801-2025</t>
+          <t>A 46998-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17490,10 +17500,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45931</v>
+        <v>45586</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17506,7 +17516,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17549,7 +17559,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 47704-2025</t>
+          <t>A 2263-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17563,10 +17573,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45931</v>
+        <v>44941</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17579,7 +17589,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17622,7 +17632,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 47722-2025</t>
+          <t>A 38499-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17636,10 +17646,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45931</v>
+        <v>46282</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17652,7 +17662,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17695,7 +17705,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 47798-2025</t>
+          <t>A 38494-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17709,10 +17719,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45931</v>
+        <v>46282</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17725,7 +17735,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17768,7 +17778,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 47804-2025</t>
+          <t>A 38489-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17782,10 +17792,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45931</v>
+        <v>46282</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17798,7 +17808,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17841,7 +17851,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 47784-2025</t>
+          <t>A 34846-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17855,10 +17865,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45931</v>
+        <v>46258</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17914,7 +17924,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 57011-2025</t>
+          <t>A 50252-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17928,10 +17938,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45978</v>
+        <v>45600</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17943,13 +17953,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17992,7 +17997,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 56957-2025</t>
+          <t>A 4832-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18002,14 +18007,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45978</v>
+        <v>44592</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18021,13 +18026,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18070,7 +18070,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 61436-2025</t>
+          <t>A 38517-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18084,10 +18084,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46001</v>
+        <v>46283</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18099,8 +18099,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18143,7 +18148,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 63811-2025</t>
+          <t>A 33037-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18157,10 +18162,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46020</v>
+        <v>46245</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18173,7 +18178,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18216,7 +18221,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 3174-2026</t>
+          <t>A 38835-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18230,10 +18235,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46041</v>
+        <v>45547</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18246,7 +18251,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18289,7 +18294,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 969-2022</t>
+          <t>A 59871-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18303,10 +18308,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44571</v>
+        <v>45640</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18319,7 +18324,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18362,7 +18367,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 13504-2026</t>
+          <t>A 33233-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18376,10 +18381,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46094</v>
+        <v>46246</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18392,7 +18397,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18435,7 +18440,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 14036-2026</t>
+          <t>A 2309-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18449,10 +18454,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46098</v>
+        <v>45310</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18508,7 +18513,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 16585-2026</t>
+          <t>A 33266-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18522,10 +18527,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46112</v>
+        <v>46246</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18538,7 +18543,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18581,7 +18586,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 18101-2026</t>
+          <t>A 2306-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18595,10 +18600,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46125</v>
+        <v>45310</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18611,7 +18616,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18654,7 +18659,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 18096-2026</t>
+          <t>A 59200-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18668,10 +18673,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46125</v>
+        <v>45253</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18684,7 +18689,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18727,7 +18732,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 1847-2025</t>
+          <t>A 3851-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18741,10 +18746,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45671</v>
+        <v>45683</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18757,7 +18762,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18800,7 +18805,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 20259-2026</t>
+          <t>A 26263-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18814,10 +18819,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46139</v>
+        <v>45091</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18873,7 +18878,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 58244-2025</t>
+          <t>A 44646-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18887,10 +18892,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45985</v>
+        <v>45574</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18903,7 +18908,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18946,7 +18951,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 24247-2025</t>
+          <t>A 36305-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18960,10 +18965,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45797</v>
+        <v>44803</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18976,7 +18981,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19019,7 +19024,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 20184-2026</t>
+          <t>A 10374-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19033,10 +19038,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46139</v>
+        <v>44623</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19049,7 +19054,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19092,7 +19097,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 26438-2025</t>
+          <t>A 4069-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19106,10 +19111,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45807</v>
+        <v>45684</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19121,8 +19126,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19165,7 +19175,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 26910-2025</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19179,10 +19189,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45811</v>
+        <v>44489</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19195,7 +19205,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19238,7 +19248,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 33475-2024</t>
+          <t>A 27792-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19252,10 +19262,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45519</v>
+        <v>45098</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19268,7 +19278,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19311,7 +19321,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 43194-2025</t>
+          <t>A 32839-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19325,10 +19335,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45910</v>
+        <v>45109</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19384,7 +19394,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 22226-2026</t>
+          <t>A 53956-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19398,10 +19408,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46150</v>
+        <v>45616</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19414,7 +19424,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19457,7 +19467,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 8541-2025</t>
+          <t>A 17816-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19471,10 +19481,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45709</v>
+        <v>45037</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19487,7 +19497,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19530,7 +19540,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 7822-2024</t>
+          <t>A 33566-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19544,10 +19554,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45349</v>
+        <v>45520</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19560,7 +19570,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19603,7 +19613,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 24262-2025</t>
+          <t>A 16596-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19617,10 +19627,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45797</v>
+        <v>45030</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19633,7 +19643,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19676,7 +19686,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 23327-2026</t>
+          <t>A 43285-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19690,10 +19700,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46162</v>
+        <v>45568</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19706,7 +19716,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19749,7 +19759,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 24640-2026</t>
+          <t>A 64374-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19763,10 +19773,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46171</v>
+        <v>45280</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19779,7 +19789,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19822,7 +19832,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 27638-2026</t>
+          <t>A 59061-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19832,14 +19842,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46190</v>
+        <v>45252</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19851,13 +19861,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I255" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19900,7 +19905,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 71728-2021</t>
+          <t>A 30951-2022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19914,10 +19919,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>44543</v>
+        <v>44768</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19930,7 +19935,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19973,7 +19978,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 34846-2026</t>
+          <t>A 5758-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19987,10 +19992,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46258</v>
+        <v>45694</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20046,7 +20051,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 38499-2026</t>
+          <t>A 5753-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20060,10 +20065,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46282</v>
+        <v>45694</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20076,7 +20081,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20119,7 +20124,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 38494-2026</t>
+          <t>A 15962-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20133,10 +20138,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46282</v>
+        <v>45749</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20149,7 +20154,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20192,7 +20197,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 38489-2026</t>
+          <t>A 37622-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20206,10 +20211,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46282</v>
+        <v>45541</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20222,7 +20227,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20265,7 +20270,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 38517-2026</t>
+          <t>A 22008-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20279,10 +20284,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46283</v>
+        <v>45784</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20294,13 +20299,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I261" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 33266-2026</t>
+          <t>A 14954-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20357,10 +20357,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46246</v>
+        <v>45398</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20416,7 +20416,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 33037-2026</t>
+          <t>A 65002-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20430,10 +20430,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>46245</v>
+        <v>45287</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>5.4</v>
+        <v>6.9</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20489,7 +20489,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 33233-2026</t>
+          <t>A 57220-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20503,10 +20503,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>46246</v>
+        <v>45629</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20579,7 +20579,7 @@
         <v>44755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45569</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45266</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45266</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45476</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45476</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45499</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46037</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45093</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44809</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45544</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45907</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45531</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>45232</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>44893</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>45230</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44936</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>45078</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45371</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>44914</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45558</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44847</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44474</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44482</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44846</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44511</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44581</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44572</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44483</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44511</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44820</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44474</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44589</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45378</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44927</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45397</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44847</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44847</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45252</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>46001</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45501</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>45243</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>46020</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45538</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>45037</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45749</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>46041</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>45747</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44571</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45194</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45705</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>45727</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45294</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44754</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45264</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45419</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>45531</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>45538</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45931</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>45931</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>45194</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>45931</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>45931</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45931</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45931</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45163</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45934</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>45037</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45568</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45789</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44966</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>44510</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>45252</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>45953</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>45953</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45547</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45683</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>45956</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45961</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45961</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45965</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45548</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45279</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>46094</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45271</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>45720</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>45310</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>46098</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44657</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45978</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>45287</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>46112</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>45978</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>45420</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>44825</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>46125</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>45827</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>46125</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44768</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45579</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>45309</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>45271</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45671</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45839</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>46139</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45112</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45838</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45985</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>45797</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45245</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45757</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>46139</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45531</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>44942</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>44581</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>44581</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45807</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45694</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45280</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45811</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45642</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>44680</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45519</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45910</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45527</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45427</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45378</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45175</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>44847</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>46150</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>44995</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45640</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>44578</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44489</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45709</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45349</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45797</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>44991</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>45384</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45098</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45642</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>46162</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45435</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45109</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45525</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44942</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>46171</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45404</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44489</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44550</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45399</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45399</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44623</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45378</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44959</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45694</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45629</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45378</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45548</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45061</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>44896</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>46190</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44481</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45586</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45287</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>44927</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44592</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45271</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44543</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45166</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>44511</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>45463</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44941</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45601</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>44915</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45582</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>45684</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45574</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45574</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>45436</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>44874</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45600</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45761</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>44587</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45621</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45541</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45541</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45229</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45484</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>44722</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>46258</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>46282</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44930</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45636</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45091</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>46282</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>46282</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45713</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45713</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45520</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>46246</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>46245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>46246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>44907</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45253</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45367</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44792</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45041</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>44544</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45030</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45694</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45463</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45448</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>45704</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45392</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>44655</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45367</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>44487</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>45310</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>45397</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44803</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44964</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45713</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45436</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45574</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45642</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45616</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44775</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45207</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>44565</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44746</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45398</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45287</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>45784</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45629</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45569</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45266</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45266</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45476</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45476</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45499</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46037</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45093</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44809</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45544</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45907</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45531</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>45232</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>44893</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>45230</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44936</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>45078</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45371</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>44914</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45558</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44847</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44474</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44482</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44846</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44511</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44581</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44572</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44483</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44511</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44820</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44474</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44589</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44811</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45378</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44927</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45397</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44847</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44847</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45252</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>46001</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45501</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>45243</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>46020</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45538</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>45037</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45749</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>46041</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>45747</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44571</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45194</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45705</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>45727</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45294</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44754</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45264</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45419</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>45531</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>45538</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45931</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>45931</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>45194</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>45931</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>45931</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45931</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45931</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45163</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45934</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>45037</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45568</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45789</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44966</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>44510</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>45252</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>45953</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>45953</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45547</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45683</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>45956</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45961</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45961</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45965</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45548</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45279</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>46094</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45271</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>45720</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>45310</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>46098</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44657</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45978</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>45287</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>46112</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>45978</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>45420</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>44825</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>46125</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>45827</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>46125</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44768</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45579</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>45309</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>45271</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45671</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45839</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>46139</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45112</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45838</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45985</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>45797</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45245</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45757</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>46139</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45531</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>44942</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>44581</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>44581</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45807</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45694</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45280</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45811</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45642</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>44680</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45519</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45910</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45527</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45427</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45378</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45175</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>44847</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>46150</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>44995</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45640</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>44578</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44489</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45709</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45349</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45797</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>44991</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>45384</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45098</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45642</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>46162</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45435</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45109</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45525</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44942</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>46171</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45404</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44489</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44550</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45399</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45399</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44623</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45378</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44959</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45694</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45629</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45378</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45548</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45061</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>44896</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>46190</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44481</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45586</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45287</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>44927</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44592</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45271</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44543</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45166</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>44511</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>45463</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44941</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45601</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>44915</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45582</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>45684</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45574</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45574</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>45436</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>44874</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45600</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45761</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>44587</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45621</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45541</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45541</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45229</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45484</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>44722</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>46258</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>46282</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44930</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45636</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45091</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>46282</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>46282</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45713</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45713</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45520</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>46246</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>46245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>46246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>44907</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45253</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45367</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44792</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45041</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>44544</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45030</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45694</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45463</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45448</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>45704</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45392</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>44655</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45367</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>44487</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>45310</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>45397</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44803</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44964</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45713</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45436</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45574</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45642</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45616</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44775</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45207</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>44565</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44746</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45398</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45287</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>45784</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45629</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45569</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45266</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45266</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45476</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45476</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45499</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46037</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 37408-2022</t>
+          <t>A 26849-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44809</v>
+        <v>45093</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -881,153 +881,153 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Gullklöver
+Skogsklocka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 26849-2023 artfynd.xlsx", "A 26849-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 26849-2023 karta.png", "A 26849-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 26849-2023 georefererad karta.tif", "A 26849-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 26849-2023 FSC-klagomål.docx", "A 26849-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 26849-2023 FSC-klagomål mail.docx", "A 26849-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 26849-2023 tillsynsbegäran.docx", "A 26849-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 26849-2023 tillsynsbegäran mail.docx", "A 26849-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 37408-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44809</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tjäder</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 37408-2022 artfynd.xlsx", "A 37408-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 37408-2022 karta.png", "A 37408-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 37408-2022 georefererad karta.tif", "A 37408-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 37408-2022 FSC-klagomål.docx", "A 37408-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 37408-2022 FSC-klagomål mail.docx", "A 37408-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 37408-2022 tillsynsbegäran.docx", "A 37408-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 37408-2022 tillsynsbegäran mail.docx", "A 37408-2022")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 37408-2022 prioriterade fågelarter.docx", "A 37408-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 26849-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45093</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Gullklöver
-Skogsklocka</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 26849-2023 artfynd.xlsx", "A 26849-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 26849-2023 karta.png", "A 26849-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 26849-2023 georefererad karta.tif", "A 26849-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 26849-2023 FSC-klagomål.docx", "A 26849-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 26849-2023 FSC-klagomål mail.docx", "A 26849-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 26849-2023 tillsynsbegäran.docx", "A 26849-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 26849-2023 tillsynsbegäran mail.docx", "A 26849-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44484</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23794-2023</t>
+          <t>A 38039-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45078</v>
+        <v>45544</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1412,46 +1412,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 54177-2023</t>
+          <t>A 8909-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45232</v>
+        <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1481,17 +1481,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>22.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1514,154 +1514,154 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 54177-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45232</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Strutbräken</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 54177-2023 artfynd.xlsx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 54177-2023 karta.png", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 54177-2023 georefererad karta.tif", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 54177-2023 FSC-klagomål.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 54177-2023 FSC-klagomål mail.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 54177-2023 tillsynsbegäran.docx", "A 54177-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 54177-2023 tillsynsbegäran mail.docx", "A 54177-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 53498-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45230</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1320-2023</t>
+          <t>A 56642-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44936</v>
+        <v>44893</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1690,14 +1690,19 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1731,35 +1736,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
     </row>
@@ -1783,7 +1788,7 @@
         <v>45907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 35453-2024</t>
+          <t>A 53498-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1890,10 +1895,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45531</v>
+        <v>45230</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1906,20 +1911,20 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -1930,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1946,46 +1951,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40853-2024</t>
+          <t>A 1320-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1999,10 +2000,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45558</v>
+        <v>44936</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2015,7 +2016,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2051,46 +2052,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 62010-2022</t>
+          <t>A 23794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2104,10 +2105,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44914</v>
+        <v>45078</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2120,13 +2121,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2156,39 +2157,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2212,7 +2213,7 @@
         <v>45371</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2305,7 +2306,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8909-2025</t>
+          <t>A 62010-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2319,10 +2320,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45713</v>
+        <v>44914</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2335,16 +2336,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>22.6</v>
+        <v>7.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2359,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2368,49 +2369,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 56642-2022</t>
+          <t>A 40853-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2424,10 +2425,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44893</v>
+        <v>45558</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2439,19 +2440,14 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2481,46 +2477,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38039-2024</t>
+          <t>A 35453-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2534,10 +2530,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45544</v>
+        <v>45531</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2553,10 +2549,10 @@
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2590,35 +2586,39 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
         <v/>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44847</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44482</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44846</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44511</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44581</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44636</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44538</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44517</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44589</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44483</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44511</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44517</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44820</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>44589</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44511</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44502</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4445-2022</t>
+          <t>A 66809-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44589</v>
+        <v>44522</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>13.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57065-2021</t>
+          <t>A 48787-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44482</v>
+        <v>44859</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 65891-2021</t>
+          <t>A 73022-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44517</v>
+        <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 66809-2021</t>
+          <t>A 33907-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44522</v>
+        <v>44790</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4776,8 +4776,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>13.7</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4820,7 +4825,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 5754-2025</t>
+          <t>A 4445-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4834,10 +4839,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45694</v>
+        <v>44589</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4850,7 +4855,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4893,7 +4898,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59012-2024</t>
+          <t>A 57065-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4907,10 +4912,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45636</v>
+        <v>44482</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4923,7 +4928,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4966,7 +4971,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2-2023</t>
+          <t>A 37962-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4976,14 +4981,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44927</v>
+        <v>44811</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4996,7 +5001,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5039,7 +5044,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48787-2022</t>
+          <t>A 56762-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5053,10 +5058,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44859</v>
+        <v>44481</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5069,7 +5074,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5112,7 +5117,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 53416-2023</t>
+          <t>A 65891-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5126,10 +5131,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45229</v>
+        <v>44517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5142,7 +5147,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5185,7 +5190,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 34402-2022</t>
+          <t>A 12280-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5199,10 +5204,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44792</v>
+        <v>45378</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5215,7 +5220,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5258,7 +5263,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 73022-2021</t>
+          <t>A 59061-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5272,10 +5277,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44550</v>
+        <v>45252</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5288,7 +5293,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5331,7 +5336,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37962-2022</t>
+          <t>A 3-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5341,14 +5346,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44811</v>
+        <v>44927</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5361,7 +5366,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5404,7 +5409,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56762-2021</t>
+          <t>A 46288-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5418,10 +5423,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44481</v>
+        <v>44847</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5434,7 +5439,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5477,7 +5482,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 5753-2025</t>
+          <t>A 46290-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5491,10 +5496,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45694</v>
+        <v>44847</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5507,7 +5512,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5550,7 +5555,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33907-2022</t>
+          <t>A 14651-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5564,10 +5569,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44790</v>
+        <v>45397</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5579,13 +5584,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 62807-2023</t>
+          <t>A 26270-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45271</v>
+        <v>44735</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12252-2024</t>
+          <t>A 31032-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45378</v>
+        <v>45501</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5774,7 +5774,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15962-2025</t>
+          <t>A 31033-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45749</v>
+        <v>45501</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5847,7 +5847,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37622-2024</t>
+          <t>A 56641-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45541</v>
+        <v>45243</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5920,7 +5920,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14675-2024</t>
+          <t>A 36971-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45397</v>
+        <v>45538</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>8.199999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5993,7 +5993,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 17816-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44489</v>
+        <v>45037</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2990-2022</t>
+          <t>A 36305-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44581</v>
+        <v>44803</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2994-2022</t>
+          <t>A 15962-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44581</v>
+        <v>45749</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22008-2025</t>
+          <t>A 7586-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6226,10 +6226,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45784</v>
+        <v>45705</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14954-2024</t>
+          <t>A 242-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45398</v>
+        <v>45294</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6314,8 +6314,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.7</v>
+        <v>8.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6358,7 +6363,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 65002-2023</t>
+          <t>A 29615-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6372,10 +6377,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45287</v>
+        <v>44754</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6387,8 +6392,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>6.9</v>
+        <v>3.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6431,7 +6441,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 41074-2022</t>
+          <t>A 61210-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6445,10 +6455,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44825</v>
+        <v>45264</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6461,7 +6471,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>7.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6521,7 +6531,7 @@
         <v>45419</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6577,689 +6587,689 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
+          <t>A 35611-2024</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>45531</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A 38760-2023</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A 17806-2023</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>45037</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A 43285-2024</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A 32982-2025</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A 32410-2025</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>A 6687-2023</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>44966</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>A 64193-2021</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>44510</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>A 59064-2023</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="n">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="n">
         <v>45252</v>
       </c>
-      <c r="E75" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
+      <c r="E83" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
         <v>1.1</v>
       </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" s="2" t="inlineStr"/>
-      <c r="Z75">
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="Z83">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AA75">
+      <c r="AA83">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AB75">
+      <c r="AB83">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AC75">
+      <c r="AC83">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
         <v/>
       </c>
-      <c r="AD75">
+      <c r="AD83">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>A 46117-2022</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="n">
-        <v>44847</v>
-      </c>
-      <c r="E76" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>A 57220-2024</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="n">
-        <v>45629</v>
-      </c>
-      <c r="E77" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>A 249-2022</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="n">
-        <v>44565</v>
-      </c>
-      <c r="E78" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>A 12652-2024</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="n">
-        <v>45384</v>
-      </c>
-      <c r="E79" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>A 14984-2024</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="n">
-        <v>45399</v>
-      </c>
-      <c r="E80" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>A 14987-2024</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="n">
-        <v>45399</v>
-      </c>
-      <c r="E81" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>A 39055-2024</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="n">
-        <v>45548</v>
-      </c>
-      <c r="E82" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>A 52438-2022</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="n">
-        <v>44874</v>
-      </c>
-      <c r="E83" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" s="2" t="inlineStr"/>
-    </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46288-2022</t>
+          <t>A 38835-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7273,10 +7283,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44847</v>
+        <v>45547</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7289,7 +7299,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7332,7 +7342,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46290-2022</t>
+          <t>A 3851-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7346,10 +7356,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44847</v>
+        <v>45683</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7362,7 +7372,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.300000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7405,7 +7415,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3-2023</t>
+          <t>A 17473-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7419,10 +7429,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44927</v>
+        <v>45757</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7435,7 +7445,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7478,7 +7488,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 65008-2023</t>
+          <t>A 35449-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7492,10 +7502,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45287</v>
+        <v>45531</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7508,7 +7518,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7551,7 +7561,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 10635-2024</t>
+          <t>A 39039-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7565,10 +7575,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45367</v>
+        <v>45548</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7580,8 +7590,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7624,7 +7639,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14143-2024</t>
+          <t>A 64140-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7638,10 +7653,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45392</v>
+        <v>45279</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7654,7 +7669,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7697,7 +7712,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17806-2023</t>
+          <t>A 62669-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7711,10 +7726,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45037</v>
+        <v>45271</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7770,7 +7785,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 29615-2022</t>
+          <t>A 10476-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7784,10 +7799,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44754</v>
+        <v>45720</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7805,7 +7820,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7848,7 +7863,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 45599-2023</t>
+          <t>A 2309-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7862,10 +7877,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45194</v>
+        <v>45310</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7878,7 +7893,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7921,7 +7936,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11558-2025</t>
+          <t>A 15039-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7935,10 +7950,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45727</v>
+        <v>44657</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7951,7 +7966,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7994,7 +8009,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59944-2024</t>
+          <t>A 65007-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8008,10 +8023,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45642</v>
+        <v>45287</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8024,7 +8039,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>14.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8067,7 +8082,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59503-2022</t>
+          <t>A 15472-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8081,10 +8096,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44907</v>
+        <v>45747</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8097,7 +8112,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8140,7 +8155,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30599-2023</t>
+          <t>A 13504-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8154,10 +8169,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45112</v>
+        <v>46094</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8170,7 +8185,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>10.1</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8213,7 +8228,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15472-2025</t>
+          <t>A 18049-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8227,10 +8242,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45747</v>
+        <v>45420</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8243,7 +8258,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8286,7 +8301,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 64518-2021</t>
+          <t>A 41074-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8300,10 +8315,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44511</v>
+        <v>44825</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8316,7 +8331,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8359,7 +8374,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62667-2023</t>
+          <t>A 30951-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8373,10 +8388,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45271</v>
+        <v>44768</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8389,7 +8404,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8432,7 +8447,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 64193-2021</t>
+          <t>A 14036-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8446,10 +8461,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44510</v>
+        <v>46098</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8462,7 +8477,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8505,7 +8520,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 22566-2025</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8519,10 +8534,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45789</v>
+        <v>44489</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8535,7 +8550,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8578,7 +8593,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 45591-2023</t>
+          <t>A 45672-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8592,10 +8607,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45194</v>
+        <v>45579</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8608,7 +8623,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>11</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8651,7 +8666,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 36795-2024</t>
+          <t>A 2077-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8665,10 +8680,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45538</v>
+        <v>45309</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8681,7 +8696,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>9.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8724,7 +8739,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 38760-2023</t>
+          <t>A 62807-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8738,10 +8753,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45163</v>
+        <v>45271</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8754,7 +8769,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8797,7 +8812,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 242-2024</t>
+          <t>A 47786-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8811,10 +8826,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45294</v>
+        <v>45931</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8826,13 +8841,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>8.5</v>
+        <v>0.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8875,7 +8885,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 25409-2024</t>
+          <t>A 47801-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8889,10 +8899,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45463</v>
+        <v>45931</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8904,13 +8914,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8953,7 +8958,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14651-2024</t>
+          <t>A 47704-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8967,10 +8972,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45397</v>
+        <v>45931</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8983,7 +8988,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9026,7 +9031,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 36971-2024</t>
+          <t>A 47722-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9040,10 +9045,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45538</v>
+        <v>45931</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9056,7 +9061,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>17.9</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9099,7 +9104,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 35611-2024</t>
+          <t>A 47798-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9113,10 +9118,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45531</v>
+        <v>45931</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9129,7 +9134,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9172,7 +9177,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 10910-2023</t>
+          <t>A 47804-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9186,10 +9191,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44991</v>
+        <v>45931</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9202,7 +9207,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9245,7 +9250,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47798-2025</t>
+          <t>A 47784-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9262,7 +9267,7 @@
         <v>45931</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9275,7 +9280,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9318,7 +9323,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 47804-2025</t>
+          <t>A 48427-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9332,10 +9337,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45931</v>
+        <v>45934</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9348,7 +9353,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9391,7 +9396,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 47801-2025</t>
+          <t>A 30599-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9405,10 +9410,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45931</v>
+        <v>45112</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9421,7 +9426,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>10.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9464,7 +9469,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 47784-2025</t>
+          <t>A 57151-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9478,10 +9483,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45931</v>
+        <v>45245</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9494,7 +9499,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9537,7 +9542,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 47722-2025</t>
+          <t>A 16585-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9551,10 +9556,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45931</v>
+        <v>46112</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,7 +9572,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9610,7 +9615,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 47704-2025</t>
+          <t>A 52621-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9624,10 +9629,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45931</v>
+        <v>45953</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,7 +9645,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9683,7 +9688,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20745-2024</t>
+          <t>A 52622-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9697,10 +9702,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45436</v>
+        <v>45953</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9718,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9756,7 +9761,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 47786-2025</t>
+          <t>A 2708-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9770,10 +9775,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45931</v>
+        <v>44942</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,7 +9791,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9829,7 +9834,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35084-2024</t>
+          <t>A 52697-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9843,10 +9848,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45527</v>
+        <v>45956</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9859,7 +9864,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9902,7 +9907,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30260-2025</t>
+          <t>A 2990-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9916,10 +9921,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45827</v>
+        <v>44581</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,7 +9937,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9975,7 +9980,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 48427-2025</t>
+          <t>A 2994-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9989,10 +9994,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45934</v>
+        <v>44581</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10005,7 +10010,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10048,7 +10053,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 57967-2021</t>
+          <t>A 53839-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10062,10 +10067,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44487</v>
+        <v>45961</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10078,7 +10083,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10121,7 +10126,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 44660-2024</t>
+          <t>A 5753-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10135,10 +10140,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45574</v>
+        <v>45694</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10151,7 +10156,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10194,7 +10199,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 44666-2024</t>
+          <t>A 64374-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10208,10 +10213,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45574</v>
+        <v>45280</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10224,7 +10229,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10267,7 +10272,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 56765-2021</t>
+          <t>A 53841-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10281,10 +10286,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44481</v>
+        <v>45961</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10297,7 +10302,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10340,7 +10345,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 22798-2024</t>
+          <t>A 18101-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10354,10 +10359,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45448</v>
+        <v>46125</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10369,13 +10374,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10418,7 +10418,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 32982-2025</t>
+          <t>A 18096-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10432,10 +10432,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45839</v>
+        <v>46125</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10447,13 +10447,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10496,7 +10491,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32410-2025</t>
+          <t>A 54593-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10510,10 +10505,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45838</v>
+        <v>45965</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10526,7 +10521,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10569,7 +10564,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 25435-2024</t>
+          <t>A 59944-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10583,10 +10578,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45463</v>
+        <v>45642</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10598,13 +10593,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10647,7 +10637,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 666-2023</t>
+          <t>A 17635-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10661,10 +10651,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44930</v>
+        <v>44680</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10677,7 +10667,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10720,7 +10710,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 3996-2022</t>
+          <t>A 57011-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10734,10 +10724,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44587</v>
+        <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10749,8 +10739,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10793,7 +10788,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 11929-2023</t>
+          <t>A 35084-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10807,10 +10802,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44995</v>
+        <v>45527</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10823,7 +10818,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10866,7 +10861,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 20476-2024</t>
+          <t>A 18948-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10880,10 +10875,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45435</v>
+        <v>45427</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10896,7 +10891,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10939,7 +10934,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 52621-2025</t>
+          <t>A 56957-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10949,14 +10944,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45953</v>
+        <v>45978</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10968,8 +10963,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 52622-2025</t>
+          <t>A 12252-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11026,10 +11026,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45953</v>
+        <v>45378</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11085,7 +11085,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 14732-2022</t>
+          <t>A 41526-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11099,10 +11099,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44655</v>
+        <v>45175</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11114,8 +11114,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11158,7 +11163,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 17473-2025</t>
+          <t>A 1847-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11172,10 +11177,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45757</v>
+        <v>45671</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11188,7 +11193,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11231,7 +11236,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 52697-2025</t>
+          <t>A 20259-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11245,10 +11250,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45956</v>
+        <v>46139</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11261,7 +11266,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11304,7 +11309,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 8911-2025</t>
+          <t>A 58244-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11318,10 +11323,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45713</v>
+        <v>45985</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11334,7 +11339,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11377,7 +11382,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 35449-2024</t>
+          <t>A 46117-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11391,10 +11396,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45531</v>
+        <v>44847</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11407,7 +11412,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11450,7 +11455,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 18049-2024</t>
+          <t>A 24247-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11464,10 +11469,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45420</v>
+        <v>45797</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11480,7 +11485,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11523,7 +11528,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 57483-2022</t>
+          <t>A 11929-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11537,10 +11542,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44896</v>
+        <v>44995</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11552,13 +11557,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11601,7 +11601,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 53841-2025</t>
+          <t>A 61436-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11615,10 +11615,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45961</v>
+        <v>46001</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11674,7 +11674,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 29698-2024</t>
+          <t>A 59871-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11684,14 +11684,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45484</v>
+        <v>45640</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11747,7 +11747,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 53839-2025</t>
+          <t>A 2314-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45961</v>
+        <v>44578</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11820,7 +11820,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 45672-2024</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45579</v>
+        <v>44489</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11893,7 +11893,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31032-2024</t>
+          <t>A 10910-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11907,10 +11907,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45501</v>
+        <v>44991</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11966,7 +11966,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31033-2024</t>
+          <t>A 12652-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11980,10 +11980,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45501</v>
+        <v>45384</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12039,7 +12039,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 50461-2024</t>
+          <t>A 27792-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12053,10 +12053,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45601</v>
+        <v>45098</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12112,7 +12112,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 54593-2025</t>
+          <t>A 20184-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45965</v>
+        <v>46139</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12185,7 +12185,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 18948-2024</t>
+          <t>A 60201-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12199,10 +12199,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45427</v>
+        <v>45642</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12258,7 +12258,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37620-2024</t>
+          <t>A 63811-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12272,10 +12272,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45541</v>
+        <v>46020</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12331,7 +12331,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 15721-2024</t>
+          <t>A 20476-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45404</v>
+        <v>45435</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 2708-2023</t>
+          <t>A 26438-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12418,10 +12418,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44942</v>
+        <v>45807</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12477,7 +12477,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 10634-2024</t>
+          <t>A 32839-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12491,10 +12491,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45367</v>
+        <v>45109</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12550,7 +12550,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 39039-2024</t>
+          <t>A 34408-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12560,14 +12560,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45548</v>
+        <v>45525</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12579,13 +12579,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12628,7 +12623,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 46445-2024</t>
+          <t>A 2688-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12642,10 +12637,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45582</v>
+        <v>44942</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12658,7 +12653,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12701,7 +12696,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 49604-2023</t>
+          <t>A 3174-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12715,10 +12710,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45207</v>
+        <v>46041</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12731,7 +12726,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12774,7 +12769,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 59938-2024</t>
+          <t>A 26910-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12788,10 +12783,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45642</v>
+        <v>45811</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12804,7 +12799,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12847,7 +12842,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 12272-2024</t>
+          <t>A 969-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12861,10 +12856,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45378</v>
+        <v>44571</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12877,7 +12872,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12920,7 +12915,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 12281-2024</t>
+          <t>A 15721-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12934,10 +12929,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45378</v>
+        <v>45404</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12950,7 +12945,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12993,7 +12988,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 26438-2025</t>
+          <t>A 73251-2021</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13007,10 +13002,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45807</v>
+        <v>44550</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13023,7 +13018,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13066,7 +13061,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 7586-2025</t>
+          <t>A 14984-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13080,10 +13075,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45705</v>
+        <v>45399</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13096,7 +13091,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13139,7 +13134,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 1847-2025</t>
+          <t>A 14987-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13153,10 +13148,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45671</v>
+        <v>45399</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13169,7 +13164,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13212,7 +13207,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 20259-2026</t>
+          <t>A 33475-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13226,10 +13221,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46139</v>
+        <v>45519</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13242,7 +13237,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13285,7 +13280,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 57011-2025</t>
+          <t>A 10374-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13299,10 +13294,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45978</v>
+        <v>44623</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13314,13 +13309,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13363,7 +13353,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 2688-2023</t>
+          <t>A 12281-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13377,10 +13367,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44942</v>
+        <v>45378</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13393,7 +13383,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13436,7 +13426,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 24247-2025</t>
+          <t>A 5286-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13450,10 +13440,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45797</v>
+        <v>44959</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13466,7 +13456,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13509,7 +13499,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 43194-2025</t>
+          <t>A 5754-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13523,10 +13513,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45910</v>
+        <v>45694</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13539,7 +13529,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13582,7 +13572,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 33475-2024</t>
+          <t>A 57386-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13596,10 +13586,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45519</v>
+        <v>45629</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13612,7 +13602,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13655,7 +13645,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 7368-2025</t>
+          <t>A 12272-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13669,10 +13659,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45704</v>
+        <v>45378</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13685,7 +13675,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13728,7 +13718,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 26910-2025</t>
+          <t>A 39055-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13742,10 +13732,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45811</v>
+        <v>45548</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13757,8 +13747,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13801,7 +13796,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 23786-2022</t>
+          <t>A 21032-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13815,10 +13810,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44722</v>
+        <v>45061</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13831,7 +13826,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13874,7 +13869,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 62669-2023</t>
+          <t>A 57483-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13888,10 +13883,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45271</v>
+        <v>44896</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13903,8 +13898,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13947,7 +13947,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 15039-2022</t>
+          <t>A 56765-2021</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13961,10 +13961,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44657</v>
+        <v>44481</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14020,7 +14020,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 56957-2025</t>
+          <t>A 43194-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14030,14 +14030,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45978</v>
+        <v>45910</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14049,13 +14049,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14098,7 +14093,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 21032-2023</t>
+          <t>A 46998-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14112,10 +14107,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45061</v>
+        <v>45586</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14128,7 +14123,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14171,7 +14166,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 55306-2024</t>
+          <t>A 65008-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14185,10 +14180,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45621</v>
+        <v>45287</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14201,7 +14196,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14244,7 +14239,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 26270-2022</t>
+          <t>A 2-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14258,10 +14253,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44735</v>
+        <v>44927</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14274,7 +14269,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14317,7 +14312,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 22226-2026</t>
+          <t>A 4832-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14331,10 +14326,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46150</v>
+        <v>44592</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14347,7 +14342,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14390,7 +14385,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 57386-2024</t>
+          <t>A 62667-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14404,10 +14399,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45629</v>
+        <v>45271</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14420,7 +14415,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14463,7 +14458,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 5286-2023</t>
+          <t>A 39492-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14477,10 +14472,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44959</v>
+        <v>45166</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14492,8 +14487,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>5.3</v>
+        <v>24.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 7822-2024</t>
+          <t>A 22226-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14550,10 +14550,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45349</v>
+        <v>46150</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14609,7 +14609,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 8541-2025</t>
+          <t>A 64518-2021</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14623,10 +14623,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45709</v>
+        <v>44511</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14682,7 +14682,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 61436-2025</t>
+          <t>A 25409-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14696,10 +14696,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46001</v>
+        <v>45463</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14711,8 +14711,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14755,7 +14760,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 24262-2025</t>
+          <t>A 2263-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14769,10 +14774,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45797</v>
+        <v>44941</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14785,7 +14790,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14828,7 +14833,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 60201-2024</t>
+          <t>A 50461-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14842,10 +14847,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45642</v>
+        <v>45601</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14858,7 +14863,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14901,7 +14906,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 65007-2023</t>
+          <t>A 61229-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14915,10 +14920,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45287</v>
+        <v>44915</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14931,7 +14936,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>14.2</v>
+        <v>1.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14974,7 +14979,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 6015-2023</t>
+          <t>A 46445-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14988,10 +14993,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44964</v>
+        <v>45582</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15047,7 +15052,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 23327-2026</t>
+          <t>A 4069-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15061,10 +15066,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46162</v>
+        <v>45684</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15076,8 +15081,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15120,7 +15130,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 20743-2024</t>
+          <t>A 44660-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15134,10 +15144,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45436</v>
+        <v>45574</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15150,7 +15160,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15193,7 +15203,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 39492-2023</t>
+          <t>A 44666-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15207,10 +15217,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45166</v>
+        <v>45574</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15222,13 +15232,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>24.9</v>
+        <v>1.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15271,7 +15276,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 64140-2023</t>
+          <t>A 20745-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15285,10 +15290,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45279</v>
+        <v>45436</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15301,7 +15306,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15344,7 +15349,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 18336-2023</t>
+          <t>A 8541-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15358,10 +15363,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45041</v>
+        <v>45709</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15373,13 +15378,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 28195-2022</t>
+          <t>A 7822-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15436,10 +15436,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44746</v>
+        <v>45349</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15451,13 +15451,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15500,7 +15495,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 34408-2024</t>
+          <t>A 24262-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15510,14 +15505,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45525</v>
+        <v>45797</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15530,7 +15525,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15573,7 +15568,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 12280-2024</t>
+          <t>A 52438-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15587,10 +15582,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45378</v>
+        <v>44874</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15603,7 +15598,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15646,7 +15641,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 63811-2025</t>
+          <t>A 50252-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15660,10 +15655,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46020</v>
+        <v>45600</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15676,7 +15671,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15719,7 +15714,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 18117-2025</t>
+          <t>A 23327-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15733,10 +15728,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45761</v>
+        <v>46162</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15749,7 +15744,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15792,7 +15787,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 24640-2026</t>
+          <t>A 18117-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15806,10 +15801,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46171</v>
+        <v>45761</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15822,7 +15817,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15865,7 +15860,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 6687-2023</t>
+          <t>A 3996-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15879,10 +15874,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44966</v>
+        <v>44587</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15895,7 +15890,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15938,7 +15933,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 8910-2025</t>
+          <t>A 55306-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15952,10 +15947,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45713</v>
+        <v>45621</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15968,7 +15963,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16011,7 +16006,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 8916-2025</t>
+          <t>A 24640-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16025,10 +16020,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45713</v>
+        <v>46171</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16041,7 +16036,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16084,7 +16079,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 73251-2021</t>
+          <t>A 37620-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16098,10 +16093,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44550</v>
+        <v>45541</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16114,7 +16109,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16157,7 +16152,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 72073-2021</t>
+          <t>A 37622-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16171,10 +16166,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44544</v>
+        <v>45541</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16187,7 +16182,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>9.6</v>
+        <v>0.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16230,7 +16225,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 56641-2023</t>
+          <t>A 53416-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16244,10 +16239,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45243</v>
+        <v>45229</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16260,7 +16255,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16303,7 +16298,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 61229-2022</t>
+          <t>A 29698-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16313,14 +16308,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44915</v>
+        <v>45484</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16333,7 +16328,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16376,7 +16371,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 17635-2022</t>
+          <t>A 23786-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16390,10 +16385,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44680</v>
+        <v>44722</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16406,7 +16401,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16449,7 +16444,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 36296-2022</t>
+          <t>A 666-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16463,10 +16458,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44803</v>
+        <v>44930</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16479,7 +16474,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16522,7 +16517,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 2077-2024</t>
+          <t>A 59012-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16536,10 +16531,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45309</v>
+        <v>45636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16552,7 +16547,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16595,7 +16590,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 61210-2023</t>
+          <t>A 26263-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16609,10 +16604,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45264</v>
+        <v>45091</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16625,7 +16620,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16668,7 +16663,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 57151-2023</t>
+          <t>A 8910-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16682,10 +16677,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45245</v>
+        <v>45713</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16698,7 +16693,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16741,7 +16736,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 969-2022</t>
+          <t>A 8916-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16755,10 +16750,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44571</v>
+        <v>45713</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16771,7 +16766,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16814,7 +16809,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 3174-2026</t>
+          <t>A 33566-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16828,10 +16823,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46041</v>
+        <v>45520</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16844,7 +16839,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16887,7 +16882,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 10476-2025</t>
+          <t>A 27638-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16897,14 +16892,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45720</v>
+        <v>46190</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16922,7 +16917,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16965,7 +16960,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 41526-2023</t>
+          <t>A 59503-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16979,10 +16974,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45175</v>
+        <v>44907</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16994,13 +16989,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17043,7 +17033,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 27638-2026</t>
+          <t>A 59200-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17053,14 +17043,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46190</v>
+        <v>45253</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17072,13 +17062,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17121,7 +17106,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 31621-2022</t>
+          <t>A 10634-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17135,10 +17120,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44775</v>
+        <v>45367</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17151,7 +17136,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17194,7 +17179,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 2314-2022</t>
+          <t>A 34402-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17208,10 +17193,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44578</v>
+        <v>44792</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17224,7 +17209,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17267,7 +17252,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 46998-2024</t>
+          <t>A 18336-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17281,10 +17266,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45586</v>
+        <v>45041</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17296,8 +17281,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17357,7 +17347,7 @@
         <v>44543</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17413,7 +17403,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 2263-2023</t>
+          <t>A 72073-2021</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17427,10 +17417,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44941</v>
+        <v>44544</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17443,7 +17433,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2</v>
+        <v>9.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17486,7 +17476,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 50252-2024</t>
+          <t>A 16596-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17500,10 +17490,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45600</v>
+        <v>45030</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17559,7 +17549,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 4832-2022</t>
+          <t>A 5758-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17573,10 +17563,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44592</v>
+        <v>45694</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17589,7 +17579,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17632,7 +17622,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 13504-2026</t>
+          <t>A 25435-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17646,10 +17636,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46094</v>
+        <v>45463</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17661,8 +17651,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17705,7 +17700,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 14036-2026</t>
+          <t>A 22798-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17719,10 +17714,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46098</v>
+        <v>45448</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17734,8 +17729,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17778,7 +17778,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 38835-2024</t>
+          <t>A 7368-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17792,10 +17792,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45547</v>
+        <v>45704</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17851,7 +17851,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 59871-2024</t>
+          <t>A 14143-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17865,10 +17865,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45640</v>
+        <v>45392</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17924,7 +17924,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 2309-2024</t>
+          <t>A 14732-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17938,10 +17938,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45310</v>
+        <v>44655</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 16585-2026</t>
+          <t>A 10635-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18011,10 +18011,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46112</v>
+        <v>45367</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18070,7 +18070,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 2306-2024</t>
+          <t>A 57967-2021</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18084,10 +18084,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45310</v>
+        <v>44487</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18143,7 +18143,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 59200-2023</t>
+          <t>A 2306-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18157,10 +18157,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45253</v>
+        <v>45310</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18216,7 +18216,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 18096-2026</t>
+          <t>A 14675-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18230,10 +18230,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46125</v>
+        <v>45397</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18289,7 +18289,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 3851-2025</t>
+          <t>A 36296-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18303,10 +18303,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45683</v>
+        <v>44803</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18362,7 +18362,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 18101-2026</t>
+          <t>A 6015-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18376,10 +18376,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46125</v>
+        <v>44964</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18435,7 +18435,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 26263-2023</t>
+          <t>A 8911-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18449,10 +18449,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45091</v>
+        <v>45713</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18508,7 +18508,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 44646-2024</t>
+          <t>A 20743-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18522,10 +18522,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45574</v>
+        <v>45436</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 36305-2022</t>
+          <t>A 44646-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18595,10 +18595,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44803</v>
+        <v>45574</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18654,7 +18654,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 10374-2022</t>
+          <t>A 59938-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18668,10 +18668,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44623</v>
+        <v>45642</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18727,7 +18727,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 4069-2025</t>
+          <t>A 53956-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18741,10 +18741,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45684</v>
+        <v>45616</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18756,13 +18756,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18805,7 +18800,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 31621-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18819,10 +18814,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44489</v>
+        <v>44775</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18835,7 +18830,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18878,7 +18873,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 58244-2025</t>
+          <t>A 49604-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18892,10 +18887,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45985</v>
+        <v>45207</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18908,7 +18903,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18951,7 +18946,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 27792-2023</t>
+          <t>A 249-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18965,10 +18960,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45098</v>
+        <v>44565</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18981,7 +18976,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.3</v>
+        <v>5.5</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19024,7 +19019,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 20184-2026</t>
+          <t>A 28195-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19038,10 +19033,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46139</v>
+        <v>44746</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19053,8 +19048,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I244" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19097,7 +19097,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 32839-2023</t>
+          <t>A 14954-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19111,10 +19111,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45109</v>
+        <v>45398</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19170,7 +19170,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 53956-2024</t>
+          <t>A 65002-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19184,10 +19184,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45616</v>
+        <v>45287</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>4.7</v>
+        <v>6.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19243,7 +19243,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 17816-2023</t>
+          <t>A 22008-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19257,10 +19257,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45037</v>
+        <v>45784</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19316,7 +19316,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 33566-2024</t>
+          <t>A 38499-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19330,10 +19330,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45520</v>
+        <v>46282</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19389,7 +19389,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 16596-2023</t>
+          <t>A 57220-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19403,10 +19403,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45030</v>
+        <v>45629</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19462,7 +19462,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 43285-2024</t>
+          <t>A 38494-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19476,10 +19476,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45568</v>
+        <v>46282</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 64374-2023</t>
+          <t>A 38489-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19549,10 +19549,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45280</v>
+        <v>46282</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19608,7 +19608,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 59061-2023</t>
+          <t>A 38517-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19622,10 +19622,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45252</v>
+        <v>46283</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19637,8 +19637,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I252" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19681,7 +19686,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 30951-2022</t>
+          <t>A 45599-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19695,10 +19700,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44768</v>
+        <v>45194</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19711,7 +19716,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19754,7 +19759,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 5758-2025</t>
+          <t>A 11558-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19768,10 +19773,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45694</v>
+        <v>45727</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19827,7 +19832,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 38499-2026</t>
+          <t>A 33266-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19841,10 +19846,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46282</v>
+        <v>46246</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19857,7 +19862,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19900,7 +19905,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 38494-2026</t>
+          <t>A 33037-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19914,10 +19919,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46282</v>
+        <v>46245</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19930,7 +19935,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19973,7 +19978,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 38489-2026</t>
+          <t>A 33233-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19987,10 +19992,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46282</v>
+        <v>46246</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20003,7 +20008,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20046,7 +20051,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 38517-2026</t>
+          <t>A 36795-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20060,10 +20065,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46283</v>
+        <v>45538</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20075,13 +20080,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I258" t="n">
-        <v>3.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20124,7 +20124,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 33037-2026</t>
+          <t>A 45591-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20138,10 +20138,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46245</v>
+        <v>45194</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20197,7 +20197,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 33233-2026</t>
+          <t>A 22566-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20211,10 +20211,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46246</v>
+        <v>45789</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 33266-2026</t>
+          <t>A 30260-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20284,10 +20284,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46246</v>
+        <v>45827</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 41128-2026</t>
+          <t>A 34846-2026</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20357,10 +20357,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46300</v>
+        <v>46258</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20416,7 +20416,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 34846-2026</t>
+          <t>A 41128-2026</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20430,10 +20430,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>46258</v>
+        <v>46300</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20506,7 +20506,7 @@
         <v>44755</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45569</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45266</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>44901</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45476</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45476</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45499</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>46037</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45093</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44809</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57743-2021</t>
+          <t>A 54177-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44484</v>
+        <v>45232</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1307,151 +1307,151 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 54177-2023 artfynd.xlsx", "A 54177-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 54177-2023 karta.png", "A 54177-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 54177-2023 georefererad karta.tif", "A 54177-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 54177-2023 FSC-klagomål.docx", "A 54177-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 54177-2023 FSC-klagomål mail.docx", "A 54177-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 54177-2023 tillsynsbegäran.docx", "A 54177-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 54177-2023 tillsynsbegäran mail.docx", "A 54177-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 57743-2021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44484</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 57743-2021 artfynd.xlsx", "A 57743-2021")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 57743-2021 karta.png", "A 57743-2021")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 57743-2021 georefererad karta.tif", "A 57743-2021")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 57743-2021 FSC-klagomål.docx", "A 57743-2021")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 57743-2021 FSC-klagomål mail.docx", "A 57743-2021")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 57743-2021 tillsynsbegäran.docx", "A 57743-2021")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 57743-2021 tillsynsbegäran mail.docx", "A 57743-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 38039-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45544</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8909-2025</t>
+          <t>A 53498-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45713</v>
+        <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.6</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1490,10 +1490,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1508,55 +1508,55 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 54177-2023</t>
+          <t>A 1320-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45232</v>
+        <v>44936</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1626,42 +1626,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 54177-2023 artfynd.xlsx", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 54177-2023 karta.png", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 54177-2023 georefererad karta.tif", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 54177-2023 FSC-klagomål.docx", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 54177-2023 FSC-klagomål mail.docx", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 54177-2023 tillsynsbegäran.docx", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 54177-2023 tillsynsbegäran mail.docx", "A 54177-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 56642-2022</t>
+          <t>A 40853-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44893</v>
+        <v>45558</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1690,19 +1690,14 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1732,39 +1727,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
         <v/>
       </c>
     </row>
@@ -1788,7 +1783,7 @@
         <v>45907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53498-2023</t>
+          <t>A 62010-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1895,10 +1890,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45230</v>
+        <v>44914</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1911,19 +1906,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>7.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1935,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1951,42 +1946,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 53498-2023 artfynd.xlsx", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 53498-2023 karta.png", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 53498-2023 georefererad karta.tif", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 53498-2023 FSC-klagomål.docx", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 53498-2023 FSC-klagomål mail.docx", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 53498-2023 tillsynsbegäran.docx", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 53498-2023 tillsynsbegäran mail.docx", "A 53498-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1320-2023</t>
+          <t>A 11330-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2000,10 +1995,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44936</v>
+        <v>45371</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2015,8 +2010,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2056,42 +2056,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 1320-2023 artfynd.xlsx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 11330-2024 artfynd.xlsx", "A 11330-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 1320-2023 karta.png", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 11330-2024 karta.png", "A 11330-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 1320-2023 georefererad karta.tif", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 11330-2024 georefererad karta.tif", "A 11330-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 1320-2023 FSC-klagomål.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 11330-2024 FSC-klagomål.docx", "A 11330-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 1320-2023 FSC-klagomål mail.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 11330-2024 FSC-klagomål mail.docx", "A 11330-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 1320-2023 tillsynsbegäran.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 11330-2024 tillsynsbegäran.docx", "A 11330-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 1320-2023 tillsynsbegäran mail.docx", "A 1320-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 11330-2024 tillsynsbegäran mail.docx", "A 11330-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 23794-2023</t>
+          <t>A 35453-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45078</v>
+        <v>45531</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2157,261 +2157,260 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 8909-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45713</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 8909-2025 artfynd.xlsx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 8909-2025 karta.png", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 8909-2025 georefererad karta.tif", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 8909-2025 FSC-klagomål.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 8909-2025 FSC-klagomål mail.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 8909-2025 tillsynsbegäran.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 8909-2025 tillsynsbegäran mail.docx", "A 8909-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 23794-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIL</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 23794-2023 artfynd.xlsx", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 23794-2023 karta.png", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 23794-2023 georefererad karta.tif", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 23794-2023 FSC-klagomål.docx", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 23794-2023 FSC-klagomål mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 23794-2023 tillsynsbegäran.docx", "A 23794-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 23794-2023 tillsynsbegäran mail.docx", "A 23794-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 11330-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45371</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 11330-2024 artfynd.xlsx", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 11330-2024 karta.png", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 11330-2024 georefererad karta.tif", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 11330-2024 FSC-klagomål.docx", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 11330-2024 FSC-klagomål mail.docx", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 11330-2024 tillsynsbegäran.docx", "A 11330-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 11330-2024 tillsynsbegäran mail.docx", "A 11330-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 62010-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44914</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KIL</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 62010-2022 artfynd.xlsx", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 62010-2022 karta.png", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 62010-2022 georefererad karta.tif", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 62010-2022 FSC-klagomål.docx", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 62010-2022 FSC-klagomål mail.docx", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 62010-2022 tillsynsbegäran.docx", "A 62010-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 62010-2022 tillsynsbegäran mail.docx", "A 62010-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40853-2024</t>
+          <t>A 56642-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2425,10 +2424,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45558</v>
+        <v>44893</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2440,14 +2439,19 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2477,46 +2481,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 40853-2024 artfynd.xlsx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 56642-2022 artfynd.xlsx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 40853-2024 karta.png", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 56642-2022 karta.png", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 40853-2024 georefererad karta.tif", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 56642-2022 georefererad karta.tif", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 40853-2024 FSC-klagomål.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 56642-2022 FSC-klagomål.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 40853-2024 FSC-klagomål mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 56642-2022 FSC-klagomål mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 40853-2024 tillsynsbegäran.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 56642-2022 tillsynsbegäran.docx", "A 56642-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 40853-2024 tillsynsbegäran mail.docx", "A 40853-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 56642-2022 tillsynsbegäran mail.docx", "A 56642-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 35453-2024</t>
+          <t>A 38039-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,10 +2534,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45531</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2549,10 +2553,10 @@
         <v>4</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2586,39 +2590,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 35453-2024 artfynd.xlsx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/artfynd/A 38039-2024 artfynd.xlsx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 35453-2024 karta.png", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor/A 38039-2024 karta.png", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 35453-2024 georefererad karta.tif", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/kartor_geotiff/A 38039-2024 georefererad karta.tif", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 35453-2024 FSC-klagomål.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 38039-2024 FSC-klagomål.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 35453-2024 FSC-klagomål mail.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 38039-2024 FSC-klagomål mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 35453-2024 tillsynsbegäran.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 38039-2024 tillsynsbegäran.docx", "A 38039-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 35453-2024 tillsynsbegäran mail.docx", "A 35453-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/fåglar/A 35453-2024 prioriterade fågelarter.docx", "A 35453-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 38039-2024 tillsynsbegäran mail.docx", "A 38039-2024")</f>
         <v/>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44847</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36302-2022</t>
+          <t>A 57069-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44803</v>
+        <v>44482</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 57069-2021</t>
+          <t>A 36302-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44482</v>
+        <v>44803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>44846</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44511</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44581</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44636</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44538</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44517</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4450-2022</t>
+          <t>A 40107-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44589</v>
+        <v>44820</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3895,8 +3895,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3939,7 +3944,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57314-2021</t>
+          <t>A 4448-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3953,10 +3958,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44483</v>
+        <v>44589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3969,7 +3974,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4012,7 +4017,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 64543-2021</t>
+          <t>A 4445-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4026,10 +4031,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44511</v>
+        <v>44589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4042,7 +4047,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4085,7 +4090,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64559-2021</t>
+          <t>A 4450-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4099,10 +4104,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44511</v>
+        <v>44589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4115,7 +4120,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4158,7 +4163,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 65900-2021</t>
+          <t>A 57065-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4172,10 +4177,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44517</v>
+        <v>44482</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4188,7 +4193,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4231,7 +4236,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40107-2022</t>
+          <t>A 57314-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4245,10 +4250,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44820</v>
+        <v>44483</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4260,13 +4265,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4309,7 +4309,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4448-2022</t>
+          <t>A 48787-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44589</v>
+        <v>44859</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64552-2021</t>
+          <t>A 64543-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4399,7 +4399,7 @@
         <v>44511</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4455,7 +4455,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62135-2021</t>
+          <t>A 64559-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44502</v>
+        <v>44511</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4528,7 +4528,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 66809-2021</t>
+          <t>A 64552-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44522</v>
+        <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>13.7</v>
+        <v>0.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 48787-2022</t>
+          <t>A 62135-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44859</v>
+        <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4691,7 +4691,7 @@
         <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33907-2022</t>
+          <t>A 37962-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4757,14 +4757,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44790</v>
+        <v>44811</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4776,13 +4776,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4825,7 +4820,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4445-2022</t>
+          <t>A 65900-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4839,10 +4834,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44589</v>
+        <v>44517</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4855,7 +4850,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4898,7 +4893,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57065-2021</t>
+          <t>A 56762-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4912,10 +4907,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44482</v>
+        <v>44481</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4928,7 +4923,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4971,7 +4966,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37962-2022</t>
+          <t>A 33907-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4981,14 +4976,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44811</v>
+        <v>44790</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5000,8 +4995,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 56762-2021</t>
+          <t>A 66809-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44481</v>
+        <v>44522</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>13.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>44517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12280-2024</t>
+          <t>A 3851-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45378</v>
+        <v>45683</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59061-2023</t>
+          <t>A 26263-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45252</v>
+        <v>45091</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3-2023</t>
+          <t>A 249-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44927</v>
+        <v>44565</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46288-2022</t>
+          <t>A 41074-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44847</v>
+        <v>44825</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 46290-2022</t>
+          <t>A 39055-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44847</v>
+        <v>45548</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5511,8 +5511,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>8.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5555,7 +5560,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14651-2024</t>
+          <t>A 17946-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5569,10 +5574,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45397</v>
+        <v>45419</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5585,7 +5590,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5628,7 +5633,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26270-2022</t>
+          <t>A 52438-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5642,10 +5647,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44735</v>
+        <v>44874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5658,7 +5663,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5701,7 +5706,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31032-2024</t>
+          <t>A 59064-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5715,10 +5720,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45501</v>
+        <v>45252</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5731,7 +5736,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5770,11 +5775,31 @@
         <v>0</v>
       </c>
       <c r="V63" s="2" t="inlineStr"/>
+      <c r="Z63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AA63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AB63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AC63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
+      <c r="AD63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31033-2024</t>
+          <t>A 44646-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5788,10 +5813,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45501</v>
+        <v>45574</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5804,7 +5829,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5847,7 +5872,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56641-2023</t>
+          <t>A 46117-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5861,10 +5886,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45243</v>
+        <v>44847</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5877,7 +5902,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5920,7 +5945,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36971-2024</t>
+          <t>A 12652-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5934,10 +5959,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45538</v>
+        <v>45384</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5950,7 +5975,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>17.9</v>
+        <v>5.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5993,7 +6018,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17816-2023</t>
+          <t>A 14984-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6007,10 +6032,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45037</v>
+        <v>45399</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6023,7 +6048,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6066,7 +6091,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36305-2022</t>
+          <t>A 14987-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6080,10 +6105,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44803</v>
+        <v>45399</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6096,7 +6121,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6139,7 +6164,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15962-2025</t>
+          <t>A 53416-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6153,10 +6178,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45749</v>
+        <v>45229</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6169,7 +6194,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6212,7 +6237,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7586-2025</t>
+          <t>A 36305-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6226,10 +6251,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45705</v>
+        <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6242,7 +6267,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6285,7 +6310,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 242-2024</t>
+          <t>A 14143-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6299,10 +6324,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45294</v>
+        <v>45392</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6314,13 +6339,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6363,7 +6383,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29615-2022</t>
+          <t>A 17806-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6377,10 +6397,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44754</v>
+        <v>45037</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6392,13 +6412,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6441,7 +6456,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61210-2023</t>
+          <t>A 29615-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6455,10 +6470,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45264</v>
+        <v>44754</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6470,8 +6485,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6514,7 +6534,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17946-2024</t>
+          <t>A 10374-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6528,10 +6548,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45419</v>
+        <v>44623</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6544,7 +6564,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6587,7 +6607,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35611-2024</t>
+          <t>A 4069-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6601,10 +6621,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45531</v>
+        <v>45684</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6616,8 +6636,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6660,7 +6685,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38760-2023</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6674,10 +6699,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45163</v>
+        <v>44489</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6690,7 +6715,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6733,7 +6758,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17806-2023</t>
+          <t>A 46288-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6747,10 +6772,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45037</v>
+        <v>44847</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6763,7 +6788,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6806,7 +6831,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43285-2024</t>
+          <t>A 46290-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6820,10 +6845,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45568</v>
+        <v>44847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6836,7 +6861,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6879,7 +6904,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32982-2025</t>
+          <t>A 59944-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6893,10 +6918,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45839</v>
+        <v>45642</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6908,13 +6933,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6957,7 +6977,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 32410-2025</t>
+          <t>A 59503-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6971,10 +6991,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45838</v>
+        <v>44907</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6987,7 +7007,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7030,7 +7050,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6687-2023</t>
+          <t>A 3-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7044,10 +7064,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44966</v>
+        <v>44927</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7060,7 +7080,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7103,7 +7123,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 64193-2021</t>
+          <t>A 65008-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7117,10 +7137,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44510</v>
+        <v>45287</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7133,7 +7153,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7176,7 +7196,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59064-2023</t>
+          <t>A 62807-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7190,10 +7210,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45252</v>
+        <v>45271</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7206,7 +7226,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7245,31 +7265,11 @@
         <v>0</v>
       </c>
       <c r="V83" s="2" t="inlineStr"/>
-      <c r="Z83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/knärot/A 59064-2023 karta knärot.png", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomål/A 59064-2023 FSC-klagomål.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/klagomålsmail/A 59064-2023 FSC-klagomål mail.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsyn/A 59064-2023 tillsynsbegäran.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
-      <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1715/tillsynsmail/A 59064-2023 tillsynsbegäran mail.docx", "A 59064-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38835-2024</t>
+          <t>A 30599-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7283,10 +7283,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45547</v>
+        <v>45112</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>10.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7342,7 +7342,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3851-2025</t>
+          <t>A 10635-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45683</v>
+        <v>45367</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7415,7 +7415,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17473-2025</t>
+          <t>A 27792-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7429,10 +7429,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45757</v>
+        <v>45098</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7488,7 +7488,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35449-2024</t>
+          <t>A 32839-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7502,10 +7502,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45531</v>
+        <v>45109</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39039-2024</t>
+          <t>A 64518-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7575,10 +7575,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45548</v>
+        <v>44511</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7590,13 +7590,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7639,7 +7634,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 64140-2023</t>
+          <t>A 14675-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7653,10 +7648,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45279</v>
+        <v>45397</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7669,7 +7664,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7712,7 +7707,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62669-2023</t>
+          <t>A 64193-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7726,10 +7721,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45271</v>
+        <v>44510</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7742,7 +7737,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7785,7 +7780,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10476-2025</t>
+          <t>A 58679-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7799,10 +7794,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45720</v>
+        <v>44489</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7814,13 +7809,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7863,7 +7853,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2309-2024</t>
+          <t>A 53956-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7877,10 +7867,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45310</v>
+        <v>45616</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7893,7 +7883,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7936,7 +7926,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15039-2022</t>
+          <t>A 17816-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7950,10 +7940,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44657</v>
+        <v>45037</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7966,7 +7956,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8009,7 +7999,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 65007-2023</t>
+          <t>A 33566-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8023,10 +8013,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45287</v>
+        <v>45520</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8039,7 +8029,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>14.2</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8082,7 +8072,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 15472-2025</t>
+          <t>A 16596-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8096,10 +8086,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45747</v>
+        <v>45030</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8112,7 +8102,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8155,7 +8145,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13504-2026</t>
+          <t>A 62667-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8169,10 +8159,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46094</v>
+        <v>45271</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8185,7 +8175,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8228,7 +8218,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 18049-2024</t>
+          <t>A 43285-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8242,10 +8232,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45420</v>
+        <v>45568</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8258,7 +8248,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8301,7 +8291,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 41074-2022</t>
+          <t>A 64374-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8315,10 +8305,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44825</v>
+        <v>45280</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8331,7 +8321,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8374,7 +8364,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30951-2022</t>
+          <t>A 59061-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8388,10 +8378,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44768</v>
+        <v>45252</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8404,7 +8394,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8447,7 +8437,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 14036-2026</t>
+          <t>A 38760-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8461,10 +8451,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46098</v>
+        <v>45163</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8477,7 +8467,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8520,7 +8510,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 25409-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8534,10 +8524,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44489</v>
+        <v>45463</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8549,8 +8539,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8593,7 +8588,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 45672-2024</t>
+          <t>A 30951-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8607,10 +8602,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45579</v>
+        <v>44768</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8623,7 +8618,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8666,7 +8661,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 2077-2024</t>
+          <t>A 14651-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8680,10 +8675,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45309</v>
+        <v>45397</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8696,7 +8691,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8739,7 +8734,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 62807-2023</t>
+          <t>A 242-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8753,10 +8748,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45271</v>
+        <v>45294</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8768,8 +8763,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>8.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8812,7 +8812,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 47786-2025</t>
+          <t>A 5758-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8826,10 +8826,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45931</v>
+        <v>45694</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8885,7 +8885,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47801-2025</t>
+          <t>A 35611-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45931</v>
+        <v>45531</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8958,7 +8958,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47704-2025</t>
+          <t>A 5753-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8972,10 +8972,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45931</v>
+        <v>45694</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 47722-2025</t>
+          <t>A 36971-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45931</v>
+        <v>45538</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>17.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9104,7 +9104,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 47798-2025</t>
+          <t>A 15962-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45931</v>
+        <v>45749</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9177,7 +9177,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 47804-2025</t>
+          <t>A 20745-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9191,10 +9191,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45931</v>
+        <v>45436</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9250,7 +9250,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47784-2025</t>
+          <t>A 37622-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45931</v>
+        <v>45541</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9323,7 +9323,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 48427-2025</t>
+          <t>A 57967-2021</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45934</v>
+        <v>44487</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9396,7 +9396,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 30599-2023</t>
+          <t>A 10910-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9410,10 +9410,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45112</v>
+        <v>44991</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>10.1</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9469,7 +9469,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 57151-2023</t>
+          <t>A 15472-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9483,10 +9483,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45245</v>
+        <v>45747</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9542,7 +9542,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 16585-2026</t>
+          <t>A 56765-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9556,10 +9556,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46112</v>
+        <v>44481</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9615,7 +9615,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 52621-2025</t>
+          <t>A 35084-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9629,10 +9629,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45953</v>
+        <v>45527</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9688,7 +9688,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 52622-2025</t>
+          <t>A 22798-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9702,10 +9702,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45953</v>
+        <v>45448</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9717,8 +9717,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9761,7 +9766,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 2708-2023</t>
+          <t>A 44660-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9775,10 +9780,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44942</v>
+        <v>45574</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9791,7 +9796,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9834,7 +9839,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 52697-2025</t>
+          <t>A 44666-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9848,10 +9853,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45956</v>
+        <v>45574</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9864,7 +9869,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9907,7 +9912,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 2990-2022</t>
+          <t>A 22008-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9921,10 +9926,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44581</v>
+        <v>45784</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9937,7 +9942,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9980,7 +9985,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 2994-2022</t>
+          <t>A 666-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9994,10 +9999,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44581</v>
+        <v>44930</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10010,7 +10015,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10053,7 +10058,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 53839-2025</t>
+          <t>A 3996-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10067,10 +10072,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45961</v>
+        <v>44587</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10083,7 +10088,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10126,7 +10131,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 5753-2025</t>
+          <t>A 14954-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10140,10 +10145,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45694</v>
+        <v>45398</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10156,7 +10161,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10199,7 +10204,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 64374-2023</t>
+          <t>A 65002-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10213,10 +10218,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45280</v>
+        <v>45287</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10229,7 +10234,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10272,7 +10277,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53841-2025</t>
+          <t>A 25435-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10286,10 +10291,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45961</v>
+        <v>45463</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10301,8 +10306,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10345,7 +10355,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 18101-2026</t>
+          <t>A 20476-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10359,10 +10369,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46125</v>
+        <v>45435</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10375,7 +10385,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10418,7 +10428,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 18096-2026</t>
+          <t>A 57220-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10432,10 +10442,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46125</v>
+        <v>45629</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10448,7 +10458,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10491,7 +10501,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 54593-2025</t>
+          <t>A 11929-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10505,10 +10515,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45965</v>
+        <v>44995</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10564,7 +10574,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59944-2024</t>
+          <t>A 14732-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10578,10 +10588,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45642</v>
+        <v>44655</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10594,7 +10604,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10637,7 +10647,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 17635-2022</t>
+          <t>A 57483-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10651,10 +10661,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44680</v>
+        <v>44896</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10666,8 +10676,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10710,7 +10725,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 57011-2025</t>
+          <t>A 8911-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10724,10 +10739,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45978</v>
+        <v>45713</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10739,13 +10754,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10788,7 +10798,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 35084-2024</t>
+          <t>A 47798-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10802,10 +10812,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45527</v>
+        <v>45931</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10818,7 +10828,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10861,7 +10871,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 18948-2024</t>
+          <t>A 47804-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10875,10 +10885,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45427</v>
+        <v>45931</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10891,7 +10901,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10934,7 +10944,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56957-2025</t>
+          <t>A 18049-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10944,14 +10954,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45978</v>
+        <v>45420</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10963,13 +10973,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11012,7 +11017,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 12252-2024</t>
+          <t>A 47801-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11026,10 +11031,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45378</v>
+        <v>45931</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11042,7 +11047,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11085,7 +11090,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 41526-2023</t>
+          <t>A 47784-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11099,10 +11104,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45175</v>
+        <v>45931</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11114,13 +11119,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1847-2025</t>
+          <t>A 45599-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11177,10 +11177,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45671</v>
+        <v>45194</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11236,7 +11236,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 20259-2026</t>
+          <t>A 29698-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11246,14 +11246,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46139</v>
+        <v>45484</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11309,7 +11309,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 58244-2025</t>
+          <t>A 11558-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11323,10 +11323,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45985</v>
+        <v>45727</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11382,7 +11382,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 46117-2022</t>
+          <t>A 37620-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11396,10 +11396,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44847</v>
+        <v>45541</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 24247-2025</t>
+          <t>A 47722-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11469,10 +11469,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45797</v>
+        <v>45931</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11528,7 +11528,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 11929-2023</t>
+          <t>A 15721-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11542,10 +11542,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44995</v>
+        <v>45404</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11601,7 +11601,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 61436-2025</t>
+          <t>A 47704-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11615,10 +11615,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46001</v>
+        <v>45931</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11674,7 +11674,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 59871-2024</t>
+          <t>A 47786-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11688,10 +11688,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45640</v>
+        <v>45931</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11747,7 +11747,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 2314-2022</t>
+          <t>A 45672-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44578</v>
+        <v>45579</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11820,7 +11820,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 58679-2021</t>
+          <t>A 31032-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44489</v>
+        <v>45501</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11893,7 +11893,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 10910-2023</t>
+          <t>A 31033-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11907,10 +11907,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44991</v>
+        <v>45501</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11966,7 +11966,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 12652-2024</t>
+          <t>A 2708-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11980,10 +11980,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45384</v>
+        <v>44942</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12039,7 +12039,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 27792-2023</t>
+          <t>A 48427-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12053,10 +12053,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45098</v>
+        <v>45934</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12112,7 +12112,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 20184-2026</t>
+          <t>A 50461-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46139</v>
+        <v>45601</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12185,7 +12185,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 60201-2024</t>
+          <t>A 10634-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12199,10 +12199,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45642</v>
+        <v>45367</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12258,7 +12258,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 63811-2025</t>
+          <t>A 39039-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12272,10 +12272,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46020</v>
+        <v>45548</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12287,8 +12287,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12331,7 +12336,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 20476-2024</t>
+          <t>A 46445-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12345,10 +12350,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45435</v>
+        <v>45582</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12361,7 +12366,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12404,7 +12409,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 26438-2025</t>
+          <t>A 18948-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12418,10 +12423,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45807</v>
+        <v>45427</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12434,7 +12439,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12477,7 +12482,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 32839-2023</t>
+          <t>A 12272-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12491,10 +12496,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45109</v>
+        <v>45378</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12507,7 +12512,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12550,7 +12555,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 34408-2024</t>
+          <t>A 12281-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12560,14 +12565,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45525</v>
+        <v>45378</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12580,7 +12585,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12623,7 +12628,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 2688-2023</t>
+          <t>A 7586-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12637,10 +12642,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44942</v>
+        <v>45705</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12653,7 +12658,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12696,7 +12701,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 3174-2026</t>
+          <t>A 22566-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12710,10 +12715,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46041</v>
+        <v>45789</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12726,7 +12731,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12769,7 +12774,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 26910-2025</t>
+          <t>A 45591-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12783,10 +12788,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45811</v>
+        <v>45194</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12799,7 +12804,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.7</v>
+        <v>11</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12842,7 +12847,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 969-2022</t>
+          <t>A 49604-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12856,10 +12861,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44571</v>
+        <v>45207</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12872,7 +12877,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12915,7 +12920,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 15721-2024</t>
+          <t>A 59938-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12929,10 +12934,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45404</v>
+        <v>45642</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12945,7 +12950,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12988,7 +12993,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 73251-2021</t>
+          <t>A 36795-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13002,10 +13007,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44550</v>
+        <v>45538</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13018,7 +13023,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13061,7 +13066,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 14984-2024</t>
+          <t>A 2688-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13075,10 +13080,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45399</v>
+        <v>44942</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13091,7 +13096,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13134,7 +13139,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 14987-2024</t>
+          <t>A 62669-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13148,10 +13153,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45399</v>
+        <v>45271</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13164,7 +13169,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13207,7 +13212,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 33475-2024</t>
+          <t>A 15039-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13221,10 +13226,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45519</v>
+        <v>44657</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13237,7 +13242,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13280,7 +13285,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 10374-2022</t>
+          <t>A 5286-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13294,10 +13299,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44623</v>
+        <v>44959</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13310,7 +13315,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13353,7 +13358,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 12281-2024</t>
+          <t>A 7368-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13367,10 +13372,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45378</v>
+        <v>45704</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13383,7 +13388,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13426,7 +13431,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 5286-2023</t>
+          <t>A 23786-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13440,10 +13445,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44959</v>
+        <v>44722</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13456,7 +13461,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5.3</v>
+        <v>7.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13499,7 +13504,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 5754-2025</t>
+          <t>A 21032-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13513,10 +13518,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45694</v>
+        <v>45061</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13529,7 +13534,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13572,7 +13577,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 57386-2024</t>
+          <t>A 55306-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13586,10 +13591,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45629</v>
+        <v>45621</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13602,7 +13607,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13645,7 +13650,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 12272-2024</t>
+          <t>A 26270-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13659,10 +13664,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45378</v>
+        <v>44735</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13675,7 +13680,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13718,7 +13723,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 39055-2024</t>
+          <t>A 57386-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13732,10 +13737,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45548</v>
+        <v>45629</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13747,13 +13752,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 21032-2023</t>
+          <t>A 30260-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13810,10 +13810,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45061</v>
+        <v>45827</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13869,7 +13869,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 57483-2022</t>
+          <t>A 52621-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13883,10 +13883,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44896</v>
+        <v>45953</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13898,13 +13898,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13947,7 +13942,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 56765-2021</t>
+          <t>A 52622-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13961,10 +13956,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44481</v>
+        <v>45953</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13977,7 +13972,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14020,7 +14015,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 43194-2025</t>
+          <t>A 52697-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14034,10 +14029,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45910</v>
+        <v>45956</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14050,7 +14045,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14093,7 +14088,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 46998-2024</t>
+          <t>A 53841-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14107,10 +14102,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45586</v>
+        <v>45961</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14166,7 +14161,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 65008-2023</t>
+          <t>A 6015-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14180,10 +14175,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45287</v>
+        <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14196,7 +14191,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14239,7 +14234,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 2-2023</t>
+          <t>A 53839-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14253,10 +14248,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44927</v>
+        <v>45961</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14269,7 +14264,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14312,7 +14307,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 4832-2022</t>
+          <t>A 20743-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14326,10 +14321,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44592</v>
+        <v>45436</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14342,7 +14337,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14385,7 +14380,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 62667-2023</t>
+          <t>A 32982-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14399,10 +14394,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45271</v>
+        <v>45839</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14414,8 +14409,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14458,7 +14458,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 39492-2023</t>
+          <t>A 32410-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14472,10 +14472,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45166</v>
+        <v>45838</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14487,13 +14487,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>24.9</v>
+        <v>4.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14536,7 +14531,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 22226-2026</t>
+          <t>A 60201-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14550,10 +14545,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46150</v>
+        <v>45642</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14566,7 +14561,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14609,7 +14604,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 64518-2021</t>
+          <t>A 65007-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14623,10 +14618,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44511</v>
+        <v>45287</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14639,7 +14634,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.1</v>
+        <v>14.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14682,7 +14677,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 25409-2024</t>
+          <t>A 39492-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14696,10 +14691,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45463</v>
+        <v>45166</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14717,7 +14712,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.7</v>
+        <v>24.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14760,7 +14755,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 2263-2023</t>
+          <t>A 54593-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14774,10 +14769,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44941</v>
+        <v>45965</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14790,7 +14785,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14833,7 +14828,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 50461-2024</t>
+          <t>A 17473-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14847,10 +14842,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45601</v>
+        <v>45757</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14863,7 +14858,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14906,7 +14901,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 61229-2022</t>
+          <t>A 64140-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14920,10 +14915,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44915</v>
+        <v>45279</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14936,7 +14931,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14979,7 +14974,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 46445-2024</t>
+          <t>A 35449-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14993,10 +14988,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45582</v>
+        <v>45531</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15009,7 +15004,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15052,7 +15047,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 4069-2025</t>
+          <t>A 28195-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15066,10 +15061,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45684</v>
+        <v>44746</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15083,11 +15078,11 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15130,7 +15125,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 44660-2024</t>
+          <t>A 8910-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15144,10 +15139,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45574</v>
+        <v>45713</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15160,7 +15155,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15203,7 +15198,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 44666-2024</t>
+          <t>A 8916-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15217,10 +15212,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45574</v>
+        <v>45713</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15233,7 +15228,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15276,7 +15271,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 20745-2024</t>
+          <t>A 34408-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15286,14 +15281,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45436</v>
+        <v>45525</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15306,7 +15301,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15349,7 +15344,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 8541-2025</t>
+          <t>A 12280-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15363,10 +15358,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45709</v>
+        <v>45378</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15379,7 +15374,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15422,7 +15417,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 7822-2024</t>
+          <t>A 72073-2021</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15436,10 +15431,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45349</v>
+        <v>44544</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15452,7 +15447,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.7</v>
+        <v>9.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15495,7 +15490,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 24262-2025</t>
+          <t>A 18117-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15509,10 +15504,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45797</v>
+        <v>45761</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15525,7 +15520,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15568,7 +15563,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 52438-2022</t>
+          <t>A 6687-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15582,10 +15577,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44874</v>
+        <v>44966</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15598,7 +15593,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15641,7 +15636,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 50252-2024</t>
+          <t>A 5754-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15655,10 +15650,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45600</v>
+        <v>45694</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15671,7 +15666,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15714,7 +15709,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 23327-2026</t>
+          <t>A 73251-2021</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15728,10 +15723,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46162</v>
+        <v>44550</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15744,7 +15739,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15787,7 +15782,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 18117-2025</t>
+          <t>A 59012-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15801,10 +15796,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45761</v>
+        <v>45636</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15817,7 +15812,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15860,7 +15855,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 3996-2022</t>
+          <t>A 56641-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15874,10 +15869,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44587</v>
+        <v>45243</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15890,7 +15885,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15933,7 +15928,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 55306-2024</t>
+          <t>A 61229-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15947,10 +15942,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45621</v>
+        <v>44915</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15963,7 +15958,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16006,7 +16001,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 24640-2026</t>
+          <t>A 2-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16020,10 +16015,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46171</v>
+        <v>44927</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16079,7 +16074,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37620-2024</t>
+          <t>A 17635-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16093,10 +16088,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45541</v>
+        <v>44680</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16109,7 +16104,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16152,7 +16147,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37622-2024</t>
+          <t>A 57011-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16166,10 +16161,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45541</v>
+        <v>45978</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16181,8 +16176,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16225,7 +16225,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 53416-2023</t>
+          <t>A 36296-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16239,10 +16239,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45229</v>
+        <v>44803</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 29698-2024</t>
+          <t>A 34402-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16308,14 +16308,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45484</v>
+        <v>44792</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 23786-2022</t>
+          <t>A 2077-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16385,10 +16385,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44722</v>
+        <v>45309</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>7.3</v>
+        <v>0.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16444,7 +16444,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 666-2023</t>
+          <t>A 61210-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16458,10 +16458,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44930</v>
+        <v>45264</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16517,7 +16517,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 59012-2024</t>
+          <t>A 57151-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16531,10 +16531,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45636</v>
+        <v>45245</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16590,7 +16590,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 26263-2023</t>
+          <t>A 13504-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16604,10 +16604,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45091</v>
+        <v>46094</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16663,7 +16663,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 8910-2025</t>
+          <t>A 14036-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16677,10 +16677,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45713</v>
+        <v>46098</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16736,7 +16736,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 8916-2025</t>
+          <t>A 12252-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16750,10 +16750,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45713</v>
+        <v>45378</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16809,7 +16809,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 33566-2024</t>
+          <t>A 2990-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16823,10 +16823,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45520</v>
+        <v>44581</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16882,7 +16882,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 27638-2026</t>
+          <t>A 2994-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16892,14 +16892,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46190</v>
+        <v>44581</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16911,13 +16911,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16960,7 +16955,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 59503-2022</t>
+          <t>A 56957-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16970,14 +16965,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44907</v>
+        <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16989,8 +16984,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17033,7 +17033,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 59200-2023</t>
+          <t>A 10476-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17047,10 +17047,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45253</v>
+        <v>45720</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17062,8 +17062,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17106,7 +17111,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 10634-2024</t>
+          <t>A 16585-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17120,10 +17125,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45367</v>
+        <v>46112</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17179,7 +17184,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 34402-2022</t>
+          <t>A 41526-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17193,10 +17198,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44792</v>
+        <v>45175</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17208,8 +17213,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17252,7 +17262,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 18336-2023</t>
+          <t>A 18096-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17266,10 +17276,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45041</v>
+        <v>46125</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17281,13 +17291,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17330,7 +17335,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 71728-2021</t>
+          <t>A 18101-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17344,10 +17349,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44543</v>
+        <v>46125</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17360,7 +17365,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17403,7 +17408,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 72073-2021</t>
+          <t>A 61436-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17417,10 +17422,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44544</v>
+        <v>46001</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17433,7 +17438,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17476,7 +17481,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 16596-2023</t>
+          <t>A 31621-2022</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17490,10 +17495,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45030</v>
+        <v>44775</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17506,7 +17511,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17549,7 +17554,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 5758-2025</t>
+          <t>A 2314-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17563,10 +17568,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45694</v>
+        <v>44578</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17622,7 +17627,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 25435-2024</t>
+          <t>A 46998-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17636,10 +17641,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45463</v>
+        <v>45586</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17651,13 +17656,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17700,7 +17700,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 22798-2024</t>
+          <t>A 2263-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17714,10 +17714,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45448</v>
+        <v>44941</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17729,13 +17729,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17778,7 +17773,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 7368-2025</t>
+          <t>A 58244-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17792,10 +17787,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45704</v>
+        <v>45985</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17808,7 +17803,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17851,7 +17846,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 14143-2024</t>
+          <t>A 20184-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17865,10 +17860,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45392</v>
+        <v>46139</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17881,7 +17876,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17924,7 +17919,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 14732-2022</t>
+          <t>A 63811-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17938,10 +17933,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44655</v>
+        <v>46020</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17954,7 +17949,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17997,7 +17992,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 10635-2024</t>
+          <t>A 50252-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18011,10 +18006,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45367</v>
+        <v>45600</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18027,7 +18022,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18070,7 +18065,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 57967-2021</t>
+          <t>A 4832-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18084,10 +18079,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44487</v>
+        <v>44592</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18100,7 +18095,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18143,7 +18138,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 2306-2024</t>
+          <t>A 26438-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18157,10 +18152,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45310</v>
+        <v>45807</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18173,7 +18168,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18216,7 +18211,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 14675-2024</t>
+          <t>A 1847-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18230,10 +18225,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45397</v>
+        <v>45671</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18246,7 +18241,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18289,7 +18284,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 36296-2022</t>
+          <t>A 969-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18303,10 +18298,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44803</v>
+        <v>44571</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18319,7 +18314,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18362,7 +18357,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 6015-2023</t>
+          <t>A 3174-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18376,10 +18371,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44964</v>
+        <v>46041</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18392,7 +18387,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18435,7 +18430,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 8911-2025</t>
+          <t>A 20259-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18449,10 +18444,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45713</v>
+        <v>46139</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18465,7 +18460,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18508,7 +18503,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 20743-2024</t>
+          <t>A 38835-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18522,10 +18517,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45436</v>
+        <v>45547</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18538,7 +18533,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18581,7 +18576,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 44646-2024</t>
+          <t>A 59871-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18595,10 +18590,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45574</v>
+        <v>45640</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18611,7 +18606,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18654,7 +18649,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 59938-2024</t>
+          <t>A 24247-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18668,10 +18663,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45642</v>
+        <v>45797</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18684,7 +18679,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18727,7 +18722,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 53956-2024</t>
+          <t>A 2309-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18741,10 +18736,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45616</v>
+        <v>45310</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18757,7 +18752,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18800,7 +18795,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 31621-2022</t>
+          <t>A 2306-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18814,10 +18809,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44775</v>
+        <v>45310</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18830,7 +18825,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18873,7 +18868,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 49604-2023</t>
+          <t>A 59200-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18887,10 +18882,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45207</v>
+        <v>45253</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18903,7 +18898,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18946,7 +18941,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 249-2022</t>
+          <t>A 43194-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18960,10 +18955,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44565</v>
+        <v>45910</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18976,7 +18971,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19019,7 +19014,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 28195-2022</t>
+          <t>A 33475-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19033,10 +19028,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44746</v>
+        <v>45519</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19048,13 +19043,8 @@
           <t>KIL</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19097,7 +19087,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 14954-2024</t>
+          <t>A 26910-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19111,10 +19101,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45398</v>
+        <v>45811</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19127,7 +19117,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19170,7 +19160,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 65002-2023</t>
+          <t>A 22226-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19184,10 +19174,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45287</v>
+        <v>46150</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19200,7 +19190,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>6.9</v>
+        <v>2.1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19243,7 +19233,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 22008-2025</t>
+          <t>A 7822-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19257,10 +19247,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45784</v>
+        <v>45349</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19273,7 +19263,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19316,7 +19306,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 38499-2026</t>
+          <t>A 8541-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19330,10 +19320,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46282</v>
+        <v>45709</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19346,7 +19336,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19389,7 +19379,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 57220-2024</t>
+          <t>A 24262-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19403,10 +19393,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45629</v>
+        <v>45797</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19419,7 +19409,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19462,7 +19452,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 38494-2026</t>
+          <t>A 23327-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19476,10 +19466,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46282</v>
+        <v>46162</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19492,7 +19482,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19535,7 +19525,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 38489-2026</t>
+          <t>A 24640-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19549,10 +19539,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46282</v>
+        <v>46171</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19608,7 +19598,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 38517-2026</t>
+          <t>A 27638-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19618,14 +19608,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46283</v>
+        <v>46190</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19639,11 +19629,11 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I252" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19686,7 +19676,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 45599-2023</t>
+          <t>A 71728-2021</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19700,10 +19690,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45194</v>
+        <v>44543</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19716,7 +19706,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19759,7 +19749,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 11558-2025</t>
+          <t>A 38499-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19773,10 +19763,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45727</v>
+        <v>46282</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19789,7 +19779,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19832,7 +19822,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 33266-2026</t>
+          <t>A 38494-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19846,10 +19836,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46246</v>
+        <v>46282</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19862,7 +19852,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -19905,7 +19895,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 33037-2026</t>
+          <t>A 38489-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19919,10 +19909,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46245</v>
+        <v>46282</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19935,7 +19925,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -19978,7 +19968,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 33233-2026</t>
+          <t>A 38517-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19992,10 +19982,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46246</v>
+        <v>46283</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20007,8 +19997,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I257" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20051,7 +20046,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 36795-2024</t>
+          <t>A 33037-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20065,10 +20060,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45538</v>
+        <v>46245</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20081,7 +20076,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>9.300000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20124,7 +20119,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 45591-2023</t>
+          <t>A 33233-2026</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20138,10 +20133,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45194</v>
+        <v>46246</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20154,7 +20149,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>11</v>
+        <v>1.2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20197,7 +20192,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 22566-2025</t>
+          <t>A 33266-2026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20211,10 +20206,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45789</v>
+        <v>46246</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20227,7 +20222,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20270,7 +20265,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 30260-2025</t>
+          <t>A 41128-2026</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20284,10 +20279,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45827</v>
+        <v>46300</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20300,7 +20295,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20360,7 +20355,7 @@
         <v>46258</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20416,7 +20411,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 41128-2026</t>
+          <t>A 18336-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20430,10 +20425,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>46300</v>
+        <v>45041</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20445,8 +20440,13 @@
           <t>KIL</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I263" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20506,7 +20506,7 @@
         <v>44755</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45569</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45266</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>44901</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45476</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45476</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45499</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>46037</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>

--- a/Översikt KIL.xlsx
+++ b/Översikt KIL.xlsx
@@ -601,7 +601,7 @@
         <v>45971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45093</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44809</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44581</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>44581</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>45232</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>44484</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>44936</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>45558</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>45907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44914</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45371</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45531</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>45713</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45078</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>44893</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44501</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44594</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44847</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44482</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44846</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44511</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44581</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44636</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44538</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44517</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44820</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>44589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>44589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>44482</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44483</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>44859</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44511</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44511</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44502</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44811</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>44517</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44481</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>44790</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44522</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45683</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45091</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44565</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44825</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45548</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45419</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>44874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45252</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45574</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>44847</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45384</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45399</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>45399</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>45229</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45392</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>45037</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44754</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>44623</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>45684</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44489</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44847</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45642</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>44907</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>44927</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45287</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>45271</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45112</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>45367</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>45098</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>45109</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>44511</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>45397</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44510</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>44489</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45616</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45037</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45520</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>45030</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45271</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45568</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45280</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>45252</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>45163</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>45463</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44768</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45397</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>45294</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45694</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>45531</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45694</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>45538</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>45749</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>45436</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>45541</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>44487</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>44991</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>45747</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>44481</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>45527</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>45448</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45574</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>45574</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45784</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>44930</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>44587</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>45398</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45287</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>45463</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45435</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45629</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>44995</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44655</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>44896</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>45713</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45931</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45931</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45420</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>45931</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>45931</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45194</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45484</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45727</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45541</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45931</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45404</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45931</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>45931</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45579</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45501</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45501</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>44942</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>45934</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>45601</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45367</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>45548</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45582</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>45427</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>45378</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45378</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45705</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45789</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45194</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45207</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45642</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45538</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>44942</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45271</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44657</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>44959</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45704</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44722</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>45061</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45621</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44735</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45629</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45827</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>45953</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45953</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45956</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45961</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45961</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45436</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45839</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45838</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45642</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45287</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45166</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45965</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45757</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>45279</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45531</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>44746</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45713</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>45713</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>45525</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45378</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>44544</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45761</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44966</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45694</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>44550</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>45636</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45243</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44915</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>44927</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>44680</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45978</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44803</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>44792</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>45309</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>45264</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45245</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>46094</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>46098</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45378</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44581</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44581</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45720</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>46112</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45175</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>46125</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>46125</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>46001</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>44775</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>44578</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45586</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44941</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45985</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>46139</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>46020</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45600</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>44592</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>45807</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45671</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>44571</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>46041</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>46139</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>45547</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>45640</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45797</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45310</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45310</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45253</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45910</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45519</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45811</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>46150</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45349</v>
       </c>
   